--- a/data/deliverables/resume_portfolio/resume_portfolio.xlsx
+++ b/data/deliverables/resume_portfolio/resume_portfolio.xlsx
@@ -197,9 +197,7 @@
       <c r="P2">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nokia/2026-04-08/69b622b956973837413b6091/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nokia/2026-04-08/69b622b956973837413b6091/resume.md")</f>
       </c>
-      <c r="Q2">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nokia/2026-04-08/69b622b956973837413b6091/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nokia/2026-04-08/69b622b956973837413b6091/resume.pdf")</f>
-      </c>
+      <c r="Q2"/>
       <c r="R2">
         <f>HYPERLINK("https://fa-evmr-saasfaprod1.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/job/23181/?utm_medium=jobshare&amp;src=SNS-102","https://fa-evmr-saasfaprod1.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/job/23181/?utm_medium=jobshare&amp;src=SNS-102")</f>
       </c>
@@ -257,9 +255,7 @@
       <c r="P3">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/general-motors/2026-04-08/69ac98f42747003c3d523072/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/general-motors/2026-04-08/69ac98f42747003c3d523072/resume.md")</f>
       </c>
-      <c r="Q3">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/general-motors/2026-04-08/69ac98f42747003c3d523072/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/general-motors/2026-04-08/69ac98f42747003c3d523072/resume.pdf")</f>
-      </c>
+      <c r="Q3"/>
       <c r="R3">
         <f>HYPERLINK("https://generalmotors.wd5.myworkdayjobs.com/Careers_GM/job/Sunnyvale-California-United-States-of-America/Senior-ML-AI-Software-Engineer---Evaluation-Insights_JR-202519722?source=LinkedIn","https://generalmotors.wd5.myworkdayjobs.com/Careers_GM/job/Sunnyvale-California-United-States-of-America/Senior-ML-AI-Software-Engineer---Evaluation-Insights_JR-202519722?source=LinkedIn")</f>
       </c>
@@ -375,9 +371,7 @@
       <c r="P5">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d650cfe63cea7a8b6685f9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d650cfe63cea7a8b6685f9/resume.md")</f>
       </c>
-      <c r="Q5">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d650cfe63cea7a8b6685f9/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d650cfe63cea7a8b6685f9/resume.pdf")</f>
-      </c>
+      <c r="Q5"/>
       <c r="R5">
         <f>HYPERLINK("https://apply.careers.microsoft.com/careers/job/1970393556856000?utm_source=linkedin&amp;domain=microsoft.com&amp;src=LinkedIn","https://apply.careers.microsoft.com/careers/job/1970393556856000?utm_source=linkedin&amp;domain=microsoft.com&amp;src=LinkedIn")</f>
       </c>
@@ -517,9 +511,7 @@
       <c r="P7">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-08/699d6a6d81476f6176b63dce/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-08/699d6a6d81476f6176b63dce/resume.md")</f>
       </c>
-      <c r="Q7">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-08/699d6a6d81476f6176b63dce/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-08/699d6a6d81476f6176b63dce/resume.pdf")</f>
-      </c>
+      <c r="Q7"/>
       <c r="R7">
         <f>HYPERLINK("https://www.amazon.jobs/jobs/3127822/sde-ml-engineer-frontier-ai-robotics?cmpid=SPLICX0248M&amp;utm_source=linkedin.com&amp;utm_campaign=cxro&amp;utm_medium=social_media&amp;utm_content=job_posting&amp;ss=paid","https://www.amazon.jobs/jobs/3127822/sde-ml-engineer-frontier-ai-robotics?cmpid=SPLICX0248M&amp;utm_source=linkedin.com&amp;utm_campaign=cxro&amp;utm_medium=social_media&amp;utm_content=job_posting&amp;ss=paid")</f>
       </c>
@@ -585,9 +577,7 @@
       <c r="P8">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d6501bcfdc6132f9469623/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d6501bcfdc6132f9469623/resume.md")</f>
       </c>
-      <c r="Q8">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d6501bcfdc6132f9469623/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d6501bcfdc6132f9469623/resume.pdf")</f>
-      </c>
+      <c r="Q8"/>
       <c r="R8">
         <f>HYPERLINK("https://apply.careers.microsoft.com/careers/job/1970393556857255?utm_source=linkedin&amp;domain=microsoft.com&amp;src=LinkedIn","https://apply.careers.microsoft.com/careers/job/1970393556857255?utm_source=linkedin&amp;domain=microsoft.com&amp;src=LinkedIn")</f>
       </c>
@@ -653,9 +643,7 @@
       <c r="P9">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d65016cfdc6132f946961a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d65016cfdc6132f946961a/resume.md")</f>
       </c>
-      <c r="Q9">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d65016cfdc6132f946961a/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d65016cfdc6132f946961a/resume.pdf")</f>
-      </c>
+      <c r="Q9"/>
       <c r="R9">
         <f>HYPERLINK("https://apply.careers.microsoft.com/careers/job/1970393556853526?utm_source=linkedin&amp;domain=microsoft.com&amp;src=LinkedIn","https://apply.careers.microsoft.com/careers/job/1970393556853526?utm_source=linkedin&amp;domain=microsoft.com&amp;src=LinkedIn")</f>
       </c>
@@ -1011,9 +999,7 @@
       <c r="P15">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba9dd95697383741406e1b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba9dd95697383741406e1b/resume.md")</f>
       </c>
-      <c r="Q15">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba9dd95697383741406e1b/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba9dd95697383741406e1b/resume.pdf")</f>
-      </c>
+      <c r="Q15"/>
       <c r="R15">
         <f>HYPERLINK("https://careers.google.com/jobs/results/82077133681107654-software-engineer/?src=Online/LinkedIn/linkedin_us&amp;utm_source=linkedin&amp;utm_medium=jobposting&amp;utm_campaign=contract","https://careers.google.com/jobs/results/82077133681107654-software-engineer/?src=Online/LinkedIn/linkedin_us&amp;utm_source=linkedin&amp;utm_medium=jobposting&amp;utm_campaign=contract")</f>
       </c>
@@ -1079,9 +1065,7 @@
       <c r="P16">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d64f92706f771673baa293/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d64f92706f771673baa293/resume.md")</f>
       </c>
-      <c r="Q16">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d64f92706f771673baa293/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d64f92706f771673baa293/resume.pdf")</f>
-      </c>
+      <c r="Q16"/>
       <c r="R16">
         <f>HYPERLINK("https://apply.careers.microsoft.com/careers/job/1970393556619657?utm_source=linkedin&amp;domain=microsoft.com&amp;src=LinkedIn","https://apply.careers.microsoft.com/careers/job/1970393556619657?utm_source=linkedin&amp;domain=microsoft.com&amp;src=LinkedIn")</f>
       </c>
@@ -1221,9 +1205,7 @@
       <c r="P18">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba92be06c1ba00c54cb3d5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba92be06c1ba00c54cb3d5/resume.md")</f>
       </c>
-      <c r="Q18">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba92be06c1ba00c54cb3d5/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba92be06c1ba00c54cb3d5/resume.pdf")</f>
-      </c>
+      <c r="Q18"/>
       <c r="R18">
         <f>HYPERLINK("https://careers.google.com/jobs/results/142994355647324870-software-engineer/?src=Online/LinkedIn/linkedin_us&amp;utm_source=linkedin&amp;utm_medium=jobposting&amp;utm_campaign=contract","https://careers.google.com/jobs/results/142994355647324870-software-engineer/?src=Online/LinkedIn/linkedin_us&amp;utm_source=linkedin&amp;utm_medium=jobposting&amp;utm_campaign=contract")</f>
       </c>
@@ -1289,9 +1271,7 @@
       <c r="P19">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-08/69d64ba948f0c8161d2f7366/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-08/69d64ba948f0c8161d2f7366/resume.md")</f>
       </c>
-      <c r="Q19">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-08/69d64ba948f0c8161d2f7366/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-08/69d64ba948f0c8161d2f7366/resume.pdf")</f>
-      </c>
+      <c r="Q19"/>
       <c r="R19">
         <f>HYPERLINK("https://www.linkedin.com/jobs/view/4386975352","https://www.linkedin.com/jobs/view/4386975352")</f>
       </c>
@@ -1365,9 +1345,7 @@
       <c r="P20">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba8bc25697383741402b0f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba8bc25697383741402b0f/resume.md")</f>
       </c>
-      <c r="Q20">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba8bc25697383741402b0f/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba8bc25697383741402b0f/resume.pdf")</f>
-      </c>
+      <c r="Q20"/>
       <c r="R20">
         <f>HYPERLINK("https://careers.google.com/jobs/results/111930608938033862-software-engineer-iii/?src=Online/LinkedIn/linkedin_us&amp;utm_source=linkedin&amp;utm_medium=jobposting&amp;utm_campaign=contract","https://careers.google.com/jobs/results/111930608938033862-software-engineer-iii/?src=Online/LinkedIn/linkedin_us&amp;utm_source=linkedin&amp;utm_medium=jobposting&amp;utm_campaign=contract")</f>
       </c>
@@ -1433,9 +1411,7 @@
       <c r="P21">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/garmin/2026-04-08/699dccab81476f6176b6af20/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/garmin/2026-04-08/699dccab81476f6176b6af20/resume.md")</f>
       </c>
-      <c r="Q21">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/garmin/2026-04-08/699dccab81476f6176b6af20/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/garmin/2026-04-08/699dccab81476f6176b6af20/resume.pdf")</f>
-      </c>
+      <c r="Q21"/>
       <c r="R21">
         <f>HYPERLINK("https://careers.garmin.com/jobs/18098?lang=en-us&amp;iis=Job+Board&amp;iisn=LinkedIn","https://careers.garmin.com/jobs/18098?lang=en-us&amp;iis=Job+Board&amp;iisn=LinkedIn")</f>
       </c>
@@ -1625,9 +1601,7 @@
       <c r="P24">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/netjets/2026-04-08/69ba8d643b74eb1e2c887f2b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/netjets/2026-04-08/69ba8d643b74eb1e2c887f2b/resume.md")</f>
       </c>
-      <c r="Q24">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/netjets/2026-04-08/69ba8d643b74eb1e2c887f2b/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/netjets/2026-04-08/69ba8d643b74eb1e2c887f2b/resume.pdf")</f>
-      </c>
+      <c r="Q24"/>
       <c r="R24">
         <f>HYPERLINK("https://netjets.jobs.hr.cloud.sap/us/job/Columbus-Software-Engineer-(NJUS)-OH-43219/1374174100/?feedId=386400&amp;utm_source=LinkedInJobPostings&amp;utm_campaign=NJUS_LinkedIn&amp;src=LinkedIn","https://netjets.jobs.hr.cloud.sap/us/job/Columbus-Software-Engineer-(NJUS)-OH-43219/1374174100/?feedId=386400&amp;utm_source=LinkedInJobPostings&amp;utm_campaign=NJUS_LinkedIn&amp;src=LinkedIn")</f>
       </c>
@@ -1685,9 +1659,7 @@
       <c r="P25">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-08/69d6128ae63cea7a8b66768d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-08/69d6128ae63cea7a8b66768d/resume.md")</f>
       </c>
-      <c r="Q25">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-08/69d6128ae63cea7a8b66768d/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-08/69d6128ae63cea7a8b66768d/resume.pdf")</f>
-      </c>
+      <c r="Q25"/>
       <c r="R25">
         <f>HYPERLINK("https://wd1.myworkdaysite.com/recruiting/ssctech/SSCTechnologies/job/Jacksonville-FL/Data-Scientist_R32997-1?source=LinkedIn","https://wd1.myworkdaysite.com/recruiting/ssctech/SSCTechnologies/job/Jacksonville-FL/Data-Scientist_R32997-1?source=LinkedIn")</f>
       </c>
@@ -1761,9 +1733,7 @@
       <c r="P26">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualcomm/2026-04-08/69a504290da45516f16da9ce/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualcomm/2026-04-08/69a504290da45516f16da9ce/resume.md")</f>
       </c>
-      <c r="Q26">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualcomm/2026-04-08/69a504290da45516f16da9ce/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualcomm/2026-04-08/69a504290da45516f16da9ce/resume.pdf")</f>
-      </c>
+      <c r="Q26"/>
       <c r="R26">
         <f>HYPERLINK("https://careers.qualcomm.com/careers/job/446717033485?hl=en-US&amp;utm_source=linkedin&amp;domain=qualcomm.com&amp;source=APPLICANT_SOURCE-6-2","https://careers.qualcomm.com/careers/job/446717033485?hl=en-US&amp;utm_source=linkedin&amp;domain=qualcomm.com&amp;source=APPLICANT_SOURCE-6-2")</f>
       </c>
@@ -1837,9 +1807,7 @@
       <c r="P27">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/699c43cb81476f6176b4bd94/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/699c43cb81476f6176b4bd94/resume.md")</f>
       </c>
-      <c r="Q27">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/699c43cb81476f6176b4bd94/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/699c43cb81476f6176b4bd94/resume.pdf")</f>
-      </c>
+      <c r="Q27"/>
       <c r="R27">
         <f>HYPERLINK("https://careers.google.com/jobs/results/124660456668177094-practice-customer-engineer/?src=Online/LinkedIn/linkedin_us&amp;utm_source=linkedin&amp;utm_medium=jobposting&amp;utm_campaign=contract","https://careers.google.com/jobs/results/124660456668177094-practice-customer-engineer/?src=Online/LinkedIn/linkedin_us&amp;utm_source=linkedin&amp;utm_medium=jobposting&amp;utm_campaign=contract")</f>
       </c>
@@ -1905,9 +1873,7 @@
       <c r="P28">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/the-walt-disney-company/2026-04-08/69b2b061ae2a534885e9dc50/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/the-walt-disney-company/2026-04-08/69b2b061ae2a534885e9dc50/resume.md")</f>
       </c>
-      <c r="Q28">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/the-walt-disney-company/2026-04-08/69b2b061ae2a534885e9dc50/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/the-walt-disney-company/2026-04-08/69b2b061ae2a534885e9dc50/resume.pdf")</f>
-      </c>
+      <c r="Q28"/>
       <c r="R28">
         <f>HYPERLINK("https://www.disneycareers.com/job/-/-/391/92655058736?source=LINKEDIN_JOB_SLOTS","https://www.disneycareers.com/job/-/-/391/92655058736?source=LINKEDIN_JOB_SLOTS")</f>
       </c>
@@ -1965,9 +1931,7 @@
       <c r="P29">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kla/2026-04-08/69d58da3366bb95ba5546066/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kla/2026-04-08/69d58da3366bb95ba5546066/resume.md")</f>
       </c>
-      <c r="Q29">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kla/2026-04-08/69d58da3366bb95ba5546066/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kla/2026-04-08/69d58da3366bb95ba5546066/resume.pdf")</f>
-      </c>
+      <c r="Q29"/>
       <c r="R29">
         <f>HYPERLINK("https://kla.wd1.myworkdayjobs.com/Search/job/Milpitas-CA/Software-Engineer_2634918-2?bid=370&amp;source=Job_Board_LinkedIn","https://kla.wd1.myworkdayjobs.com/Search/job/Milpitas-CA/Software-Engineer_2634918-2?bid=370&amp;source=Job_Board_LinkedIn")</f>
       </c>
@@ -2033,9 +1997,7 @@
       <c r="P30">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kla/2026-04-08/6969fa36639b452fb57ff3d1/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kla/2026-04-08/6969fa36639b452fb57ff3d1/resume.md")</f>
       </c>
-      <c r="Q30">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kla/2026-04-08/6969fa36639b452fb57ff3d1/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kla/2026-04-08/6969fa36639b452fb57ff3d1/resume.pdf")</f>
-      </c>
+      <c r="Q30"/>
       <c r="R30">
         <f>HYPERLINK("https://www.linkedin.com/jobs/view/3514793139","https://www.linkedin.com/jobs/view/3514793139")</f>
       </c>
@@ -2093,9 +2055,7 @@
       <c r="P31">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d6468852a5bf58001280a7/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d6468852a5bf58001280a7/resume.md")</f>
       </c>
-      <c r="Q31">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d6468852a5bf58001280a7/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d6468852a5bf58001280a7/resume.pdf")</f>
-      </c>
+      <c r="Q31"/>
       <c r="R31">
         <f>HYPERLINK("https://www.amazon.jobs/jobs/10385689/sdeii-query-processing-aurora-dsql?cmpid=SPLICX0248M&amp;utm_source=linkedin.com&amp;utm_campaign=cxro&amp;utm_medium=social_media&amp;utm_content=job_posting&amp;ss=paid","https://www.amazon.jobs/jobs/10385689/sdeii-query-processing-aurora-dsql?cmpid=SPLICX0248M&amp;utm_source=linkedin.com&amp;utm_campaign=cxro&amp;utm_medium=social_media&amp;utm_content=job_posting&amp;ss=paid")</f>
       </c>
@@ -2227,9 +2187,7 @@
       <c r="P33">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-08/69d642dc366bb95ba554bf11/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-08/69d642dc366bb95ba554bf11/resume.md")</f>
       </c>
-      <c r="Q33">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-08/69d642dc366bb95ba554bf11/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-08/69d642dc366bb95ba554bf11/resume.pdf")</f>
-      </c>
+      <c r="Q33"/>
       <c r="R33">
         <f>HYPERLINK("https://www.amazon.jobs/jobs/10385654/business-intelligence-engineer-rl-analytics?cmpid=SPLICX0248M&amp;utm_source=linkedin.com&amp;utm_campaign=cxro&amp;utm_medium=social_media&amp;utm_content=job_posting&amp;ss=paid","https://www.amazon.jobs/jobs/10385654/business-intelligence-engineer-rl-analytics?cmpid=SPLICX0248M&amp;utm_source=linkedin.com&amp;utm_campaign=cxro&amp;utm_medium=social_media&amp;utm_content=job_posting&amp;ss=paid")</f>
       </c>
@@ -2287,9 +2245,7 @@
       <c r="P34">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640ea706f771673ba9fb7/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640ea706f771673ba9fb7/resume.md")</f>
       </c>
-      <c r="Q34">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640ea706f771673ba9fb7/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640ea706f771673ba9fb7/resume.pdf")</f>
-      </c>
+      <c r="Q34"/>
       <c r="R34">
         <f>HYPERLINK("https://www.amazon.jobs/jobs/3206100/system-development-engineer-aws-redshift?cmpid=SPLICX0248M&amp;utm_source=linkedin.com&amp;utm_campaign=cxro&amp;utm_medium=social_media&amp;utm_content=job_posting&amp;ss=paid","https://www.amazon.jobs/jobs/3206100/system-development-engineer-aws-redshift?cmpid=SPLICX0248M&amp;utm_source=linkedin.com&amp;utm_campaign=cxro&amp;utm_medium=social_media&amp;utm_content=job_posting&amp;ss=paid")</f>
       </c>
@@ -2355,9 +2311,7 @@
       <c r="P35">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640de52a5bf5800128045/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640de52a5bf5800128045/resume.md")</f>
       </c>
-      <c r="Q35">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640de52a5bf5800128045/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640de52a5bf5800128045/resume.pdf")</f>
-      </c>
+      <c r="Q35"/>
       <c r="R35">
         <f>HYPERLINK("https://www.amazon.jobs/jobs/10385675/software-development-engineer-ii--builder-experience-genai-genai-codex-?cmpid=SPLICX0248M&amp;utm_source=linkedin.com&amp;utm_campaign=cxro&amp;utm_medium=social_media&amp;utm_content=job_posting&amp;ss=paid","https://www.amazon.jobs/jobs/10385675/software-development-engineer-ii--builder-experience-genai-genai-codex-?cmpid=SPLICX0248M&amp;utm_source=linkedin.com&amp;utm_campaign=cxro&amp;utm_medium=social_media&amp;utm_content=job_posting&amp;ss=paid")</f>
       </c>
@@ -2481,9 +2435,7 @@
       <c r="P37">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640cde63cea7a8b6682f4/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640cde63cea7a8b6682f4/resume.md")</f>
       </c>
-      <c r="Q37">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640cde63cea7a8b6682f4/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640cde63cea7a8b6682f4/resume.pdf")</f>
-      </c>
+      <c r="Q37"/>
       <c r="R37">
         <f>HYPERLINK("https://www.amazon.jobs/jobs/10385710/software-development-engineer-training--certifications?cmpid=SPLICX0248M&amp;utm_source=linkedin.com&amp;utm_campaign=cxro&amp;utm_medium=social_media&amp;utm_content=job_posting&amp;ss=paid","https://www.amazon.jobs/jobs/10385710/software-development-engineer-training--certifications?cmpid=SPLICX0248M&amp;utm_source=linkedin.com&amp;utm_campaign=cxro&amp;utm_medium=social_media&amp;utm_content=job_posting&amp;ss=paid")</f>
       </c>
@@ -2599,9 +2551,7 @@
       <c r="P39">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sony-interactive-entertainment/2026-04-08/698130ba49964d25b5e4135f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sony-interactive-entertainment/2026-04-08/698130ba49964d25b5e4135f/resume.md")</f>
       </c>
-      <c r="Q39">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sony-interactive-entertainment/2026-04-08/698130ba49964d25b5e4135f/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sony-interactive-entertainment/2026-04-08/698130ba49964d25b5e4135f/resume.pdf")</f>
-      </c>
+      <c r="Q39"/>
       <c r="R39">
         <f>HYPERLINK("https://boards.greenhouse.io/embed/job_app?token=5789638004&amp;utm_source=jobright","https://boards.greenhouse.io/embed/job_app?token=5789638004&amp;utm_source=jobright")</f>
       </c>
@@ -2865,9 +2815,7 @@
       <c r="P43">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intel/2026-04-08/69d63f4dcfdc6132f9469275/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intel/2026-04-08/69d63f4dcfdc6132f9469275/resume.md")</f>
       </c>
-      <c r="Q43">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intel/2026-04-08/69d63f4dcfdc6132f9469275/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intel/2026-04-08/69d63f4dcfdc6132f9469275/resume.pdf")</f>
-      </c>
+      <c r="Q43"/>
       <c r="R43">
         <f>HYPERLINK("https://intel.wd1.myworkdayjobs.com/external/job/US-Arizona-Phoenix/Junior-Software-Performance-Analysis-and-Optimization-Engineer_JR0280963","https://intel.wd1.myworkdayjobs.com/external/job/US-Arizona-Phoenix/Junior-Software-Performance-Analysis-and-Optimization-Engineer_JR0280963")</f>
       </c>
@@ -3049,9 +2997,7 @@
       <c r="P46">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/travelers/2026-04-08/69cc5d28366bb95ba54ef2a0/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/travelers/2026-04-08/69cc5d28366bb95ba54ef2a0/resume.md")</f>
       </c>
-      <c r="Q46">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/travelers/2026-04-08/69cc5d28366bb95ba54ef2a0/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/travelers/2026-04-08/69cc5d28366bb95ba54ef2a0/resume.pdf")</f>
-      </c>
+      <c r="Q46"/>
       <c r="R46">
         <f>HYPERLINK("https://careers.travelers.com/job/22643600/data-scientist-applied-research-hartford-ct/?source=S0791","https://careers.travelers.com/job/22643600/data-scientist-applied-research-hartford-ct/?source=S0791")</f>
       </c>
@@ -3191,9 +3137,7 @@
       <c r="P48">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/snowflake/2026-04-08/699e4a4e81476f6176b73aab/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/snowflake/2026-04-08/699e4a4e81476f6176b73aab/resume.md")</f>
       </c>
-      <c r="Q48">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/snowflake/2026-04-08/699e4a4e81476f6176b73aab/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/snowflake/2026-04-08/699e4a4e81476f6176b73aab/resume.pdf")</f>
-      </c>
+      <c r="Q48"/>
       <c r="R48">
         <f>HYPERLINK("https://careers.snowflake.com/us/en/job/SNCOUSD43A772689EB407E83CE3B247592DF49EXTERNALENUS950ABC308BFB4F159BB962713C93AA5F/Software-Engineer-Frontend?utm_source=Q2P9NP2NNP&amp;utm_medium=phenom-feeds&amp;gh_src=ed5543a62","https://careers.snowflake.com/us/en/job/SNCOUSD43A772689EB407E83CE3B247592DF49EXTERNALENUS950ABC308BFB4F159BB962713C93AA5F/Software-Engineer-Frontend?utm_source=Q2P9NP2NNP&amp;utm_medium=phenom-feeds&amp;gh_src=ed5543a62")</f>
       </c>
@@ -3251,9 +3195,7 @@
       <c r="P49">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hp/2026-04-08/69d6319c706f771673ba9d05/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hp/2026-04-08/69d6319c706f771673ba9d05/resume.md")</f>
       </c>
-      <c r="Q49">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hp/2026-04-08/69d6319c706f771673ba9d05/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hp/2026-04-08/69d6319c706f771673ba9d05/resume.pdf")</f>
-      </c>
+      <c r="Q49"/>
       <c r="R49">
         <f>HYPERLINK("https://HPINC.contacthr.com/151731015?src=Linkedin+Full+Feed","https://HPINC.contacthr.com/151731015?src=Linkedin+Full+Feed")</f>
       </c>
@@ -3311,9 +3253,7 @@
       <c r="P50">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-08/699e270c81476f6176b707f8/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-08/699e270c81476f6176b707f8/resume.md")</f>
       </c>
-      <c r="Q50">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-08/699e270c81476f6176b707f8/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-08/699e270c81476f6176b707f8/resume.pdf")</f>
-      </c>
+      <c r="Q50"/>
       <c r="R50">
         <f>HYPERLINK("https://paypal.eightfold.ai/careers?domain=paypal.com&amp;sort_by=relevance&amp;query=R0134713&amp;Codes=W-LINKEDIN","https://paypal.eightfold.ai/careers?domain=paypal.com&amp;sort_by=relevance&amp;query=R0134713&amp;Codes=W-LINKEDIN")</f>
       </c>
@@ -3379,9 +3319,7 @@
       <c r="P51">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-08/699e256cce78e77b4fe33807/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-08/699e256cce78e77b4fe33807/resume.md")</f>
       </c>
-      <c r="Q51">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-08/699e256cce78e77b4fe33807/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-08/699e256cce78e77b4fe33807/resume.pdf")</f>
-      </c>
+      <c r="Q51"/>
       <c r="R51">
         <f>HYPERLINK("https://paypal.eightfold.ai/careers?domain=paypal.com&amp;sort_by=relevance&amp;query=R0135240&amp;Codes=W-LINKEDIN","https://paypal.eightfold.ai/careers?domain=paypal.com&amp;sort_by=relevance&amp;query=R0135240&amp;Codes=W-LINKEDIN")</f>
       </c>
@@ -3447,9 +3385,7 @@
       <c r="P52">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hdr/2026-04-08/69a2c0750da45516f16c299c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hdr/2026-04-08/69a2c0750da45516f16c299c/resume.md")</f>
       </c>
-      <c r="Q52">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hdr/2026-04-08/69a2c0750da45516f16c299c/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hdr/2026-04-08/69a2c0750da45516f16c299c/resume.pdf")</f>
-      </c>
+      <c r="Q52"/>
       <c r="R52">
         <f>HYPERLINK("https://hdr.taleo.net/careersection/ex/jobdetail.ftl?job=190711&amp;lang=en&amp;src=SNS-10025","https://hdr.taleo.net/careersection/ex/jobdetail.ftl?job=190711&amp;lang=en&amp;src=SNS-10025")</f>
       </c>
@@ -3507,9 +3443,7 @@
       <c r="P53">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69cc9f35cfdc6132f94112d9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69cc9f35cfdc6132f94112d9/resume.md")</f>
       </c>
-      <c r="Q53">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69cc9f35cfdc6132f94112d9/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69cc9f35cfdc6132f94112d9/resume.pdf")</f>
-      </c>
+      <c r="Q53"/>
       <c r="R53">
         <f>HYPERLINK("https://JPMorganChase.contacthr.com/151492194","https://JPMorganChase.contacthr.com/151492194")</f>
       </c>
@@ -3633,9 +3567,7 @@
       <c r="P55">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/synopsys-inc/2026-04-08/69bb8c0706c1ba00c54e14e4/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/synopsys-inc/2026-04-08/69bb8c0706c1ba00c54e14e4/resume.md")</f>
       </c>
-      <c r="Q55">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/synopsys-inc/2026-04-08/69bb8c0706c1ba00c54e14e4/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/synopsys-inc/2026-04-08/69bb8c0706c1ba00c54e14e4/resume.pdf")</f>
-      </c>
+      <c r="Q55"/>
       <c r="R55">
         <f>HYPERLINK("https://careers.synopsys.com/job/-/-/44408/90427979216","https://careers.synopsys.com/job/-/-/44408/90427979216")</f>
       </c>
@@ -3701,9 +3633,7 @@
       <c r="P56">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/keysight-technologies/2026-04-08/69a213f8359fe034b1cd5272/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/keysight-technologies/2026-04-08/69a213f8359fe034b1cd5272/resume.md")</f>
       </c>
-      <c r="Q56">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/keysight-technologies/2026-04-08/69a213f8359fe034b1cd5272/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/keysight-technologies/2026-04-08/69a213f8359fe034b1cd5272/resume.pdf")</f>
-      </c>
+      <c r="Q56"/>
       <c r="R56">
         <f>HYPERLINK("https://jobs.keysight.com/jobs/51804?lang=en-us&amp;iis=LinkedIn&amp;iisn=Linkedin&amp;mode=apply","https://jobs.keysight.com/jobs/51804?lang=en-us&amp;iis=LinkedIn&amp;iisn=Linkedin&amp;mode=apply")</f>
       </c>
@@ -3769,9 +3699,7 @@
       <c r="P57">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intertek/2026-04-08/69c8e5a61818a24cd84d814a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intertek/2026-04-08/69c8e5a61818a24cd84d814a/resume.md")</f>
       </c>
-      <c r="Q57">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intertek/2026-04-08/69c8e5a61818a24cd84d814a/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intertek/2026-04-08/69c8e5a61818a24cd84d814a/resume.pdf")</f>
-      </c>
+      <c r="Q57"/>
       <c r="R57">
         <f>HYPERLINK("https://hcog.fa.em2.oraclecloud.com/hcmUI/CandidateExperience/en/job/14083/?utm_medium=jobshare","https://hcog.fa.em2.oraclecloud.com/hcmUI/CandidateExperience/en/job/14083/?utm_medium=jobshare")</f>
       </c>
@@ -3837,9 +3765,7 @@
       <c r="P58">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-08/690e2f0a221b890c2780b8ea/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-08/690e2f0a221b890c2780b8ea/resume.md")</f>
       </c>
-      <c r="Q58">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-08/690e2f0a221b890c2780b8ea/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-08/690e2f0a221b890c2780b8ea/resume.pdf")</f>
-      </c>
+      <c r="Q58"/>
       <c r="R58">
         <f>HYPERLINK("https://careers.adobe.com/us/en/job/ADOBUSR162315EXTERNALENUS/Software-Development-Engineer-3?utm_source=linkedin&amp;utm_medium=phenom-feeds&amp;source=LinkedIn","https://careers.adobe.com/us/en/job/ADOBUSR162315EXTERNALENUS/Software-Development-Engineer-3?utm_source=linkedin&amp;utm_medium=phenom-feeds&amp;source=LinkedIn")</f>
       </c>
@@ -3905,9 +3831,7 @@
       <c r="P59">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tiktok/2026-04-08/69d61c52cfdc6132f9468a50/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tiktok/2026-04-08/69d61c52cfdc6132f9468a50/resume.md")</f>
       </c>
-      <c r="Q59">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tiktok/2026-04-08/69d61c52cfdc6132f9468a50/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tiktok/2026-04-08/69d61c52cfdc6132f9468a50/resume.pdf")</f>
-      </c>
+      <c r="Q59"/>
       <c r="R59">
         <f>HYPERLINK("https://lifeattiktok.com/search/7553175919393802503?spread=5MWH5CQ","https://lifeattiktok.com/search/7553175919393802503?spread=5MWH5CQ")</f>
       </c>
@@ -4039,9 +3963,7 @@
       <c r="P61">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69d6104ba5c9786095e4919f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69d6104ba5c9786095e4919f/resume.md")</f>
       </c>
-      <c r="Q61">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69d6104ba5c9786095e4919f/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69d6104ba5c9786095e4919f/resume.pdf")</f>
-      </c>
+      <c r="Q61"/>
       <c r="R61">
         <f>HYPERLINK("https://JPMorganChase.contacthr.com/151731457","https://JPMorganChase.contacthr.com/151731457")</f>
       </c>
@@ -4099,9 +4021,7 @@
       <c r="P62">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69d60e05cfdc6132f946857c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69d60e05cfdc6132f946857c/resume.md")</f>
       </c>
-      <c r="Q62">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69d60e05cfdc6132f946857c/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69d60e05cfdc6132f946857c/resume.pdf")</f>
-      </c>
+      <c r="Q62"/>
       <c r="R62">
         <f>HYPERLINK("https://JPMorganChase.contacthr.com/151730357","https://JPMorganChase.contacthr.com/151730357")</f>
       </c>
@@ -4373,9 +4293,7 @@
       <c r="P66">
         <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/thermo-fisher-scientific/2026-04-08/69d5d8a0cfdc6132f946677d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/thermo-fisher-scientific/2026-04-08/69d5d8a0cfdc6132f946677d/resume.md")</f>
       </c>
-      <c r="Q66">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/thermo-fisher-scientific/2026-04-08/69d5d8a0cfdc6132f946677d/resume.pdf","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/thermo-fisher-scientific/2026-04-08/69d5d8a0cfdc6132f946677d/resume.pdf")</f>
-      </c>
+      <c r="Q66"/>
       <c r="R66">
         <f>HYPERLINK("https://jobs.thermofisher.com/global/en/job/R-01345491/Data-Scientist-I?rx_ch=jobpost&amp;rx_id=7d2f6645-32af-11f1-ac04-cfc7f8abaa70&amp;rx_job=R-01345491&amp;rx_medium=post&amp;rx_paid=0&amp;rx_r=none&amp;rx_source=linkedin&amp;rx_ts=20260408T024003Z&amp;rx_vp=linkedindirectindex&amp;utm_medium=post&amp;utm_source=jobright","https://jobs.thermofisher.com/global/en/job/R-01345491/Data-Scientist-I?rx_ch=jobpost&amp;rx_id=7d2f6645-32af-11f1-ac04-cfc7f8abaa70&amp;rx_job=R-01345491&amp;rx_medium=post&amp;rx_paid=0&amp;rx_r=none&amp;rx_source=linkedin&amp;rx_ts=20260408T024003Z&amp;rx_vp=linkedindirectindex&amp;utm_medium=post&amp;utm_source=jobright")</f>
       </c>

--- a/data/deliverables/resume_portfolio/resume_portfolio.xlsx
+++ b/data/deliverables/resume_portfolio/resume_portfolio.xlsx
@@ -1128,8 +1128,14 @@
       </c>
       <c r="L17"/>
       <c r="M17"/>
-      <c r="N17"/>
-      <c r="O17"/>
+      <c r="N17">
+        <v>88.8</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P17"/>
       <c r="Q17"/>
       <c r="R17">
@@ -1474,8 +1480,14 @@
       </c>
       <c r="L22"/>
       <c r="M22"/>
-      <c r="N22"/>
-      <c r="O22"/>
+      <c r="N22">
+        <v>93.0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P22"/>
       <c r="Q22"/>
       <c r="R22">
@@ -2110,8 +2122,14 @@
       <c r="K32"/>
       <c r="L32"/>
       <c r="M32"/>
-      <c r="N32"/>
-      <c r="O32"/>
+      <c r="N32">
+        <v>94.6</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P32"/>
       <c r="Q32"/>
       <c r="R32">
@@ -2374,8 +2392,14 @@
       </c>
       <c r="L36"/>
       <c r="M36"/>
-      <c r="N36"/>
-      <c r="O36"/>
+      <c r="N36">
+        <v>94.2</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P36"/>
       <c r="Q36"/>
       <c r="R36">
@@ -2490,8 +2514,14 @@
       <c r="K38"/>
       <c r="L38"/>
       <c r="M38"/>
-      <c r="N38"/>
-      <c r="O38"/>
+      <c r="N38">
+        <v>93.6</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P38"/>
       <c r="Q38"/>
       <c r="R38">
@@ -2672,8 +2702,14 @@
       <c r="K41"/>
       <c r="L41"/>
       <c r="M41"/>
-      <c r="N41"/>
-      <c r="O41"/>
+      <c r="N41">
+        <v>94.0</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P41"/>
       <c r="Q41"/>
       <c r="R41">
@@ -4480,8 +4516,14 @@
       </c>
       <c r="L69"/>
       <c r="M69"/>
-      <c r="N69"/>
-      <c r="O69"/>
+      <c r="N69">
+        <v>79.0</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P69"/>
       <c r="Q69"/>
       <c r="R69">
@@ -4546,8 +4588,14 @@
       </c>
       <c r="L70"/>
       <c r="M70"/>
-      <c r="N70"/>
-      <c r="O70"/>
+      <c r="N70">
+        <v>65.2</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P70"/>
       <c r="Q70"/>
       <c r="R70">
@@ -4778,8 +4826,14 @@
       <c r="K74"/>
       <c r="L74"/>
       <c r="M74"/>
-      <c r="N74"/>
-      <c r="O74"/>
+      <c r="N74">
+        <v>93.3</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P74"/>
       <c r="Q74"/>
       <c r="R74">
@@ -4952,8 +5006,14 @@
       <c r="K77"/>
       <c r="L77"/>
       <c r="M77"/>
-      <c r="N77"/>
-      <c r="O77"/>
+      <c r="N77">
+        <v>85.9</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P77"/>
       <c r="Q77"/>
       <c r="R77">
@@ -5126,8 +5186,14 @@
       <c r="K80"/>
       <c r="L80"/>
       <c r="M80"/>
-      <c r="N80"/>
-      <c r="O80"/>
+      <c r="N80">
+        <v>94.8</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P80"/>
       <c r="Q80"/>
       <c r="R80">
@@ -7300,8 +7366,14 @@
       </c>
       <c r="L115"/>
       <c r="M115"/>
-      <c r="N115"/>
-      <c r="O115"/>
+      <c r="N115">
+        <v>85.5</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P115"/>
       <c r="Q115"/>
       <c r="R115">
@@ -7366,8 +7438,14 @@
       </c>
       <c r="L116"/>
       <c r="M116"/>
-      <c r="N116"/>
-      <c r="O116"/>
+      <c r="N116">
+        <v>94.0</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P116"/>
       <c r="Q116"/>
       <c r="R116">
@@ -10760,8 +10838,14 @@
       </c>
       <c r="L169"/>
       <c r="M169"/>
-      <c r="N169"/>
-      <c r="O169"/>
+      <c r="N169">
+        <v>93.6</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P169"/>
       <c r="Q169"/>
       <c r="R169">
@@ -10876,8 +10960,14 @@
       <c r="K171"/>
       <c r="L171"/>
       <c r="M171"/>
-      <c r="N171"/>
-      <c r="O171"/>
+      <c r="N171">
+        <v>78.5</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P171"/>
       <c r="Q171"/>
       <c r="R171">
@@ -11280,8 +11370,14 @@
       </c>
       <c r="L177"/>
       <c r="M177"/>
-      <c r="N177"/>
-      <c r="O177"/>
+      <c r="N177">
+        <v>93.8</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P177"/>
       <c r="Q177"/>
       <c r="R177">
@@ -11652,8 +11748,14 @@
       <c r="K183"/>
       <c r="L183"/>
       <c r="M183"/>
-      <c r="N183"/>
-      <c r="O183"/>
+      <c r="N183">
+        <v>80.8</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P183"/>
       <c r="Q183"/>
       <c r="R183">
@@ -11776,8 +11878,14 @@
       <c r="K185"/>
       <c r="L185"/>
       <c r="M185"/>
-      <c r="N185"/>
-      <c r="O185"/>
+      <c r="N185">
+        <v>86.7</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P185"/>
       <c r="Q185"/>
       <c r="R185">
@@ -14220,8 +14328,14 @@
       <c r="K223"/>
       <c r="L223"/>
       <c r="M223"/>
-      <c r="N223"/>
-      <c r="O223"/>
+      <c r="N223">
+        <v>77.5</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P223"/>
       <c r="Q223"/>
       <c r="R223">
@@ -14666,8 +14780,14 @@
       <c r="K230"/>
       <c r="L230"/>
       <c r="M230"/>
-      <c r="N230"/>
-      <c r="O230"/>
+      <c r="N230">
+        <v>82.6</v>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P230"/>
       <c r="Q230"/>
       <c r="R230">
@@ -15772,8 +15892,14 @@
       <c r="K247"/>
       <c r="L247"/>
       <c r="M247"/>
-      <c r="N247"/>
-      <c r="O247"/>
+      <c r="N247">
+        <v>94.6</v>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P247"/>
       <c r="Q247"/>
       <c r="R247">
@@ -16664,8 +16790,14 @@
       <c r="K261"/>
       <c r="L261"/>
       <c r="M261"/>
-      <c r="N261"/>
-      <c r="O261"/>
+      <c r="N261">
+        <v>93.2</v>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P261"/>
       <c r="Q261"/>
       <c r="R261">
@@ -17392,8 +17524,14 @@
       <c r="K273"/>
       <c r="L273"/>
       <c r="M273"/>
-      <c r="N273"/>
-      <c r="O273"/>
+      <c r="N273">
+        <v>93.8</v>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P273"/>
       <c r="Q273"/>
       <c r="R273">
@@ -19160,8 +19298,14 @@
       <c r="K301"/>
       <c r="L301"/>
       <c r="M301"/>
-      <c r="N301"/>
-      <c r="O301"/>
+      <c r="N301">
+        <v>96.2</v>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P301"/>
       <c r="Q301"/>
       <c r="R301">
@@ -19392,8 +19536,14 @@
       <c r="K305"/>
       <c r="L305"/>
       <c r="M305"/>
-      <c r="N305"/>
-      <c r="O305"/>
+      <c r="N305">
+        <v>88.9</v>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P305"/>
       <c r="Q305"/>
       <c r="R305">
@@ -19508,8 +19658,14 @@
       <c r="K307"/>
       <c r="L307"/>
       <c r="M307"/>
-      <c r="N307"/>
-      <c r="O307"/>
+      <c r="N307">
+        <v>94.3</v>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P307"/>
       <c r="Q307"/>
       <c r="R307">
@@ -20160,8 +20316,14 @@
       <c r="K317"/>
       <c r="L317"/>
       <c r="M317"/>
-      <c r="N317"/>
-      <c r="O317"/>
+      <c r="N317">
+        <v>95.0</v>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P317"/>
       <c r="Q317"/>
       <c r="R317">
@@ -22076,8 +22238,14 @@
       <c r="K347"/>
       <c r="L347"/>
       <c r="M347"/>
-      <c r="N347"/>
-      <c r="O347"/>
+      <c r="N347">
+        <v>93.1</v>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P347"/>
       <c r="Q347"/>
       <c r="R347">
@@ -25676,8 +25844,14 @@
       <c r="K403"/>
       <c r="L403"/>
       <c r="M403"/>
-      <c r="N403"/>
-      <c r="O403"/>
+      <c r="N403">
+        <v>74.2</v>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P403"/>
       <c r="Q403"/>
       <c r="R403">
@@ -26064,8 +26238,14 @@
       </c>
       <c r="L409"/>
       <c r="M409"/>
-      <c r="N409"/>
-      <c r="O409"/>
+      <c r="N409">
+        <v>93.9</v>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P409"/>
       <c r="Q409"/>
       <c r="R409">
@@ -26436,8 +26616,14 @@
       <c r="K415"/>
       <c r="L415"/>
       <c r="M415"/>
-      <c r="N415"/>
-      <c r="O415"/>
+      <c r="N415">
+        <v>95.0</v>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P415"/>
       <c r="Q415"/>
       <c r="R415">
@@ -26940,8 +27126,14 @@
       <c r="K423"/>
       <c r="L423"/>
       <c r="M423"/>
-      <c r="N423"/>
-      <c r="O423"/>
+      <c r="N423">
+        <v>92.6</v>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P423"/>
       <c r="Q423"/>
       <c r="R423">
@@ -26998,8 +27190,14 @@
       <c r="K424"/>
       <c r="L424"/>
       <c r="M424"/>
-      <c r="N424"/>
-      <c r="O424"/>
+      <c r="N424">
+        <v>94.1</v>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P424"/>
       <c r="Q424"/>
       <c r="R424">
@@ -29534,8 +29732,14 @@
       <c r="K464"/>
       <c r="L464"/>
       <c r="M464"/>
-      <c r="N464"/>
-      <c r="O464"/>
+      <c r="N464">
+        <v>82.7</v>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P464"/>
       <c r="Q464"/>
       <c r="R464">
@@ -29880,8 +30084,14 @@
       <c r="K469"/>
       <c r="L469"/>
       <c r="M469"/>
-      <c r="N469"/>
-      <c r="O469"/>
+      <c r="N469">
+        <v>95.0</v>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P469"/>
       <c r="Q469"/>
       <c r="R469">
@@ -29938,8 +30148,14 @@
       <c r="K470"/>
       <c r="L470"/>
       <c r="M470"/>
-      <c r="N470"/>
-      <c r="O470"/>
+      <c r="N470">
+        <v>90.7</v>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P470"/>
       <c r="Q470"/>
       <c r="R470">
@@ -29996,8 +30212,14 @@
       <c r="K471"/>
       <c r="L471"/>
       <c r="M471"/>
-      <c r="N471"/>
-      <c r="O471"/>
+      <c r="N471">
+        <v>92.7</v>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P471"/>
       <c r="Q471"/>
       <c r="R471">
@@ -30170,8 +30392,14 @@
       <c r="K474"/>
       <c r="L474"/>
       <c r="M474"/>
-      <c r="N474"/>
-      <c r="O474"/>
+      <c r="N474">
+        <v>94.5</v>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P474"/>
       <c r="Q474"/>
       <c r="R474">
@@ -31086,8 +31314,14 @@
       <c r="K488"/>
       <c r="L488"/>
       <c r="M488"/>
-      <c r="N488"/>
-      <c r="O488"/>
+      <c r="N488">
+        <v>84.8</v>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P488"/>
       <c r="Q488"/>
       <c r="R488">
@@ -34018,8 +34252,14 @@
       <c r="K534"/>
       <c r="L534"/>
       <c r="M534"/>
-      <c r="N534"/>
-      <c r="O534"/>
+      <c r="N534">
+        <v>93.6</v>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P534"/>
       <c r="Q534"/>
       <c r="R534">
@@ -34084,8 +34324,14 @@
       </c>
       <c r="L535"/>
       <c r="M535"/>
-      <c r="N535"/>
-      <c r="O535"/>
+      <c r="N535">
+        <v>83.4</v>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P535"/>
       <c r="Q535"/>
       <c r="R535">
@@ -35520,8 +35766,14 @@
       <c r="K557"/>
       <c r="L557"/>
       <c r="M557"/>
-      <c r="N557"/>
-      <c r="O557"/>
+      <c r="N557">
+        <v>84.8</v>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P557"/>
       <c r="Q557"/>
       <c r="R557">
@@ -35776,8 +36028,14 @@
       <c r="K561"/>
       <c r="L561"/>
       <c r="M561"/>
-      <c r="N561"/>
-      <c r="O561"/>
+      <c r="N561">
+        <v>85.9</v>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P561"/>
       <c r="Q561"/>
       <c r="R561">
@@ -38658,8 +38916,14 @@
       </c>
       <c r="L606"/>
       <c r="M606"/>
-      <c r="N606"/>
-      <c r="O606"/>
+      <c r="N606">
+        <v>94.4</v>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P606"/>
       <c r="Q606"/>
       <c r="R606">
@@ -41886,8 +42150,14 @@
       <c r="K656"/>
       <c r="L656"/>
       <c r="M656"/>
-      <c r="N656"/>
-      <c r="O656"/>
+      <c r="N656">
+        <v>88.4</v>
+      </c>
+      <c r="O656" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P656"/>
       <c r="Q656"/>
       <c r="R656">
@@ -41952,8 +42222,14 @@
       </c>
       <c r="L657"/>
       <c r="M657"/>
-      <c r="N657"/>
-      <c r="O657"/>
+      <c r="N657">
+        <v>89.2</v>
+      </c>
+      <c r="O657" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P657"/>
       <c r="Q657"/>
       <c r="R657">
@@ -42018,8 +42294,14 @@
       </c>
       <c r="L658"/>
       <c r="M658"/>
-      <c r="N658"/>
-      <c r="O658"/>
+      <c r="N658">
+        <v>94.3</v>
+      </c>
+      <c r="O658" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P658"/>
       <c r="Q658"/>
       <c r="R658">
@@ -42150,8 +42432,14 @@
       </c>
       <c r="L660"/>
       <c r="M660"/>
-      <c r="N660"/>
-      <c r="O660"/>
+      <c r="N660">
+        <v>91.3</v>
+      </c>
+      <c r="O660" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P660"/>
       <c r="Q660"/>
       <c r="R660">
@@ -44092,8 +44380,14 @@
       </c>
       <c r="L691"/>
       <c r="M691"/>
-      <c r="N691"/>
-      <c r="O691"/>
+      <c r="N691">
+        <v>81.5</v>
+      </c>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P691"/>
       <c r="Q691"/>
       <c r="R691">
@@ -44224,8 +44518,14 @@
       </c>
       <c r="L693"/>
       <c r="M693"/>
-      <c r="N693"/>
-      <c r="O693"/>
+      <c r="N693">
+        <v>85.8</v>
+      </c>
+      <c r="O693" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P693"/>
       <c r="Q693"/>
       <c r="R693">
@@ -44414,8 +44714,14 @@
       <c r="K696"/>
       <c r="L696"/>
       <c r="M696"/>
-      <c r="N696"/>
-      <c r="O696"/>
+      <c r="N696">
+        <v>94.6</v>
+      </c>
+      <c r="O696" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P696"/>
       <c r="Q696"/>
       <c r="R696">
@@ -44472,8 +44778,14 @@
       <c r="K697"/>
       <c r="L697"/>
       <c r="M697"/>
-      <c r="N697"/>
-      <c r="O697"/>
+      <c r="N697">
+        <v>74.4</v>
+      </c>
+      <c r="O697" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P697"/>
       <c r="Q697"/>
       <c r="R697">
@@ -45364,8 +45676,14 @@
       <c r="K711"/>
       <c r="L711"/>
       <c r="M711"/>
-      <c r="N711"/>
-      <c r="O711"/>
+      <c r="N711">
+        <v>94.1</v>
+      </c>
+      <c r="O711" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P711"/>
       <c r="Q711"/>
       <c r="R711">
@@ -47196,8 +47514,14 @@
       <c r="K739"/>
       <c r="L739"/>
       <c r="M739"/>
-      <c r="N739"/>
-      <c r="O739"/>
+      <c r="N739">
+        <v>80.5</v>
+      </c>
+      <c r="O739" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P739"/>
       <c r="Q739"/>
       <c r="R739">
@@ -48558,8 +48882,14 @@
       </c>
       <c r="L760"/>
       <c r="M760"/>
-      <c r="N760"/>
-      <c r="O760"/>
+      <c r="N760">
+        <v>94.5</v>
+      </c>
+      <c r="O760" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P760"/>
       <c r="Q760"/>
       <c r="R760">
@@ -51266,8 +51596,14 @@
       </c>
       <c r="L802"/>
       <c r="M802"/>
-      <c r="N802"/>
-      <c r="O802"/>
+      <c r="N802">
+        <v>94.3</v>
+      </c>
+      <c r="O802" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P802"/>
       <c r="Q802"/>
       <c r="R802">
@@ -51794,8 +52130,14 @@
       </c>
       <c r="L810"/>
       <c r="M810"/>
-      <c r="N810"/>
-      <c r="O810"/>
+      <c r="N810">
+        <v>87.9</v>
+      </c>
+      <c r="O810" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P810"/>
       <c r="Q810"/>
       <c r="R810">
@@ -55054,8 +55396,14 @@
       <c r="K860"/>
       <c r="L860"/>
       <c r="M860"/>
-      <c r="N860"/>
-      <c r="O860"/>
+      <c r="N860">
+        <v>80.2</v>
+      </c>
+      <c r="O860" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P860"/>
       <c r="Q860"/>
       <c r="R860">
@@ -55302,8 +55650,14 @@
       <c r="K864"/>
       <c r="L864"/>
       <c r="M864"/>
-      <c r="N864"/>
-      <c r="O864"/>
+      <c r="N864">
+        <v>83.5</v>
+      </c>
+      <c r="O864" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P864"/>
       <c r="Q864"/>
       <c r="R864">
@@ -57004,8 +57358,14 @@
       <c r="K891"/>
       <c r="L891"/>
       <c r="M891"/>
-      <c r="N891"/>
-      <c r="O891"/>
+      <c r="N891">
+        <v>87.7</v>
+      </c>
+      <c r="O891" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P891"/>
       <c r="Q891"/>
       <c r="R891">
@@ -58342,8 +58702,14 @@
       </c>
       <c r="L912"/>
       <c r="M912"/>
-      <c r="N912"/>
-      <c r="O912"/>
+      <c r="N912">
+        <v>78.9</v>
+      </c>
+      <c r="O912" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P912"/>
       <c r="Q912"/>
       <c r="R912">
@@ -60432,8 +60798,14 @@
       <c r="K945"/>
       <c r="L945"/>
       <c r="M945"/>
-      <c r="N945"/>
-      <c r="O945"/>
+      <c r="N945">
+        <v>80.0</v>
+      </c>
+      <c r="O945" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="P945"/>
       <c r="Q945"/>
       <c r="R945">
@@ -63808,8 +64180,14 @@
       <c r="K997"/>
       <c r="L997"/>
       <c r="M997"/>
-      <c r="N997"/>
-      <c r="O997"/>
+      <c r="N997">
+        <v>93.6</v>
+      </c>
+      <c r="O997" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P997"/>
       <c r="Q997"/>
       <c r="R997">
@@ -66962,8 +67340,14 @@
       <c r="K1046"/>
       <c r="L1046"/>
       <c r="M1046"/>
-      <c r="N1046"/>
-      <c r="O1046"/>
+      <c r="N1046">
+        <v>95.2</v>
+      </c>
+      <c r="O1046" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
       <c r="P1046"/>
       <c r="Q1046"/>
       <c r="R1046">

--- a/data/deliverables/resume_portfolio/resume_portfolio.xlsx
+++ b/data/deliverables/resume_portfolio/resume_portfolio.xlsx
@@ -195,7 +195,7 @@
         </is>
       </c>
       <c r="P2">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nokia/2026-04-08/69b622b956973837413b6091/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nokia/2026-04-08/69b622b956973837413b6091/resume.md")</f>
+        <f>HYPERLINK("by_company/nokia/2026-04-08/69b622b956973837413b6091/resume.md","data/deliverables/resume_portfolio/by_company/nokia/2026-04-08/69b622b956973837413b6091/resume.md")</f>
       </c>
       <c r="Q2"/>
       <c r="R2">
@@ -253,7 +253,7 @@
         </is>
       </c>
       <c r="P3">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/general-motors/2026-04-08/69ac98f42747003c3d523072/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/general-motors/2026-04-08/69ac98f42747003c3d523072/resume.md")</f>
+        <f>HYPERLINK("by_company/general-motors/2026-04-08/69ac98f42747003c3d523072/resume.md","data/deliverables/resume_portfolio/by_company/general-motors/2026-04-08/69ac98f42747003c3d523072/resume.md")</f>
       </c>
       <c r="Q3"/>
       <c r="R3">
@@ -369,7 +369,7 @@
         </is>
       </c>
       <c r="P5">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d650cfe63cea7a8b6685f9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d650cfe63cea7a8b6685f9/resume.md")</f>
+        <f>HYPERLINK("by_company/microsoft/2026-04-08/69d650cfe63cea7a8b6685f9/resume.md","data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d650cfe63cea7a8b6685f9/resume.md")</f>
       </c>
       <c r="Q5"/>
       <c r="R5">
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="P6">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/bytedance/2026-04-08/69d650b9e63cea7a8b6685db/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/bytedance/2026-04-08/69d650b9e63cea7a8b6685db/resume.md")</f>
+        <f>HYPERLINK("by_company/bytedance/2026-04-08/69d650b9e63cea7a8b6685db/resume.md","data/deliverables/resume_portfolio/by_company/bytedance/2026-04-08/69d650b9e63cea7a8b6685db/resume.md")</f>
       </c>
       <c r="Q6"/>
       <c r="R6">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="P7">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-08/699d6a6d81476f6176b63dce/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-08/699d6a6d81476f6176b63dce/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon/2026-04-08/699d6a6d81476f6176b63dce/resume.md","data/deliverables/resume_portfolio/by_company/amazon/2026-04-08/699d6a6d81476f6176b63dce/resume.md")</f>
       </c>
       <c r="Q7"/>
       <c r="R7">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="P8">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d6501bcfdc6132f9469623/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d6501bcfdc6132f9469623/resume.md")</f>
+        <f>HYPERLINK("by_company/microsoft/2026-04-08/69d6501bcfdc6132f9469623/resume.md","data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d6501bcfdc6132f9469623/resume.md")</f>
       </c>
       <c r="Q8"/>
       <c r="R8">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="P9">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d65016cfdc6132f946961a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d65016cfdc6132f946961a/resume.md")</f>
+        <f>HYPERLINK("by_company/microsoft/2026-04-08/69d65016cfdc6132f946961a/resume.md","data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d65016cfdc6132f946961a/resume.md")</f>
       </c>
       <c r="Q9"/>
       <c r="R9">
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="P15">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba9dd95697383741406e1b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba9dd95697383741406e1b/resume.md")</f>
+        <f>HYPERLINK("by_company/google/2026-04-08/69ba9dd95697383741406e1b/resume.md","data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba9dd95697383741406e1b/resume.md")</f>
       </c>
       <c r="Q15"/>
       <c r="R15">
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="P16">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d64f92706f771673baa293/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d64f92706f771673baa293/resume.md")</f>
+        <f>HYPERLINK("by_company/microsoft/2026-04-08/69d64f92706f771673baa293/resume.md","data/deliverables/resume_portfolio/by_company/microsoft/2026-04-08/69d64f92706f771673baa293/resume.md")</f>
       </c>
       <c r="Q16"/>
       <c r="R16">
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="P18">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba92be06c1ba00c54cb3d5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba92be06c1ba00c54cb3d5/resume.md")</f>
+        <f>HYPERLINK("by_company/google/2026-04-08/69ba92be06c1ba00c54cb3d5/resume.md","data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba92be06c1ba00c54cb3d5/resume.md")</f>
       </c>
       <c r="Q18"/>
       <c r="R18">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P19">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-08/69d64ba948f0c8161d2f7366/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-08/69d64ba948f0c8161d2f7366/resume.md")</f>
+        <f>HYPERLINK("by_company/ss-c-technologies/2026-04-08/69d64ba948f0c8161d2f7366/resume.md","data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-08/69d64ba948f0c8161d2f7366/resume.md")</f>
       </c>
       <c r="Q19"/>
       <c r="R19">
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="P20">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba8bc25697383741402b0f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba8bc25697383741402b0f/resume.md")</f>
+        <f>HYPERLINK("by_company/google/2026-04-08/69ba8bc25697383741402b0f/resume.md","data/deliverables/resume_portfolio/by_company/google/2026-04-08/69ba8bc25697383741402b0f/resume.md")</f>
       </c>
       <c r="Q20"/>
       <c r="R20">
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="P21">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/garmin/2026-04-08/699dccab81476f6176b6af20/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/garmin/2026-04-08/699dccab81476f6176b6af20/resume.md")</f>
+        <f>HYPERLINK("by_company/garmin/2026-04-08/699dccab81476f6176b6af20/resume.md","data/deliverables/resume_portfolio/by_company/garmin/2026-04-08/699dccab81476f6176b6af20/resume.md")</f>
       </c>
       <c r="Q21"/>
       <c r="R21">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="P23">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/bytedance/2026-04-08/69d64881706f771673baa044/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/bytedance/2026-04-08/69d64881706f771673baa044/resume.md")</f>
+        <f>HYPERLINK("by_company/bytedance/2026-04-08/69d64881706f771673baa044/resume.md","data/deliverables/resume_portfolio/by_company/bytedance/2026-04-08/69d64881706f771673baa044/resume.md")</f>
       </c>
       <c r="Q23"/>
       <c r="R23">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="P24">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/netjets/2026-04-08/69ba8d643b74eb1e2c887f2b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/netjets/2026-04-08/69ba8d643b74eb1e2c887f2b/resume.md")</f>
+        <f>HYPERLINK("by_company/netjets/2026-04-08/69ba8d643b74eb1e2c887f2b/resume.md","data/deliverables/resume_portfolio/by_company/netjets/2026-04-08/69ba8d643b74eb1e2c887f2b/resume.md")</f>
       </c>
       <c r="Q24"/>
       <c r="R24">
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="P25">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-08/69d6128ae63cea7a8b66768d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-08/69d6128ae63cea7a8b66768d/resume.md")</f>
+        <f>HYPERLINK("by_company/ss-c-technologies/2026-04-08/69d6128ae63cea7a8b66768d/resume.md","data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-08/69d6128ae63cea7a8b66768d/resume.md")</f>
       </c>
       <c r="Q25"/>
       <c r="R25">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="P26">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualcomm/2026-04-08/69a504290da45516f16da9ce/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualcomm/2026-04-08/69a504290da45516f16da9ce/resume.md")</f>
+        <f>HYPERLINK("by_company/qualcomm/2026-04-08/69a504290da45516f16da9ce/resume.md","data/deliverables/resume_portfolio/by_company/qualcomm/2026-04-08/69a504290da45516f16da9ce/resume.md")</f>
       </c>
       <c r="Q26"/>
       <c r="R26">
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="P27">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/699c43cb81476f6176b4bd94/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-08/699c43cb81476f6176b4bd94/resume.md")</f>
+        <f>HYPERLINK("by_company/google/2026-04-08/699c43cb81476f6176b4bd94/resume.md","data/deliverables/resume_portfolio/by_company/google/2026-04-08/699c43cb81476f6176b4bd94/resume.md")</f>
       </c>
       <c r="Q27"/>
       <c r="R27">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="P28">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/the-walt-disney-company/2026-04-08/69b2b061ae2a534885e9dc50/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/the-walt-disney-company/2026-04-08/69b2b061ae2a534885e9dc50/resume.md")</f>
+        <f>HYPERLINK("by_company/the-walt-disney-company/2026-04-08/69b2b061ae2a534885e9dc50/resume.md","data/deliverables/resume_portfolio/by_company/the-walt-disney-company/2026-04-08/69b2b061ae2a534885e9dc50/resume.md")</f>
       </c>
       <c r="Q28"/>
       <c r="R28">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="P29">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kla/2026-04-08/69d58da3366bb95ba5546066/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kla/2026-04-08/69d58da3366bb95ba5546066/resume.md")</f>
+        <f>HYPERLINK("by_company/kla/2026-04-08/69d58da3366bb95ba5546066/resume.md","data/deliverables/resume_portfolio/by_company/kla/2026-04-08/69d58da3366bb95ba5546066/resume.md")</f>
       </c>
       <c r="Q29"/>
       <c r="R29">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="P30">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kla/2026-04-08/6969fa36639b452fb57ff3d1/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kla/2026-04-08/6969fa36639b452fb57ff3d1/resume.md")</f>
+        <f>HYPERLINK("by_company/kla/2026-04-08/6969fa36639b452fb57ff3d1/resume.md","data/deliverables/resume_portfolio/by_company/kla/2026-04-08/6969fa36639b452fb57ff3d1/resume.md")</f>
       </c>
       <c r="Q30"/>
       <c r="R30">
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="P31">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d6468852a5bf58001280a7/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d6468852a5bf58001280a7/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon-web-services-aws/2026-04-08/69d6468852a5bf58001280a7/resume.md","data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d6468852a5bf58001280a7/resume.md")</f>
       </c>
       <c r="Q31"/>
       <c r="R31">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="P33">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-08/69d642dc366bb95ba554bf11/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-08/69d642dc366bb95ba554bf11/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon/2026-04-08/69d642dc366bb95ba554bf11/resume.md","data/deliverables/resume_portfolio/by_company/amazon/2026-04-08/69d642dc366bb95ba554bf11/resume.md")</f>
       </c>
       <c r="Q33"/>
       <c r="R33">
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="P34">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640ea706f771673ba9fb7/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640ea706f771673ba9fb7/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon-web-services-aws/2026-04-08/69d640ea706f771673ba9fb7/resume.md","data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640ea706f771673ba9fb7/resume.md")</f>
       </c>
       <c r="Q34"/>
       <c r="R34">
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="P35">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640de52a5bf5800128045/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640de52a5bf5800128045/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon-web-services-aws/2026-04-08/69d640de52a5bf5800128045/resume.md","data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640de52a5bf5800128045/resume.md")</f>
       </c>
       <c r="Q35"/>
       <c r="R35">
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="P37">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640cde63cea7a8b6682f4/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640cde63cea7a8b6682f4/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon-web-services-aws/2026-04-08/69d640cde63cea7a8b6682f4/resume.md","data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-08/69d640cde63cea7a8b6682f4/resume.md")</f>
       </c>
       <c r="Q37"/>
       <c r="R37">
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="P39">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sony-interactive-entertainment/2026-04-08/698130ba49964d25b5e4135f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sony-interactive-entertainment/2026-04-08/698130ba49964d25b5e4135f/resume.md")</f>
+        <f>HYPERLINK("by_company/sony-interactive-entertainment/2026-04-08/698130ba49964d25b5e4135f/resume.md","data/deliverables/resume_portfolio/by_company/sony-interactive-entertainment/2026-04-08/698130ba49964d25b5e4135f/resume.md")</f>
       </c>
       <c r="Q39"/>
       <c r="R39">
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="P43">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intel/2026-04-08/69d63f4dcfdc6132f9469275/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intel/2026-04-08/69d63f4dcfdc6132f9469275/resume.md")</f>
+        <f>HYPERLINK("by_company/intel/2026-04-08/69d63f4dcfdc6132f9469275/resume.md","data/deliverables/resume_portfolio/by_company/intel/2026-04-08/69d63f4dcfdc6132f9469275/resume.md")</f>
       </c>
       <c r="Q43"/>
       <c r="R43">
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="P46">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/travelers/2026-04-08/69cc5d28366bb95ba54ef2a0/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/travelers/2026-04-08/69cc5d28366bb95ba54ef2a0/resume.md")</f>
+        <f>HYPERLINK("by_company/travelers/2026-04-08/69cc5d28366bb95ba54ef2a0/resume.md","data/deliverables/resume_portfolio/by_company/travelers/2026-04-08/69cc5d28366bb95ba54ef2a0/resume.md")</f>
       </c>
       <c r="Q46"/>
       <c r="R46">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="P48">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/snowflake/2026-04-08/699e4a4e81476f6176b73aab/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/snowflake/2026-04-08/699e4a4e81476f6176b73aab/resume.md")</f>
+        <f>HYPERLINK("by_company/snowflake/2026-04-08/699e4a4e81476f6176b73aab/resume.md","data/deliverables/resume_portfolio/by_company/snowflake/2026-04-08/699e4a4e81476f6176b73aab/resume.md")</f>
       </c>
       <c r="Q48"/>
       <c r="R48">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="P49">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hp/2026-04-08/69d6319c706f771673ba9d05/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hp/2026-04-08/69d6319c706f771673ba9d05/resume.md")</f>
+        <f>HYPERLINK("by_company/hp/2026-04-08/69d6319c706f771673ba9d05/resume.md","data/deliverables/resume_portfolio/by_company/hp/2026-04-08/69d6319c706f771673ba9d05/resume.md")</f>
       </c>
       <c r="Q49"/>
       <c r="R49">
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="P50">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-08/699e270c81476f6176b707f8/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-08/699e270c81476f6176b707f8/resume.md")</f>
+        <f>HYPERLINK("by_company/paypal/2026-04-08/699e270c81476f6176b707f8/resume.md","data/deliverables/resume_portfolio/by_company/paypal/2026-04-08/699e270c81476f6176b707f8/resume.md")</f>
       </c>
       <c r="Q50"/>
       <c r="R50">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="P51">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-08/699e256cce78e77b4fe33807/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-08/699e256cce78e77b4fe33807/resume.md")</f>
+        <f>HYPERLINK("by_company/paypal/2026-04-08/699e256cce78e77b4fe33807/resume.md","data/deliverables/resume_portfolio/by_company/paypal/2026-04-08/699e256cce78e77b4fe33807/resume.md")</f>
       </c>
       <c r="Q51"/>
       <c r="R51">
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="P52">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hdr/2026-04-08/69a2c0750da45516f16c299c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hdr/2026-04-08/69a2c0750da45516f16c299c/resume.md")</f>
+        <f>HYPERLINK("by_company/hdr/2026-04-08/69a2c0750da45516f16c299c/resume.md","data/deliverables/resume_portfolio/by_company/hdr/2026-04-08/69a2c0750da45516f16c299c/resume.md")</f>
       </c>
       <c r="Q52"/>
       <c r="R52">
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="P53">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69cc9f35cfdc6132f94112d9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69cc9f35cfdc6132f94112d9/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-08/69cc9f35cfdc6132f94112d9/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69cc9f35cfdc6132f94112d9/resume.md")</f>
       </c>
       <c r="Q53"/>
       <c r="R53">
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="P55">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/synopsys-inc/2026-04-08/69bb8c0706c1ba00c54e14e4/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/synopsys-inc/2026-04-08/69bb8c0706c1ba00c54e14e4/resume.md")</f>
+        <f>HYPERLINK("by_company/synopsys-inc/2026-04-08/69bb8c0706c1ba00c54e14e4/resume.md","data/deliverables/resume_portfolio/by_company/synopsys-inc/2026-04-08/69bb8c0706c1ba00c54e14e4/resume.md")</f>
       </c>
       <c r="Q55"/>
       <c r="R55">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="P56">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/keysight-technologies/2026-04-08/69a213f8359fe034b1cd5272/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/keysight-technologies/2026-04-08/69a213f8359fe034b1cd5272/resume.md")</f>
+        <f>HYPERLINK("by_company/keysight-technologies/2026-04-08/69a213f8359fe034b1cd5272/resume.md","data/deliverables/resume_portfolio/by_company/keysight-technologies/2026-04-08/69a213f8359fe034b1cd5272/resume.md")</f>
       </c>
       <c r="Q56"/>
       <c r="R56">
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="P57">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intertek/2026-04-08/69c8e5a61818a24cd84d814a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intertek/2026-04-08/69c8e5a61818a24cd84d814a/resume.md")</f>
+        <f>HYPERLINK("by_company/intertek/2026-04-08/69c8e5a61818a24cd84d814a/resume.md","data/deliverables/resume_portfolio/by_company/intertek/2026-04-08/69c8e5a61818a24cd84d814a/resume.md")</f>
       </c>
       <c r="Q57"/>
       <c r="R57">
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="P58">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-08/690e2f0a221b890c2780b8ea/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-08/690e2f0a221b890c2780b8ea/resume.md")</f>
+        <f>HYPERLINK("by_company/adobe/2026-04-08/690e2f0a221b890c2780b8ea/resume.md","data/deliverables/resume_portfolio/by_company/adobe/2026-04-08/690e2f0a221b890c2780b8ea/resume.md")</f>
       </c>
       <c r="Q58"/>
       <c r="R58">
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="P59">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tiktok/2026-04-08/69d61c52cfdc6132f9468a50/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tiktok/2026-04-08/69d61c52cfdc6132f9468a50/resume.md")</f>
+        <f>HYPERLINK("by_company/tiktok/2026-04-08/69d61c52cfdc6132f9468a50/resume.md","data/deliverables/resume_portfolio/by_company/tiktok/2026-04-08/69d61c52cfdc6132f9468a50/resume.md")</f>
       </c>
       <c r="Q59"/>
       <c r="R59">
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="P61">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69d6104ba5c9786095e4919f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69d6104ba5c9786095e4919f/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-08/69d6104ba5c9786095e4919f/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69d6104ba5c9786095e4919f/resume.md")</f>
       </c>
       <c r="Q61"/>
       <c r="R61">
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="P62">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69d60e05cfdc6132f946857c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69d60e05cfdc6132f946857c/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-08/69d60e05cfdc6132f946857c/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-08/69d60e05cfdc6132f946857c/resume.md")</f>
       </c>
       <c r="Q62"/>
       <c r="R62">
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="P64">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/bytedance/2026-04-08/69d60b53366bb95ba554b07d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/bytedance/2026-04-08/69d60b53366bb95ba554b07d/resume.md")</f>
+        <f>HYPERLINK("by_company/bytedance/2026-04-08/69d60b53366bb95ba554b07d/resume.md","data/deliverables/resume_portfolio/by_company/bytedance/2026-04-08/69d60b53366bb95ba554b07d/resume.md")</f>
       </c>
       <c r="Q64"/>
       <c r="R64">
@@ -4261,7 +4261,7 @@
         </is>
       </c>
       <c r="P65">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/bytedance/2026-04-08/69d603734a12eb12c5e15a9f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/bytedance/2026-04-08/69d603734a12eb12c5e15a9f/resume.md")</f>
+        <f>HYPERLINK("by_company/bytedance/2026-04-08/69d603734a12eb12c5e15a9f/resume.md","data/deliverables/resume_portfolio/by_company/bytedance/2026-04-08/69d603734a12eb12c5e15a9f/resume.md")</f>
       </c>
       <c r="Q65"/>
       <c r="R65">
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="P66">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/thermo-fisher-scientific/2026-04-08/69d5d8a0cfdc6132f946677d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/thermo-fisher-scientific/2026-04-08/69d5d8a0cfdc6132f946677d/resume.md")</f>
+        <f>HYPERLINK("by_company/thermo-fisher-scientific/2026-04-08/69d5d8a0cfdc6132f946677d/resume.md","data/deliverables/resume_portfolio/by_company/thermo-fisher-scientific/2026-04-08/69d5d8a0cfdc6132f946677d/resume.md")</f>
       </c>
       <c r="Q66"/>
       <c r="R66">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="P67">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/capital-one/2026-04-07/69d50a7b891d7b11cfcff19a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/capital-one/2026-04-07/69d50a7b891d7b11cfcff19a/resume.md")</f>
+        <f>HYPERLINK("by_company/capital-one/2026-04-07/69d50a7b891d7b11cfcff19a/resume.md","data/deliverables/resume_portfolio/by_company/capital-one/2026-04-07/69d50a7b891d7b11cfcff19a/resume.md")</f>
       </c>
       <c r="Q67"/>
       <c r="R67">
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="P82">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hertz/2026-04-06/69d40ba0e63cea7a8b65621c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hertz/2026-04-06/69d40ba0e63cea7a8b65621c/resume.md")</f>
+        <f>HYPERLINK("by_company/hertz/2026-04-06/69d40ba0e63cea7a8b65621c/resume.md","data/deliverables/resume_portfolio/by_company/hertz/2026-04-06/69d40ba0e63cea7a8b65621c/resume.md")</f>
       </c>
       <c r="Q82"/>
       <c r="R82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="P84">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/shelter-insurance-companies/2026-04-06/69d40a7fe63cea7a8b65619c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/shelter-insurance-companies/2026-04-06/69d40a7fe63cea7a8b65619c/resume.md")</f>
+        <f>HYPERLINK("by_company/shelter-insurance-companies/2026-04-06/69d40a7fe63cea7a8b65619c/resume.md","data/deliverables/resume_portfolio/by_company/shelter-insurance-companies/2026-04-06/69d40a7fe63cea7a8b65619c/resume.md")</f>
       </c>
       <c r="Q84"/>
       <c r="R84">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="P92">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/systems-integration-development-inc/2026-04-06/69d408c5891d7b11cfcf6bc6/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/systems-integration-development-inc/2026-04-06/69d408c5891d7b11cfcf6bc6/resume.md")</f>
+        <f>HYPERLINK("by_company/systems-integration-development-inc/2026-04-06/69d408c5891d7b11cfcf6bc6/resume.md","data/deliverables/resume_portfolio/by_company/systems-integration-development-inc/2026-04-06/69d408c5891d7b11cfcf6bc6/resume.md")</f>
       </c>
       <c r="Q92"/>
       <c r="R92">
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="P94">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ra-capital-management/2026-04-06/69d406b1891d7b11cfcf69fe/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ra-capital-management/2026-04-06/69d406b1891d7b11cfcf69fe/resume.md")</f>
+        <f>HYPERLINK("by_company/ra-capital-management/2026-04-06/69d406b1891d7b11cfcf69fe/resume.md","data/deliverables/resume_portfolio/by_company/ra-capital-management/2026-04-06/69d406b1891d7b11cfcf69fe/resume.md")</f>
       </c>
       <c r="Q94"/>
       <c r="R94">
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="P95">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/university-of-minnesota/2026-04-06/69d403db891d7b11cfcf693f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/university-of-minnesota/2026-04-06/69d403db891d7b11cfcf693f/resume.md")</f>
+        <f>HYPERLINK("by_company/university-of-minnesota/2026-04-06/69d403db891d7b11cfcf693f/resume.md","data/deliverables/resume_portfolio/by_company/university-of-minnesota/2026-04-06/69d403db891d7b11cfcf693f/resume.md")</f>
       </c>
       <c r="Q95"/>
       <c r="R95">
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="P99">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/integrity/2026-04-06/69d40138e63cea7a8b655990/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/integrity/2026-04-06/69d40138e63cea7a8b655990/resume.md")</f>
+        <f>HYPERLINK("by_company/integrity/2026-04-06/69d40138e63cea7a8b655990/resume.md","data/deliverables/resume_portfolio/by_company/integrity/2026-04-06/69d40138e63cea7a8b655990/resume.md")</f>
       </c>
       <c r="Q99"/>
       <c r="R99">
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="P103">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-06/69d400b9e63cea7a8b6556ce/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-06/69d400b9e63cea7a8b6556ce/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-06/69d400b9e63cea7a8b6556ce/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-06/69d400b9e63cea7a8b6556ce/resume.md")</f>
       </c>
       <c r="Q103"/>
       <c r="R103">
@@ -6855,7 +6855,7 @@
         </is>
       </c>
       <c r="P107">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amh/2026-04-06/69d4003a366bb95ba55394a8/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amh/2026-04-06/69d4003a366bb95ba55394a8/resume.md")</f>
+        <f>HYPERLINK("by_company/amh/2026-04-06/69d4003a366bb95ba55394a8/resume.md","data/deliverables/resume_portfolio/by_company/amh/2026-04-06/69d4003a366bb95ba55394a8/resume.md")</f>
       </c>
       <c r="Q107"/>
       <c r="R107">
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="P109">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/klaviyo/2026-04-06/69d3fceae63cea7a8b655631/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/klaviyo/2026-04-06/69d3fceae63cea7a8b655631/resume.md")</f>
+        <f>HYPERLINK("by_company/klaviyo/2026-04-06/69d3fceae63cea7a8b655631/resume.md","data/deliverables/resume_portfolio/by_company/klaviyo/2026-04-06/69d3fceae63cea7a8b655631/resume.md")</f>
       </c>
       <c r="Q109"/>
       <c r="R109">
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="P110">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/doordash/2026-04-06/69d3fcc0891d7b11cfcf61af/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/doordash/2026-04-06/69d3fcc0891d7b11cfcf61af/resume.md")</f>
+        <f>HYPERLINK("by_company/doordash/2026-04-06/69d3fcc0891d7b11cfcf61af/resume.md","data/deliverables/resume_portfolio/by_company/doordash/2026-04-06/69d3fcc0891d7b11cfcf61af/resume.md")</f>
       </c>
       <c r="Q110"/>
       <c r="R110">
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="P111">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hummingbird/2026-04-06/69d3fcbd54f00230c6d2ce9e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hummingbird/2026-04-06/69d3fcbd54f00230c6d2ce9e/resume.md")</f>
+        <f>HYPERLINK("by_company/hummingbird/2026-04-06/69d3fcbd54f00230c6d2ce9e/resume.md","data/deliverables/resume_portfolio/by_company/hummingbird/2026-04-06/69d3fcbd54f00230c6d2ce9e/resume.md")</f>
       </c>
       <c r="Q111"/>
       <c r="R111">
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="P113">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/palantir-technologies/2026-04-06/69c52d5284510008f480048c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/palantir-technologies/2026-04-06/69c52d5284510008f480048c/resume.md")</f>
+        <f>HYPERLINK("by_company/palantir-technologies/2026-04-06/69c52d5284510008f480048c/resume.md","data/deliverables/resume_portfolio/by_company/palantir-technologies/2026-04-06/69c52d5284510008f480048c/resume.md")</f>
       </c>
       <c r="Q113"/>
       <c r="R113">
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="P117">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fis/2026-04-06/69d3f35f891d7b11cfcf5c8d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fis/2026-04-06/69d3f35f891d7b11cfcf5c8d/resume.md")</f>
+        <f>HYPERLINK("by_company/fis/2026-04-06/69d3f35f891d7b11cfcf5c8d/resume.md","data/deliverables/resume_portfolio/by_company/fis/2026-04-06/69d3f35f891d7b11cfcf5c8d/resume.md")</f>
       </c>
       <c r="Q117"/>
       <c r="R117">
@@ -7701,7 +7701,7 @@
         </is>
       </c>
       <c r="P120">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nationwide/2026-04-06/69d3f32de63cea7a8b6550eb/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nationwide/2026-04-06/69d3f32de63cea7a8b6550eb/resume.md")</f>
+        <f>HYPERLINK("by_company/nationwide/2026-04-06/69d3f32de63cea7a8b6550eb/resume.md","data/deliverables/resume_portfolio/by_company/nationwide/2026-04-06/69d3f32de63cea7a8b6550eb/resume.md")</f>
       </c>
       <c r="Q120"/>
       <c r="R120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="P121">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/comcast/2026-04-06/69d3f32c366bb95ba5538f3e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/comcast/2026-04-06/69d3f32c366bb95ba5538f3e/resume.md")</f>
+        <f>HYPERLINK("by_company/comcast/2026-04-06/69d3f32c366bb95ba5538f3e/resume.md","data/deliverables/resume_portfolio/by_company/comcast/2026-04-06/69d3f32c366bb95ba5538f3e/resume.md")</f>
       </c>
       <c r="Q121"/>
       <c r="R121">
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="P122">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cvs-health/2026-04-06/69d3f322e63cea7a8b6550d5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cvs-health/2026-04-06/69d3f322e63cea7a8b6550d5/resume.md")</f>
+        <f>HYPERLINK("by_company/cvs-health/2026-04-06/69d3f322e63cea7a8b6550d5/resume.md","data/deliverables/resume_portfolio/by_company/cvs-health/2026-04-06/69d3f322e63cea7a8b6550d5/resume.md")</f>
       </c>
       <c r="Q122"/>
       <c r="R122">
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="P128">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/red-hat/2026-04-06/69d3eb5be63cea7a8b654ccb/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/red-hat/2026-04-06/69d3eb5be63cea7a8b654ccb/resume.md")</f>
+        <f>HYPERLINK("by_company/red-hat/2026-04-06/69d3eb5be63cea7a8b654ccb/resume.md","data/deliverables/resume_portfolio/by_company/red-hat/2026-04-06/69d3eb5be63cea7a8b654ccb/resume.md")</f>
       </c>
       <c r="Q128"/>
       <c r="R128">
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="P129">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/capital-one/2026-04-06/69d3eb5be63cea7a8b654ccd/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/capital-one/2026-04-06/69d3eb5be63cea7a8b654ccd/resume.md")</f>
+        <f>HYPERLINK("by_company/capital-one/2026-04-06/69d3eb5be63cea7a8b654ccd/resume.md","data/deliverables/resume_portfolio/by_company/capital-one/2026-04-06/69d3eb5be63cea7a8b654ccd/resume.md")</f>
       </c>
       <c r="Q129"/>
       <c r="R129">
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="P130">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/oracle/2026-04-06/69d3e85dcfdc6132f9455b38/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/oracle/2026-04-06/69d3e85dcfdc6132f9455b38/resume.md")</f>
+        <f>HYPERLINK("by_company/oracle/2026-04-06/69d3e85dcfdc6132f9455b38/resume.md","data/deliverables/resume_portfolio/by_company/oracle/2026-04-06/69d3e85dcfdc6132f9455b38/resume.md")</f>
       </c>
       <c r="Q130"/>
       <c r="R130">
@@ -8411,7 +8411,7 @@
         </is>
       </c>
       <c r="P131">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hewlett-packard-enterprise/2026-04-06/69d3e841cdb525785fbc4666/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hewlett-packard-enterprise/2026-04-06/69d3e841cdb525785fbc4666/resume.md")</f>
+        <f>HYPERLINK("by_company/hewlett-packard-enterprise/2026-04-06/69d3e841cdb525785fbc4666/resume.md","data/deliverables/resume_portfolio/by_company/hewlett-packard-enterprise/2026-04-06/69d3e841cdb525785fbc4666/resume.md")</f>
       </c>
       <c r="Q131"/>
       <c r="R131">
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="P132">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/astor-sanders/2026-04-06/69d3e83f891d7b11cfcf5777/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/astor-sanders/2026-04-06/69d3e83f891d7b11cfcf5777/resume.md")</f>
+        <f>HYPERLINK("by_company/astor-sanders/2026-04-06/69d3e83f891d7b11cfcf5777/resume.md","data/deliverables/resume_portfolio/by_company/astor-sanders/2026-04-06/69d3e83f891d7b11cfcf5777/resume.md")</f>
       </c>
       <c r="Q132"/>
       <c r="R132">
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="P133">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cvs-health/2026-04-06/69d3e5a1891d7b11cfcf5574/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cvs-health/2026-04-06/69d3e5a1891d7b11cfcf5574/resume.md")</f>
+        <f>HYPERLINK("by_company/cvs-health/2026-04-06/69d3e5a1891d7b11cfcf5574/resume.md","data/deliverables/resume_portfolio/by_company/cvs-health/2026-04-06/69d3e5a1891d7b11cfcf5574/resume.md")</f>
       </c>
       <c r="Q133"/>
       <c r="R133">
@@ -8733,7 +8733,7 @@
         </is>
       </c>
       <c r="P136">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hiddenlayer/2026-04-06/69d3e057366bb95ba5538162/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hiddenlayer/2026-04-06/69d3e057366bb95ba5538162/resume.md")</f>
+        <f>HYPERLINK("by_company/hiddenlayer/2026-04-06/69d3e057366bb95ba5538162/resume.md","data/deliverables/resume_portfolio/by_company/hiddenlayer/2026-04-06/69d3e057366bb95ba5538162/resume.md")</f>
       </c>
       <c r="Q136"/>
       <c r="R136">
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="P137">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hiddenlayer/2026-04-06/69d3e04a366bb95ba553814e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hiddenlayer/2026-04-06/69d3e04a366bb95ba553814e/resume.md")</f>
+        <f>HYPERLINK("by_company/hiddenlayer/2026-04-06/69d3e04a366bb95ba553814e/resume.md","data/deliverables/resume_portfolio/by_company/hiddenlayer/2026-04-06/69d3e04a366bb95ba553814e/resume.md")</f>
       </c>
       <c r="Q137"/>
       <c r="R137">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="P138">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/deepgram/2026-04-06/69d3e03ecdb525785fbc3d05/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/deepgram/2026-04-06/69d3e03ecdb525785fbc3d05/resume.md")</f>
+        <f>HYPERLINK("by_company/deepgram/2026-04-06/69d3e03ecdb525785fbc3d05/resume.md","data/deliverables/resume_portfolio/by_company/deepgram/2026-04-06/69d3e03ecdb525785fbc3d05/resume.md")</f>
       </c>
       <c r="Q138"/>
       <c r="R138">
@@ -8989,7 +8989,7 @@
         </is>
       </c>
       <c r="P140">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/selective-insurance/2026-04-06/69d3e012e63cea7a8b654262/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/selective-insurance/2026-04-06/69d3e012e63cea7a8b654262/resume.md")</f>
+        <f>HYPERLINK("by_company/selective-insurance/2026-04-06/69d3e012e63cea7a8b654262/resume.md","data/deliverables/resume_portfolio/by_company/selective-insurance/2026-04-06/69d3e012e63cea7a8b654262/resume.md")</f>
       </c>
       <c r="Q140"/>
       <c r="R140">
@@ -9055,7 +9055,7 @@
         </is>
       </c>
       <c r="P141">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/genentech/2026-04-06/69d3dd59366bb95ba5538099/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/genentech/2026-04-06/69d3dd59366bb95ba5538099/resume.md")</f>
+        <f>HYPERLINK("by_company/genentech/2026-04-06/69d3dd59366bb95ba5538099/resume.md","data/deliverables/resume_portfolio/by_company/genentech/2026-04-06/69d3dd59366bb95ba5538099/resume.md")</f>
       </c>
       <c r="Q141"/>
       <c r="R141">
@@ -9245,7 +9245,7 @@
         </is>
       </c>
       <c r="P144">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/genentech/2026-04-06/69d3dab0366bb95ba5537f43/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/genentech/2026-04-06/69d3dab0366bb95ba5537f43/resume.md")</f>
+        <f>HYPERLINK("by_company/genentech/2026-04-06/69d3dab0366bb95ba5537f43/resume.md","data/deliverables/resume_portfolio/by_company/genentech/2026-04-06/69d3dab0366bb95ba5537f43/resume.md")</f>
       </c>
       <c r="Q144"/>
       <c r="R144">
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="P145">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/beaconfire-inc/2026-04-06/69d3d7c3366bb95ba5537d8d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/beaconfire-inc/2026-04-06/69d3d7c3366bb95ba5537d8d/resume.md")</f>
+        <f>HYPERLINK("by_company/beaconfire-inc/2026-04-06/69d3d7c3366bb95ba5537d8d/resume.md","data/deliverables/resume_portfolio/by_company/beaconfire-inc/2026-04-06/69d3d7c3366bb95ba5537d8d/resume.md")</f>
       </c>
       <c r="Q145"/>
       <c r="R145">
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="P147">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/parsonskellogg/2026-04-06/69d3d603e63cea7a8b653d11/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/parsonskellogg/2026-04-06/69d3d603e63cea7a8b653d11/resume.md")</f>
+        <f>HYPERLINK("by_company/parsonskellogg/2026-04-06/69d3d603e63cea7a8b653d11/resume.md","data/deliverables/resume_portfolio/by_company/parsonskellogg/2026-04-06/69d3d603e63cea7a8b653d11/resume.md")</f>
       </c>
       <c r="Q147"/>
       <c r="R147">
@@ -9567,7 +9567,7 @@
         </is>
       </c>
       <c r="P149">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cisco/2026-04-06/69d3d5cacdb525785fbc37af/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cisco/2026-04-06/69d3d5cacdb525785fbc37af/resume.md")</f>
+        <f>HYPERLINK("by_company/cisco/2026-04-06/69d3d5cacdb525785fbc37af/resume.md","data/deliverables/resume_portfolio/by_company/cisco/2026-04-06/69d3d5cacdb525785fbc37af/resume.md")</f>
       </c>
       <c r="Q149"/>
       <c r="R149">
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="P151">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/m-science/2026-04-06/69d3bf91e63cea7a8b6525f9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/m-science/2026-04-06/69d3bf91e63cea7a8b6525f9/resume.md")</f>
+        <f>HYPERLINK("by_company/m-science/2026-04-06/69d3bf91e63cea7a8b6525f9/resume.md","data/deliverables/resume_portfolio/by_company/m-science/2026-04-06/69d3bf91e63cea7a8b6525f9/resume.md")</f>
       </c>
       <c r="Q151"/>
       <c r="R151">
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="P153">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/whsmith-north-america/2026-04-06/69b09052dfaeda6ff59aa6d4/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/whsmith-north-america/2026-04-06/69b09052dfaeda6ff59aa6d4/resume.md")</f>
+        <f>HYPERLINK("by_company/whsmith-north-america/2026-04-06/69b09052dfaeda6ff59aa6d4/resume.md","data/deliverables/resume_portfolio/by_company/whsmith-north-america/2026-04-06/69b09052dfaeda6ff59aa6d4/resume.md")</f>
       </c>
       <c r="Q153"/>
       <c r="R153">
@@ -10005,7 +10005,7 @@
         </is>
       </c>
       <c r="P156">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/pinnacle-medicines/2026-04-06/69d3cf39cdb525785fbc329c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/pinnacle-medicines/2026-04-06/69d3cf39cdb525785fbc329c/resume.md")</f>
+        <f>HYPERLINK("by_company/pinnacle-medicines/2026-04-06/69d3cf39cdb525785fbc329c/resume.md","data/deliverables/resume_portfolio/by_company/pinnacle-medicines/2026-04-06/69d3cf39cdb525785fbc329c/resume.md")</f>
       </c>
       <c r="Q156"/>
       <c r="R156">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="P160">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intel/2026-04-06/69d3ca41cfdc6132f9453dac/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intel/2026-04-06/69d3ca41cfdc6132f9453dac/resume.md")</f>
+        <f>HYPERLINK("by_company/intel/2026-04-06/69d3ca41cfdc6132f9453dac/resume.md","data/deliverables/resume_portfolio/by_company/intel/2026-04-06/69d3ca41cfdc6132f9453dac/resume.md")</f>
       </c>
       <c r="Q160"/>
       <c r="R160">
@@ -10319,7 +10319,7 @@
         </is>
       </c>
       <c r="P161">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/a-v-services-inc/2026-04-06/69b08184dfaeda6ff59a7b0f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/a-v-services-inc/2026-04-06/69b08184dfaeda6ff59a7b0f/resume.md")</f>
+        <f>HYPERLINK("by_company/a-v-services-inc/2026-04-06/69b08184dfaeda6ff59a7b0f/resume.md","data/deliverables/resume_portfolio/by_company/a-v-services-inc/2026-04-06/69b08184dfaeda6ff59a7b0f/resume.md")</f>
       </c>
       <c r="Q161"/>
       <c r="R161">
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="P162">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tiger-analytics/2026-04-06/69d3c58a54f00230c6d29e88/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tiger-analytics/2026-04-06/69d3c58a54f00230c6d29e88/resume.md")</f>
+        <f>HYPERLINK("by_company/tiger-analytics/2026-04-06/69d3c58a54f00230c6d29e88/resume.md","data/deliverables/resume_portfolio/by_company/tiger-analytics/2026-04-06/69d3c58a54f00230c6d29e88/resume.md")</f>
       </c>
       <c r="Q162"/>
       <c r="R162">
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="P163">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/lucid-motors/2026-04-06/6903bb5ad64a22104aa9240a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/lucid-motors/2026-04-06/6903bb5ad64a22104aa9240a/resume.md")</f>
+        <f>HYPERLINK("by_company/lucid-motors/2026-04-06/6903bb5ad64a22104aa9240a/resume.md","data/deliverables/resume_portfolio/by_company/lucid-motors/2026-04-06/6903bb5ad64a22104aa9240a/resume.md")</f>
       </c>
       <c r="Q163"/>
       <c r="R163">
@@ -10583,7 +10583,7 @@
         </is>
       </c>
       <c r="P165">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ramp/2026-04-06/6932ac66a0dde7020e2e80de/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ramp/2026-04-06/6932ac66a0dde7020e2e80de/resume.md")</f>
+        <f>HYPERLINK("by_company/ramp/2026-04-06/6932ac66a0dde7020e2e80de/resume.md","data/deliverables/resume_portfolio/by_company/ramp/2026-04-06/6932ac66a0dde7020e2e80de/resume.md")</f>
       </c>
       <c r="Q165"/>
       <c r="R165">
@@ -10773,7 +10773,7 @@
         </is>
       </c>
       <c r="P168">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-06/69d3b63a54f00230c6d299ab/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-06/69d3b63a54f00230c6d299ab/resume.md")</f>
+        <f>HYPERLINK("by_company/google/2026-04-06/69d3b63a54f00230c6d299ab/resume.md","data/deliverables/resume_portfolio/by_company/google/2026-04-06/69d3b63a54f00230c6d299ab/resume.md")</f>
       </c>
       <c r="Q168"/>
       <c r="R168">
@@ -11033,7 +11033,7 @@
         </is>
       </c>
       <c r="P172">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/uber/2026-04-06/699932bde0bddb6acac841d2/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/uber/2026-04-06/699932bde0bddb6acac841d2/resume.md")</f>
+        <f>HYPERLINK("by_company/uber/2026-04-06/699932bde0bddb6acac841d2/resume.md","data/deliverables/resume_portfolio/by_company/uber/2026-04-06/699932bde0bddb6acac841d2/resume.md")</f>
       </c>
       <c r="Q172"/>
       <c r="R172">
@@ -11099,7 +11099,7 @@
         </is>
       </c>
       <c r="P173">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/eliseai/2026-04-06/6913a31ae344172248f72c97/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/eliseai/2026-04-06/6913a31ae344172248f72c97/resume.md")</f>
+        <f>HYPERLINK("by_company/eliseai/2026-04-06/6913a31ae344172248f72c97/resume.md","data/deliverables/resume_portfolio/by_company/eliseai/2026-04-06/6913a31ae344172248f72c97/resume.md")</f>
       </c>
       <c r="Q173"/>
       <c r="R173">
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="P174">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/dbt-labs/2026-04-06/69d3a67fe63cea7a8b6519c9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/dbt-labs/2026-04-06/69d3a67fe63cea7a8b6519c9/resume.md")</f>
+        <f>HYPERLINK("by_company/dbt-labs/2026-04-06/69d3a67fe63cea7a8b6519c9/resume.md","data/deliverables/resume_portfolio/by_company/dbt-labs/2026-04-06/69d3a67fe63cea7a8b6519c9/resume.md")</f>
       </c>
       <c r="Q174"/>
       <c r="R174">
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="P175">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-06/68c9d1b9f9c6ff7aedf1e18a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-06/68c9d1b9f9c6ff7aedf1e18a/resume.md")</f>
+        <f>HYPERLINK("by_company/applied-intuition/2026-04-06/68c9d1b9f9c6ff7aedf1e18a/resume.md","data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-06/68c9d1b9f9c6ff7aedf1e18a/resume.md")</f>
       </c>
       <c r="Q175"/>
       <c r="R175">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="P176">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-06/69b7d08c3b74eb1e2c85793c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-06/69b7d08c3b74eb1e2c85793c/resume.md")</f>
+        <f>HYPERLINK("by_company/google/2026-04-06/69b7d08c3b74eb1e2c85793c/resume.md","data/deliverables/resume_portfolio/by_company/google/2026-04-06/69b7d08c3b74eb1e2c85793c/resume.md")</f>
       </c>
       <c r="Q176"/>
       <c r="R176">
@@ -11443,7 +11443,7 @@
         </is>
       </c>
       <c r="P178">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/openai/2026-04-06/68f0ac62eb273a32d976ba37/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/openai/2026-04-06/68f0ac62eb273a32d976ba37/resume.md")</f>
+        <f>HYPERLINK("by_company/openai/2026-04-06/68f0ac62eb273a32d976ba37/resume.md","data/deliverables/resume_portfolio/by_company/openai/2026-04-06/68f0ac62eb273a32d976ba37/resume.md")</f>
       </c>
       <c r="Q178"/>
       <c r="R178">
@@ -11625,7 +11625,7 @@
         </is>
       </c>
       <c r="P181">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/comulate/2026-04-06/69a3cfac0da45516f16cc887/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/comulate/2026-04-06/69a3cfac0da45516f16cc887/resume.md")</f>
+        <f>HYPERLINK("by_company/comulate/2026-04-06/69a3cfac0da45516f16cc887/resume.md","data/deliverables/resume_portfolio/by_company/comulate/2026-04-06/69a3cfac0da45516f16cc887/resume.md")</f>
       </c>
       <c r="Q181"/>
       <c r="R181">
@@ -11821,7 +11821,7 @@
         </is>
       </c>
       <c r="P184">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/doppel/2026-04-06/68cc6ce3128dc347fd924c22/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/doppel/2026-04-06/68cc6ce3128dc347fd924c22/resume.md")</f>
+        <f>HYPERLINK("by_company/doppel/2026-04-06/68cc6ce3128dc347fd924c22/resume.md","data/deliverables/resume_portfolio/by_company/doppel/2026-04-06/68cc6ce3128dc347fd924c22/resume.md")</f>
       </c>
       <c r="Q184"/>
       <c r="R184">
@@ -12009,7 +12009,7 @@
         </is>
       </c>
       <c r="P187">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/zoox/2026-04-06/6945bff3951654073537dcc6/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/zoox/2026-04-06/6945bff3951654073537dcc6/resume.md")</f>
+        <f>HYPERLINK("by_company/zoox/2026-04-06/6945bff3951654073537dcc6/resume.md","data/deliverables/resume_portfolio/by_company/zoox/2026-04-06/6945bff3951654073537dcc6/resume.md")</f>
       </c>
       <c r="Q187"/>
       <c r="R187">
@@ -12133,7 +12133,7 @@
         </is>
       </c>
       <c r="P189">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kikoff/2026-04-06/69d38de9cfdc6132f9451c7d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kikoff/2026-04-06/69d38de9cfdc6132f9451c7d/resume.md")</f>
+        <f>HYPERLINK("by_company/kikoff/2026-04-06/69d38de9cfdc6132f9451c7d/resume.md","data/deliverables/resume_portfolio/by_company/kikoff/2026-04-06/69d38de9cfdc6132f9451c7d/resume.md")</f>
       </c>
       <c r="Q189"/>
       <c r="R189">
@@ -12257,7 +12257,7 @@
         </is>
       </c>
       <c r="P191">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/viant-technology/2026-04-06/690e401dd046ab6061cfbaca/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/viant-technology/2026-04-06/690e401dd046ab6061cfbaca/resume.md")</f>
+        <f>HYPERLINK("by_company/viant-technology/2026-04-06/690e401dd046ab6061cfbaca/resume.md","data/deliverables/resume_portfolio/by_company/viant-technology/2026-04-06/690e401dd046ab6061cfbaca/resume.md")</f>
       </c>
       <c r="Q191"/>
       <c r="R191">
@@ -12505,7 +12505,7 @@
         </is>
       </c>
       <c r="P195">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-06/690bd915221b890c277f90de/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-06/690bd915221b890c277f90de/resume.md")</f>
+        <f>HYPERLINK("by_company/adobe/2026-04-06/690bd915221b890c277f90de/resume.md","data/deliverables/resume_portfolio/by_company/adobe/2026-04-06/690bd915221b890c277f90de/resume.md")</f>
       </c>
       <c r="Q195"/>
       <c r="R195">
@@ -12579,7 +12579,7 @@
         </is>
       </c>
       <c r="P196">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/uber/2026-04-06/69d3751954f00230c6d27f20/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/uber/2026-04-06/69d3751954f00230c6d27f20/resume.md")</f>
+        <f>HYPERLINK("by_company/uber/2026-04-06/69d3751954f00230c6d27f20/resume.md","data/deliverables/resume_portfolio/by_company/uber/2026-04-06/69d3751954f00230c6d27f20/resume.md")</f>
       </c>
       <c r="Q196"/>
       <c r="R196">
@@ -12711,7 +12711,7 @@
         </is>
       </c>
       <c r="P198">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/takedapharmaceutical-nordics-ab/2026-04-06/69d35cfa891d7b11cfcf07b1/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/takedapharmaceutical-nordics-ab/2026-04-06/69d35cfa891d7b11cfcf07b1/resume.md")</f>
+        <f>HYPERLINK("by_company/takedapharmaceutical-nordics-ab/2026-04-06/69d35cfa891d7b11cfcf07b1/resume.md","data/deliverables/resume_portfolio/by_company/takedapharmaceutical-nordics-ab/2026-04-06/69d35cfa891d7b11cfcf07b1/resume.md")</f>
       </c>
       <c r="Q198"/>
       <c r="R198">
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="P199">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ghx/2026-04-06/69d35ce7366bb95ba5533b18/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ghx/2026-04-06/69d35ce7366bb95ba5533b18/resume.md")</f>
+        <f>HYPERLINK("by_company/ghx/2026-04-06/69d35ce7366bb95ba5533b18/resume.md","data/deliverables/resume_portfolio/by_company/ghx/2026-04-06/69d35ce7366bb95ba5533b18/resume.md")</f>
       </c>
       <c r="Q199"/>
       <c r="R199">
@@ -12843,7 +12843,7 @@
         </is>
       </c>
       <c r="P200">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gap-solutions-inc/2026-04-06/69d35775891d7b11cfcf06bd/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gap-solutions-inc/2026-04-06/69d35775891d7b11cfcf06bd/resume.md")</f>
+        <f>HYPERLINK("by_company/gap-solutions-inc/2026-04-06/69d35775891d7b11cfcf06bd/resume.md","data/deliverables/resume_portfolio/by_company/gap-solutions-inc/2026-04-06/69d35775891d7b11cfcf06bd/resume.md")</f>
       </c>
       <c r="Q200"/>
       <c r="R200">
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="P201">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/stripe/2026-04-06/695c0fd1aa05c26e7ab560a9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/stripe/2026-04-06/695c0fd1aa05c26e7ab560a9/resume.md")</f>
+        <f>HYPERLINK("by_company/stripe/2026-04-06/695c0fd1aa05c26e7ab560a9/resume.md","data/deliverables/resume_portfolio/by_company/stripe/2026-04-06/695c0fd1aa05c26e7ab560a9/resume.md")</f>
       </c>
       <c r="Q201"/>
       <c r="R201">
@@ -13041,7 +13041,7 @@
         </is>
       </c>
       <c r="P203">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/raise-robotics/2026-04-05/69d335cdcfdc6132f944ebe5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/raise-robotics/2026-04-05/69d335cdcfdc6132f944ebe5/resume.md")</f>
+        <f>HYPERLINK("by_company/raise-robotics/2026-04-05/69d335cdcfdc6132f944ebe5/resume.md","data/deliverables/resume_portfolio/by_company/raise-robotics/2026-04-05/69d335cdcfdc6132f944ebe5/resume.md")</f>
       </c>
       <c r="Q203"/>
       <c r="R203">
@@ -13107,7 +13107,7 @@
         </is>
       </c>
       <c r="P204">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gei-consultants-inc/2026-04-05/69d328e7366bb95ba55314c9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gei-consultants-inc/2026-04-05/69d328e7366bb95ba55314c9/resume.md")</f>
+        <f>HYPERLINK("by_company/gei-consultants-inc/2026-04-05/69d328e7366bb95ba55314c9/resume.md","data/deliverables/resume_portfolio/by_company/gei-consultants-inc/2026-04-05/69d328e7366bb95ba55314c9/resume.md")</f>
       </c>
       <c r="Q204"/>
       <c r="R204">
@@ -13173,7 +13173,7 @@
         </is>
       </c>
       <c r="P205">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-05/69d31e2c54f00230c6d24aba/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-05/69d31e2c54f00230c6d24aba/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-05/69d31e2c54f00230c6d24aba/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-05/69d31e2c54f00230c6d24aba/resume.md")</f>
       </c>
       <c r="Q205"/>
       <c r="R205">
@@ -13355,7 +13355,7 @@
         </is>
       </c>
       <c r="P208">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/citadel-securities/2026-04-05/68c649c0c96a22563ececa76/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/citadel-securities/2026-04-05/68c649c0c96a22563ececa76/resume.md")</f>
+        <f>HYPERLINK("by_company/citadel-securities/2026-04-05/68c649c0c96a22563ececa76/resume.md","data/deliverables/resume_portfolio/by_company/citadel-securities/2026-04-05/68c649c0c96a22563ececa76/resume.md")</f>
       </c>
       <c r="Q208"/>
       <c r="R208">
@@ -13479,7 +13479,7 @@
         </is>
       </c>
       <c r="P210">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/dime-line-trading/2026-04-05/69ae1295142d5b4265fed2f9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/dime-line-trading/2026-04-05/69ae1295142d5b4265fed2f9/resume.md")</f>
+        <f>HYPERLINK("by_company/dime-line-trading/2026-04-05/69ae1295142d5b4265fed2f9/resume.md","data/deliverables/resume_portfolio/by_company/dime-line-trading/2026-04-05/69ae1295142d5b4265fed2f9/resume.md")</f>
       </c>
       <c r="Q210"/>
       <c r="R210">
@@ -13545,7 +13545,7 @@
         </is>
       </c>
       <c r="P211">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/metas-solutions/2026-04-05/69d2a4f0891d7b11cfceb69e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/metas-solutions/2026-04-05/69d2a4f0891d7b11cfceb69e/resume.md")</f>
+        <f>HYPERLINK("by_company/metas-solutions/2026-04-05/69d2a4f0891d7b11cfceb69e/resume.md","data/deliverables/resume_portfolio/by_company/metas-solutions/2026-04-05/69d2a4f0891d7b11cfceb69e/resume.md")</f>
       </c>
       <c r="Q211"/>
       <c r="R211">
@@ -13611,7 +13611,7 @@
         </is>
       </c>
       <c r="P212">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/github/2026-04-05/6999539e81476f6176b1f6b9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/github/2026-04-05/6999539e81476f6176b1f6b9/resume.md")</f>
+        <f>HYPERLINK("by_company/github/2026-04-05/6999539e81476f6176b1f6b9/resume.md","data/deliverables/resume_portfolio/by_company/github/2026-04-05/6999539e81476f6176b1f6b9/resume.md")</f>
       </c>
       <c r="Q212"/>
       <c r="R212">
@@ -13677,7 +13677,7 @@
         </is>
       </c>
       <c r="P213">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/first-citizens-bank/2026-04-05/697d289a137a051025662730/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/first-citizens-bank/2026-04-05/697d289a137a051025662730/resume.md")</f>
+        <f>HYPERLINK("by_company/first-citizens-bank/2026-04-05/697d289a137a051025662730/resume.md","data/deliverables/resume_portfolio/by_company/first-citizens-bank/2026-04-05/697d289a137a051025662730/resume.md")</f>
       </c>
       <c r="Q213"/>
       <c r="R213">
@@ -13743,7 +13743,7 @@
         </is>
       </c>
       <c r="P214">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hippocratic-ai/2026-04-05/69ad155d142d5b4265fe379e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hippocratic-ai/2026-04-05/69ad155d142d5b4265fe379e/resume.md")</f>
+        <f>HYPERLINK("by_company/hippocratic-ai/2026-04-05/69ad155d142d5b4265fe379e/resume.md","data/deliverables/resume_portfolio/by_company/hippocratic-ai/2026-04-05/69ad155d142d5b4265fe379e/resume.md")</f>
       </c>
       <c r="Q214"/>
       <c r="R214">
@@ -13809,7 +13809,7 @@
         </is>
       </c>
       <c r="P215">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/neuropace/2026-04-05/69d2981a0b098b7a6708978f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/neuropace/2026-04-05/69d2981a0b098b7a6708978f/resume.md")</f>
+        <f>HYPERLINK("by_company/neuropace/2026-04-05/69d2981a0b098b7a6708978f/resume.md","data/deliverables/resume_portfolio/by_company/neuropace/2026-04-05/69d2981a0b098b7a6708978f/resume.md")</f>
       </c>
       <c r="Q215"/>
       <c r="R215">
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="P216">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ibm/2026-04-05/69d20f73cdb525785fbb7e5b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ibm/2026-04-05/69d20f73cdb525785fbb7e5b/resume.md")</f>
+        <f>HYPERLINK("by_company/ibm/2026-04-05/69d20f73cdb525785fbb7e5b/resume.md","data/deliverables/resume_portfolio/by_company/ibm/2026-04-05/69d20f73cdb525785fbb7e5b/resume.md")</f>
       </c>
       <c r="Q216"/>
       <c r="R216">
@@ -13941,7 +13941,7 @@
         </is>
       </c>
       <c r="P217">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/synechron/2026-04-05/69c56ec4e565c26a7000f91a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/synechron/2026-04-05/69c56ec4e565c26a7000f91a/resume.md")</f>
+        <f>HYPERLINK("by_company/synechron/2026-04-05/69c56ec4e565c26a7000f91a/resume.md","data/deliverables/resume_portfolio/by_company/synechron/2026-04-05/69c56ec4e565c26a7000f91a/resume.md")</f>
       </c>
       <c r="Q217"/>
       <c r="R217">
@@ -14007,7 +14007,7 @@
         </is>
       </c>
       <c r="P218">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-05/697d7837137a051025669af8/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-05/697d7837137a051025669af8/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon-web-services-aws/2026-04-05/697d7837137a051025669af8/resume.md","data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-05/697d7837137a051025669af8/resume.md")</f>
       </c>
       <c r="Q218"/>
       <c r="R218">
@@ -14139,7 +14139,7 @@
         </is>
       </c>
       <c r="P220">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-05/697d7d4b3f57a3356967669e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-05/697d7d4b3f57a3356967669e/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon/2026-04-05/697d7d4b3f57a3356967669e/resume.md","data/deliverables/resume_portfolio/by_company/amazon/2026-04-05/697d7d4b3f57a3356967669e/resume.md")</f>
       </c>
       <c r="Q220"/>
       <c r="R220">
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="P221">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/totalenergies/2026-04-05/699931c9e0bddb6acac83f00/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/totalenergies/2026-04-05/699931c9e0bddb6acac83f00/resume.md")</f>
+        <f>HYPERLINK("by_company/totalenergies/2026-04-05/699931c9e0bddb6acac83f00/resume.md","data/deliverables/resume_portfolio/by_company/totalenergies/2026-04-05/699931c9e0bddb6acac83f00/resume.md")</f>
       </c>
       <c r="Q221"/>
       <c r="R221">
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P224">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/anyscale/2026-04-05/69b6af4206c1ba00c548855d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/anyscale/2026-04-05/69b6af4206c1ba00c548855d/resume.md")</f>
+        <f>HYPERLINK("by_company/anyscale/2026-04-05/69b6af4206c1ba00c548855d/resume.md","data/deliverables/resume_portfolio/by_company/anyscale/2026-04-05/69b6af4206c1ba00c548855d/resume.md")</f>
       </c>
       <c r="Q224"/>
       <c r="R224">
@@ -14475,7 +14475,7 @@
         </is>
       </c>
       <c r="P225">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hover/2026-04-05/69992d53ce78e77b4fdde2cf/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hover/2026-04-05/69992d53ce78e77b4fdde2cf/resume.md")</f>
+        <f>HYPERLINK("by_company/hover/2026-04-05/69992d53ce78e77b4fdde2cf/resume.md","data/deliverables/resume_portfolio/by_company/hover/2026-04-05/69992d53ce78e77b4fdde2cf/resume.md")</f>
       </c>
       <c r="Q225"/>
       <c r="R225">
@@ -14541,7 +14541,7 @@
         </is>
       </c>
       <c r="P226">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/scale-ai/2026-04-05/68cd95201ad6b16f0289bced/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/scale-ai/2026-04-05/68cd95201ad6b16f0289bced/resume.md")</f>
+        <f>HYPERLINK("by_company/scale-ai/2026-04-05/68cd95201ad6b16f0289bced/resume.md","data/deliverables/resume_portfolio/by_company/scale-ai/2026-04-05/68cd95201ad6b16f0289bced/resume.md")</f>
       </c>
       <c r="Q226"/>
       <c r="R226">
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="P229">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/the-trade-desk/2026-04-05/69cec0c8366bb95ba550ef84/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/the-trade-desk/2026-04-05/69cec0c8366bb95ba550ef84/resume.md")</f>
+        <f>HYPERLINK("by_company/the-trade-desk/2026-04-05/69cec0c8366bb95ba550ef84/resume.md","data/deliverables/resume_portfolio/by_company/the-trade-desk/2026-04-05/69cec0c8366bb95ba550ef84/resume.md")</f>
       </c>
       <c r="Q229"/>
       <c r="R229">
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="P233">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-05/689d4cb179a9f9666253eeaa/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-05/689d4cb179a9f9666253eeaa/resume.md")</f>
+        <f>HYPERLINK("by_company/applied-intuition/2026-04-05/689d4cb179a9f9666253eeaa/resume.md","data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-05/689d4cb179a9f9666253eeaa/resume.md")</f>
       </c>
       <c r="Q233"/>
       <c r="R233">
@@ -15043,7 +15043,7 @@
         </is>
       </c>
       <c r="P234">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-05/674973e29a71c8abf4986751/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-05/674973e29a71c8abf4986751/resume.md")</f>
+        <f>HYPERLINK("by_company/applied-intuition/2026-04-05/674973e29a71c8abf4986751/resume.md","data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-05/674973e29a71c8abf4986751/resume.md")</f>
       </c>
       <c r="Q234"/>
       <c r="R234">
@@ -15167,7 +15167,7 @@
         </is>
       </c>
       <c r="P236">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-05/68c8652ff9c6ff7aedf0dba6/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-05/68c8652ff9c6ff7aedf0dba6/resume.md")</f>
+        <f>HYPERLINK("by_company/applied-intuition/2026-04-05/68c8652ff9c6ff7aedf0dba6/resume.md","data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-05/68c8652ff9c6ff7aedf0dba6/resume.md")</f>
       </c>
       <c r="Q236"/>
       <c r="R236">
@@ -15241,7 +15241,7 @@
         </is>
       </c>
       <c r="P237">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/light-wonder/2026-04-05/69d259d0366bb95ba552d5f7/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/light-wonder/2026-04-05/69d259d0366bb95ba552d5f7/resume.md")</f>
+        <f>HYPERLINK("by_company/light-wonder/2026-04-05/69d259d0366bb95ba552d5f7/resume.md","data/deliverables/resume_portfolio/by_company/light-wonder/2026-04-05/69d259d0366bb95ba552d5f7/resume.md")</f>
       </c>
       <c r="Q237"/>
       <c r="R237">
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="P239">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/teza-technologies/2026-04-05/69a65e292c0d8b0f5cd07dbf/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/teza-technologies/2026-04-05/69a65e292c0d8b0f5cd07dbf/resume.md")</f>
+        <f>HYPERLINK("by_company/teza-technologies/2026-04-05/69a65e292c0d8b0f5cd07dbf/resume.md","data/deliverables/resume_portfolio/by_company/teza-technologies/2026-04-05/69a65e292c0d8b0f5cd07dbf/resume.md")</f>
       </c>
       <c r="Q239"/>
       <c r="R239">
@@ -15439,7 +15439,7 @@
         </is>
       </c>
       <c r="P240">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/appian/2026-04-05/69b423843b74eb1e2c8139c0/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/appian/2026-04-05/69b423843b74eb1e2c8139c0/resume.md")</f>
+        <f>HYPERLINK("by_company/appian/2026-04-05/69b423843b74eb1e2c8139c0/resume.md","data/deliverables/resume_portfolio/by_company/appian/2026-04-05/69b423843b74eb1e2c8139c0/resume.md")</f>
       </c>
       <c r="Q240"/>
       <c r="R240">
@@ -15505,7 +15505,7 @@
         </is>
       </c>
       <c r="P241">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hudson-river-trading/2026-04-05/690cded54a1b456627b1b2ea/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hudson-river-trading/2026-04-05/690cded54a1b456627b1b2ea/resume.md")</f>
+        <f>HYPERLINK("by_company/hudson-river-trading/2026-04-05/690cded54a1b456627b1b2ea/resume.md","data/deliverables/resume_portfolio/by_company/hudson-river-trading/2026-04-05/690cded54a1b456627b1b2ea/resume.md")</f>
       </c>
       <c r="Q241"/>
       <c r="R241">
@@ -15571,7 +15571,7 @@
         </is>
       </c>
       <c r="P242">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/oura/2026-04-05/69b1ae5c548f140066e77836/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/oura/2026-04-05/69b1ae5c548f140066e77836/resume.md")</f>
+        <f>HYPERLINK("by_company/oura/2026-04-05/69b1ae5c548f140066e77836/resume.md","data/deliverables/resume_portfolio/by_company/oura/2026-04-05/69b1ae5c548f140066e77836/resume.md")</f>
       </c>
       <c r="Q242"/>
       <c r="R242">
@@ -15637,7 +15637,7 @@
         </is>
       </c>
       <c r="P243">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/miq/2026-04-05/690d31754a1b456627b1f081/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/miq/2026-04-05/690d31754a1b456627b1f081/resume.md")</f>
+        <f>HYPERLINK("by_company/miq/2026-04-05/690d31754a1b456627b1f081/resume.md","data/deliverables/resume_portfolio/by_company/miq/2026-04-05/690d31754a1b456627b1f081/resume.md")</f>
       </c>
       <c r="Q243"/>
       <c r="R243">
@@ -15703,7 +15703,7 @@
         </is>
       </c>
       <c r="P244">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/chime/2026-04-05/690c20c14a1b456627b1666a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/chime/2026-04-05/690c20c14a1b456627b1666a/resume.md")</f>
+        <f>HYPERLINK("by_company/chime/2026-04-05/690c20c14a1b456627b1666a/resume.md","data/deliverables/resume_portfolio/by_company/chime/2026-04-05/690c20c14a1b456627b1666a/resume.md")</f>
       </c>
       <c r="Q244"/>
       <c r="R244">
@@ -15769,7 +15769,7 @@
         </is>
       </c>
       <c r="P245">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hinge/2026-04-05/69449e44a7227b3ece66379b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hinge/2026-04-05/69449e44a7227b3ece66379b/resume.md")</f>
+        <f>HYPERLINK("by_company/hinge/2026-04-05/69449e44a7227b3ece66379b/resume.md","data/deliverables/resume_portfolio/by_company/hinge/2026-04-05/69449e44a7227b3ece66379b/resume.md")</f>
       </c>
       <c r="Q245"/>
       <c r="R245">
@@ -15835,7 +15835,7 @@
         </is>
       </c>
       <c r="P246">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/shipt/2026-04-05/690a8b2ebcccf20de59e3b1e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/shipt/2026-04-05/690a8b2ebcccf20de59e3b1e/resume.md")</f>
+        <f>HYPERLINK("by_company/shipt/2026-04-05/690a8b2ebcccf20de59e3b1e/resume.md","data/deliverables/resume_portfolio/by_company/shipt/2026-04-05/690a8b2ebcccf20de59e3b1e/resume.md")</f>
       </c>
       <c r="Q246"/>
       <c r="R246">
@@ -16023,7 +16023,7 @@
         </is>
       </c>
       <c r="P249">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hopper/2026-04-05/69460fb363141d188455bea1/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hopper/2026-04-05/69460fb363141d188455bea1/resume.md")</f>
+        <f>HYPERLINK("by_company/hopper/2026-04-05/69460fb363141d188455bea1/resume.md","data/deliverables/resume_portfolio/by_company/hopper/2026-04-05/69460fb363141d188455bea1/resume.md")</f>
       </c>
       <c r="Q249"/>
       <c r="R249">
@@ -16147,7 +16147,7 @@
         </is>
       </c>
       <c r="P251">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hopper/2026-04-05/69460bf97d506e3808f16216/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hopper/2026-04-05/69460bf97d506e3808f16216/resume.md")</f>
+        <f>HYPERLINK("by_company/hopper/2026-04-05/69460bf97d506e3808f16216/resume.md","data/deliverables/resume_portfolio/by_company/hopper/2026-04-05/69460bf97d506e3808f16216/resume.md")</f>
       </c>
       <c r="Q251"/>
       <c r="R251">
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="P254">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/clay/2026-04-05/6998e02481476f6176b146be/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/clay/2026-04-05/6998e02481476f6176b146be/resume.md")</f>
+        <f>HYPERLINK("by_company/clay/2026-04-05/6998e02481476f6176b146be/resume.md","data/deliverables/resume_portfolio/by_company/clay/2026-04-05/6998e02481476f6176b146be/resume.md")</f>
       </c>
       <c r="Q254"/>
       <c r="R254">
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="P255">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/medpace/2026-04-05/6961e0ffe7ed9a5731baa692/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/medpace/2026-04-05/6961e0ffe7ed9a5731baa692/resume.md")</f>
+        <f>HYPERLINK("by_company/medpace/2026-04-05/6961e0ffe7ed9a5731baa692/resume.md","data/deliverables/resume_portfolio/by_company/medpace/2026-04-05/6961e0ffe7ed9a5731baa692/resume.md")</f>
       </c>
       <c r="Q255"/>
       <c r="R255">
@@ -16469,7 +16469,7 @@
         </is>
       </c>
       <c r="P256">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-05/69a02a9c0836fe79d860f9e2/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-05/69a02a9c0836fe79d860f9e2/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-05/69a02a9c0836fe79d860f9e2/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-05/69a02a9c0836fe79d860f9e2/resume.md")</f>
       </c>
       <c r="Q256"/>
       <c r="R256">
@@ -16535,7 +16535,7 @@
         </is>
       </c>
       <c r="P257">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-05/69bef175b106024562845264/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-05/69bef175b106024562845264/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-05/69bef175b106024562845264/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-05/69bef175b106024562845264/resume.md")</f>
       </c>
       <c r="Q257"/>
       <c r="R257">
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="P258">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/whoop/2026-04-05/697d6fc23f57a33569675482/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/whoop/2026-04-05/697d6fc23f57a33569675482/resume.md")</f>
+        <f>HYPERLINK("by_company/whoop/2026-04-05/697d6fc23f57a33569675482/resume.md","data/deliverables/resume_portfolio/by_company/whoop/2026-04-05/697d6fc23f57a33569675482/resume.md")</f>
       </c>
       <c r="Q258"/>
       <c r="R258">
@@ -16667,7 +16667,7 @@
         </is>
       </c>
       <c r="P259">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/venmo/2026-04-05/698fd90c0f6f7e7a2cec1f81/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/venmo/2026-04-05/698fd90c0f6f7e7a2cec1f81/resume.md")</f>
+        <f>HYPERLINK("by_company/venmo/2026-04-05/698fd90c0f6f7e7a2cec1f81/resume.md","data/deliverables/resume_portfolio/by_company/venmo/2026-04-05/698fd90c0f6f7e7a2cec1f81/resume.md")</f>
       </c>
       <c r="Q259"/>
       <c r="R259">
@@ -16733,7 +16733,7 @@
         </is>
       </c>
       <c r="P260">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/clear/2026-04-05/695fe269a112b402660e842a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/clear/2026-04-05/695fe269a112b402660e842a/resume.md")</f>
+        <f>HYPERLINK("by_company/clear/2026-04-05/695fe269a112b402660e842a/resume.md","data/deliverables/resume_portfolio/by_company/clear/2026-04-05/695fe269a112b402660e842a/resume.md")</f>
       </c>
       <c r="Q260"/>
       <c r="R260">
@@ -16979,7 +16979,7 @@
         </is>
       </c>
       <c r="P264">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-05/690d2c2f221b890c278043d0/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-05/690d2c2f221b890c278043d0/resume.md")</f>
+        <f>HYPERLINK("by_company/adobe/2026-04-05/690d2c2f221b890c278043d0/resume.md","data/deliverables/resume_portfolio/by_company/adobe/2026-04-05/690d2c2f221b890c278043d0/resume.md")</f>
       </c>
       <c r="Q264"/>
       <c r="R264">
@@ -17045,7 +17045,7 @@
         </is>
       </c>
       <c r="P265">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/optum/2026-04-05/69d23b090b098b7a67087951/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/optum/2026-04-05/69d23b090b098b7a67087951/resume.md")</f>
+        <f>HYPERLINK("by_company/optum/2026-04-05/69d23b090b098b7a67087951/resume.md","data/deliverables/resume_portfolio/by_company/optum/2026-04-05/69d23b090b098b7a67087951/resume.md")</f>
       </c>
       <c r="Q265"/>
       <c r="R265">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="P271">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/medidata-solutions/2026-04-04/69d189eb366bb95ba5526fce/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/medidata-solutions/2026-04-04/69d189eb366bb95ba5526fce/resume.md")</f>
+        <f>HYPERLINK("by_company/medidata-solutions/2026-04-04/69d189eb366bb95ba5526fce/resume.md","data/deliverables/resume_portfolio/by_company/medidata-solutions/2026-04-04/69d189eb366bb95ba5526fce/resume.md")</f>
       </c>
       <c r="Q271"/>
       <c r="R271">
@@ -17597,7 +17597,7 @@
         </is>
       </c>
       <c r="P274">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/capital-one/2026-04-04/697ba5b80b88cc7d6422756c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/capital-one/2026-04-04/697ba5b80b88cc7d6422756c/resume.md")</f>
+        <f>HYPERLINK("by_company/capital-one/2026-04-04/697ba5b80b88cc7d6422756c/resume.md","data/deliverables/resume_portfolio/by_company/capital-one/2026-04-04/697ba5b80b88cc7d6422756c/resume.md")</f>
       </c>
       <c r="Q274"/>
       <c r="R274">
@@ -17663,7 +17663,7 @@
         </is>
       </c>
       <c r="P275">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/twilio/2026-04-04/69c8be9783ea553769feb995/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/twilio/2026-04-04/69c8be9783ea553769feb995/resume.md")</f>
+        <f>HYPERLINK("by_company/twilio/2026-04-04/69c8be9783ea553769feb995/resume.md","data/deliverables/resume_portfolio/by_company/twilio/2026-04-04/69c8be9783ea553769feb995/resume.md")</f>
       </c>
       <c r="Q275"/>
       <c r="R275">
@@ -17729,7 +17729,7 @@
         </is>
       </c>
       <c r="P276">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/capital-one/2026-04-04/69b412be3b74eb1e2c811e87/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/capital-one/2026-04-04/69b412be3b74eb1e2c811e87/resume.md")</f>
+        <f>HYPERLINK("by_company/capital-one/2026-04-04/69b412be3b74eb1e2c811e87/resume.md","data/deliverables/resume_portfolio/by_company/capital-one/2026-04-04/69b412be3b74eb1e2c811e87/resume.md")</f>
       </c>
       <c r="Q276"/>
       <c r="R276">
@@ -17795,7 +17795,7 @@
         </is>
       </c>
       <c r="P277">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/msx-international/2026-04-04/697d23a3137a051025661bfb/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/msx-international/2026-04-04/697d23a3137a051025661bfb/resume.md")</f>
+        <f>HYPERLINK("by_company/msx-international/2026-04-04/697d23a3137a051025661bfb/resume.md","data/deliverables/resume_portfolio/by_company/msx-international/2026-04-04/697d23a3137a051025661bfb/resume.md")</f>
       </c>
       <c r="Q277"/>
       <c r="R277">
@@ -17919,7 +17919,7 @@
         </is>
       </c>
       <c r="P279">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fanduel/2026-04-04/69cd481e891d7b11cfcb709b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fanduel/2026-04-04/69cd481e891d7b11cfcb709b/resume.md")</f>
+        <f>HYPERLINK("by_company/fanduel/2026-04-04/69cd481e891d7b11cfcb709b/resume.md","data/deliverables/resume_portfolio/by_company/fanduel/2026-04-04/69cd481e891d7b11cfcb709b/resume.md")</f>
       </c>
       <c r="Q279"/>
       <c r="R279">
@@ -17985,7 +17985,7 @@
         </is>
       </c>
       <c r="P280">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/docusign/2026-04-04/69b44f483b74eb1e2c8186c8/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/docusign/2026-04-04/69b44f483b74eb1e2c8186c8/resume.md")</f>
+        <f>HYPERLINK("by_company/docusign/2026-04-04/69b44f483b74eb1e2c8186c8/resume.md","data/deliverables/resume_portfolio/by_company/docusign/2026-04-04/69b44f483b74eb1e2c8186c8/resume.md")</f>
       </c>
       <c r="Q280"/>
       <c r="R280">
@@ -18051,7 +18051,7 @@
         </is>
       </c>
       <c r="P281">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hearst-magazines/2026-04-04/69bf7ca22c312363dcd232a0/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hearst-magazines/2026-04-04/69bf7ca22c312363dcd232a0/resume.md")</f>
+        <f>HYPERLINK("by_company/hearst-magazines/2026-04-04/69bf7ca22c312363dcd232a0/resume.md","data/deliverables/resume_portfolio/by_company/hearst-magazines/2026-04-04/69bf7ca22c312363dcd232a0/resume.md")</f>
       </c>
       <c r="Q281"/>
       <c r="R281">
@@ -18117,7 +18117,7 @@
         </is>
       </c>
       <c r="P282">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/blackrock/2026-04-04/69ced72b54f00230c6d0376b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/blackrock/2026-04-04/69ced72b54f00230c6d0376b/resume.md")</f>
+        <f>HYPERLINK("by_company/blackrock/2026-04-04/69ced72b54f00230c6d0376b/resume.md","data/deliverables/resume_portfolio/by_company/blackrock/2026-04-04/69ced72b54f00230c6d0376b/resume.md")</f>
       </c>
       <c r="Q282"/>
       <c r="R282">
@@ -18183,7 +18183,7 @@
         </is>
       </c>
       <c r="P283">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/real-chemistry/2026-04-04/696192f3e7ed9a5731ba6d49/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/real-chemistry/2026-04-04/696192f3e7ed9a5731ba6d49/resume.md")</f>
+        <f>HYPERLINK("by_company/real-chemistry/2026-04-04/696192f3e7ed9a5731ba6d49/resume.md","data/deliverables/resume_portfolio/by_company/real-chemistry/2026-04-04/696192f3e7ed9a5731ba6d49/resume.md")</f>
       </c>
       <c r="Q283"/>
       <c r="R283">
@@ -18365,7 +18365,7 @@
         </is>
       </c>
       <c r="P286">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ccc-intelligent-solutions/2026-04-04/699960d5e0bddb6acac89104/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ccc-intelligent-solutions/2026-04-04/699960d5e0bddb6acac89104/resume.md")</f>
+        <f>HYPERLINK("by_company/ccc-intelligent-solutions/2026-04-04/699960d5e0bddb6acac89104/resume.md","data/deliverables/resume_portfolio/by_company/ccc-intelligent-solutions/2026-04-04/699960d5e0bddb6acac89104/resume.md")</f>
       </c>
       <c r="Q286"/>
       <c r="R286">
@@ -18547,7 +18547,7 @@
         </is>
       </c>
       <c r="P289">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fanduel/2026-04-04/68ee7e1ed078b81ad160a7de/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fanduel/2026-04-04/68ee7e1ed078b81ad160a7de/resume.md")</f>
+        <f>HYPERLINK("by_company/fanduel/2026-04-04/68ee7e1ed078b81ad160a7de/resume.md","data/deliverables/resume_portfolio/by_company/fanduel/2026-04-04/68ee7e1ed078b81ad160a7de/resume.md")</f>
       </c>
       <c r="Q289"/>
       <c r="R289">
@@ -18613,7 +18613,7 @@
         </is>
       </c>
       <c r="P290">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/goldman-sachs/2026-04-04/69c626d6e565c26a7001ac2a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/goldman-sachs/2026-04-04/69c626d6e565c26a7001ac2a/resume.md")</f>
+        <f>HYPERLINK("by_company/goldman-sachs/2026-04-04/69c626d6e565c26a7001ac2a/resume.md","data/deliverables/resume_portfolio/by_company/goldman-sachs/2026-04-04/69c626d6e565c26a7001ac2a/resume.md")</f>
       </c>
       <c r="Q290"/>
       <c r="R290">
@@ -18679,7 +18679,7 @@
         </is>
       </c>
       <c r="P291">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sofi/2026-04-04/6961ce41e7ed9a5731ba9ca2/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sofi/2026-04-04/6961ce41e7ed9a5731ba9ca2/resume.md")</f>
+        <f>HYPERLINK("by_company/sofi/2026-04-04/6961ce41e7ed9a5731ba9ca2/resume.md","data/deliverables/resume_portfolio/by_company/sofi/2026-04-04/6961ce41e7ed9a5731ba9ca2/resume.md")</f>
       </c>
       <c r="Q291"/>
       <c r="R291">
@@ -18803,7 +18803,7 @@
         </is>
       </c>
       <c r="P293">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intuit/2026-04-04/69d1454acfdc6132f9442ba5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intuit/2026-04-04/69d1454acfdc6132f9442ba5/resume.md")</f>
+        <f>HYPERLINK("by_company/intuit/2026-04-04/69d1454acfdc6132f9442ba5/resume.md","data/deliverables/resume_portfolio/by_company/intuit/2026-04-04/69d1454acfdc6132f9442ba5/resume.md")</f>
       </c>
       <c r="Q293"/>
       <c r="R293">
@@ -18927,7 +18927,7 @@
         </is>
       </c>
       <c r="P295">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/applied-materials/2026-04-04/69d14513cdb525785fbb1a6c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/applied-materials/2026-04-04/69d14513cdb525785fbb1a6c/resume.md")</f>
+        <f>HYPERLINK("by_company/applied-materials/2026-04-04/69d14513cdb525785fbb1a6c/resume.md","data/deliverables/resume_portfolio/by_company/applied-materials/2026-04-04/69d14513cdb525785fbb1a6c/resume.md")</f>
       </c>
       <c r="Q295"/>
       <c r="R295">
@@ -18993,7 +18993,7 @@
         </is>
       </c>
       <c r="P296">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/priceline/2026-04-04/6998c18ace78e77b4fdd544f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/priceline/2026-04-04/6998c18ace78e77b4fdd544f/resume.md")</f>
+        <f>HYPERLINK("by_company/priceline/2026-04-04/6998c18ace78e77b4fdd544f/resume.md","data/deliverables/resume_portfolio/by_company/priceline/2026-04-04/6998c18ace78e77b4fdd544f/resume.md")</f>
       </c>
       <c r="Q296"/>
       <c r="R296">
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="P298">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/glean/2026-04-04/69bc287f5b89c002acf160da/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/glean/2026-04-04/69bc287f5b89c002acf160da/resume.md")</f>
+        <f>HYPERLINK("by_company/glean/2026-04-04/69bc287f5b89c002acf160da/resume.md","data/deliverables/resume_portfolio/by_company/glean/2026-04-04/69bc287f5b89c002acf160da/resume.md")</f>
       </c>
       <c r="Q298"/>
       <c r="R298">
@@ -19183,7 +19183,7 @@
         </is>
       </c>
       <c r="P299">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/glean/2026-04-04/689aa14ffaa4e875e825a5de/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/glean/2026-04-04/689aa14ffaa4e875e825a5de/resume.md")</f>
+        <f>HYPERLINK("by_company/glean/2026-04-04/689aa14ffaa4e875e825a5de/resume.md","data/deliverables/resume_portfolio/by_company/glean/2026-04-04/689aa14ffaa4e875e825a5de/resume.md")</f>
       </c>
       <c r="Q299"/>
       <c r="R299">
@@ -19739,7 +19739,7 @@
         </is>
       </c>
       <c r="P308">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/glean/2026-04-04/6863515f060dab0b62ab65f0/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/glean/2026-04-04/6863515f060dab0b62ab65f0/resume.md")</f>
+        <f>HYPERLINK("by_company/glean/2026-04-04/6863515f060dab0b62ab65f0/resume.md","data/deliverables/resume_portfolio/by_company/glean/2026-04-04/6863515f060dab0b62ab65f0/resume.md")</f>
       </c>
       <c r="Q308"/>
       <c r="R308">
@@ -19805,7 +19805,7 @@
         </is>
       </c>
       <c r="P309">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/five9/2026-04-04/69b4c4cb3b74eb1e2c8223d6/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/five9/2026-04-04/69b4c4cb3b74eb1e2c8223d6/resume.md")</f>
+        <f>HYPERLINK("by_company/five9/2026-04-04/69b4c4cb3b74eb1e2c8223d6/resume.md","data/deliverables/resume_portfolio/by_company/five9/2026-04-04/69b4c4cb3b74eb1e2c8223d6/resume.md")</f>
       </c>
       <c r="Q309"/>
       <c r="R309">
@@ -19871,7 +19871,7 @@
         </is>
       </c>
       <c r="P310">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/grid/2026-04-04/69d13d7bcfdc6132f9442412/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/grid/2026-04-04/69d13d7bcfdc6132f9442412/resume.md")</f>
+        <f>HYPERLINK("by_company/grid/2026-04-04/69d13d7bcfdc6132f9442412/resume.md","data/deliverables/resume_portfolio/by_company/grid/2026-04-04/69d13d7bcfdc6132f9442412/resume.md")</f>
       </c>
       <c r="Q310"/>
       <c r="R310">
@@ -19995,7 +19995,7 @@
         </is>
       </c>
       <c r="P312">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intrinsic/2026-04-04/69991f13e0bddb6acac81f62/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intrinsic/2026-04-04/69991f13e0bddb6acac81f62/resume.md")</f>
+        <f>HYPERLINK("by_company/intrinsic/2026-04-04/69991f13e0bddb6acac81f62/resume.md","data/deliverables/resume_portfolio/by_company/intrinsic/2026-04-04/69991f13e0bddb6acac81f62/resume.md")</f>
       </c>
       <c r="Q312"/>
       <c r="R312">
@@ -20069,7 +20069,7 @@
         </is>
       </c>
       <c r="P313">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-04/697d74fd137a0510256697d9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-04/697d74fd137a0510256697d9/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon/2026-04-04/697d74fd137a0510256697d9/resume.md","data/deliverables/resume_portfolio/by_company/amazon/2026-04-04/697d74fd137a0510256697d9/resume.md")</f>
       </c>
       <c r="Q313"/>
       <c r="R313">
@@ -20201,7 +20201,7 @@
         </is>
       </c>
       <c r="P315">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/whatnot/2026-04-04/6929a3d166796e3028f8ccae/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/whatnot/2026-04-04/6929a3d166796e3028f8ccae/resume.md")</f>
+        <f>HYPERLINK("by_company/whatnot/2026-04-04/6929a3d166796e3028f8ccae/resume.md","data/deliverables/resume_portfolio/by_company/whatnot/2026-04-04/6929a3d166796e3028f8ccae/resume.md")</f>
       </c>
       <c r="Q315"/>
       <c r="R315">
@@ -20389,7 +20389,7 @@
         </is>
       </c>
       <c r="P318">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/coherent-corp/2026-04-04/69b4c47b06c1ba00c54643ae/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/coherent-corp/2026-04-04/69b4c47b06c1ba00c54643ae/resume.md")</f>
+        <f>HYPERLINK("by_company/coherent-corp/2026-04-04/69b4c47b06c1ba00c54643ae/resume.md","data/deliverables/resume_portfolio/by_company/coherent-corp/2026-04-04/69b4c47b06c1ba00c54643ae/resume.md")</f>
       </c>
       <c r="Q318"/>
       <c r="R318">
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="P320">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-04/69d130c4891d7b11cfce230e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-04/69d130c4891d7b11cfce230e/resume.md")</f>
+        <f>HYPERLINK("by_company/ss-c-technologies/2026-04-04/69d130c4891d7b11cfce230e/resume.md","data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-04/69d130c4891d7b11cfce230e/resume.md")</f>
       </c>
       <c r="Q320"/>
       <c r="R320">
@@ -20587,7 +20587,7 @@
         </is>
       </c>
       <c r="P321">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/audible/2026-04-04/6997d78ace78e77b4fdc475f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/audible/2026-04-04/6997d78ace78e77b4fdc475f/resume.md")</f>
+        <f>HYPERLINK("by_company/audible/2026-04-04/6997d78ace78e77b4fdc475f/resume.md","data/deliverables/resume_portfolio/by_company/audible/2026-04-04/6997d78ace78e77b4fdc475f/resume.md")</f>
       </c>
       <c r="Q321"/>
       <c r="R321">
@@ -20719,7 +20719,7 @@
         </is>
       </c>
       <c r="P323">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-04/69982241e0bddb6acac725a3/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-04/69982241e0bddb6acac725a3/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon/2026-04-04/69982241e0bddb6acac725a3/resume.md","data/deliverables/resume_portfolio/by_company/amazon/2026-04-04/69982241e0bddb6acac725a3/resume.md")</f>
       </c>
       <c r="Q323"/>
       <c r="R323">
@@ -20785,7 +20785,7 @@
         </is>
       </c>
       <c r="P324">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/seismic/2026-04-04/69c7507f83ea553769fe2637/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/seismic/2026-04-04/69c7507f83ea553769fe2637/resume.md")</f>
+        <f>HYPERLINK("by_company/seismic/2026-04-04/69c7507f83ea553769fe2637/resume.md","data/deliverables/resume_portfolio/by_company/seismic/2026-04-04/69c7507f83ea553769fe2637/resume.md")</f>
       </c>
       <c r="Q324"/>
       <c r="R324">
@@ -20851,7 +20851,7 @@
         </is>
       </c>
       <c r="P325">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/openai/2026-04-04/69b4e6033b74eb1e2c825a6c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/openai/2026-04-04/69b4e6033b74eb1e2c825a6c/resume.md")</f>
+        <f>HYPERLINK("by_company/openai/2026-04-04/69b4e6033b74eb1e2c825a6c/resume.md","data/deliverables/resume_portfolio/by_company/openai/2026-04-04/69b4e6033b74eb1e2c825a6c/resume.md")</f>
       </c>
       <c r="Q325"/>
       <c r="R325">
@@ -20917,7 +20917,7 @@
         </is>
       </c>
       <c r="P326">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/m3/2026-04-04/69977102ce78e77b4fdbc835/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/m3/2026-04-04/69977102ce78e77b4fdbc835/resume.md")</f>
+        <f>HYPERLINK("by_company/m3/2026-04-04/69977102ce78e77b4fdbc835/resume.md","data/deliverables/resume_portfolio/by_company/m3/2026-04-04/69977102ce78e77b4fdbc835/resume.md")</f>
       </c>
       <c r="Q326"/>
       <c r="R326">
@@ -21041,7 +21041,7 @@
         </is>
       </c>
       <c r="P328">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/helion/2026-04-04/69b45c133b74eb1e2c819503/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/helion/2026-04-04/69b45c133b74eb1e2c819503/resume.md")</f>
+        <f>HYPERLINK("by_company/helion/2026-04-04/69b45c133b74eb1e2c819503/resume.md","data/deliverables/resume_portfolio/by_company/helion/2026-04-04/69b45c133b74eb1e2c819503/resume.md")</f>
       </c>
       <c r="Q328"/>
       <c r="R328">
@@ -21165,7 +21165,7 @@
         </is>
       </c>
       <c r="P330">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/vulcan-materials-company/2026-04-04/69c918771818a24cd84d9876/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/vulcan-materials-company/2026-04-04/69c918771818a24cd84d9876/resume.md")</f>
+        <f>HYPERLINK("by_company/vulcan-materials-company/2026-04-04/69c918771818a24cd84d9876/resume.md","data/deliverables/resume_portfolio/by_company/vulcan-materials-company/2026-04-04/69c918771818a24cd84d9876/resume.md")</f>
       </c>
       <c r="Q330"/>
       <c r="R330">
@@ -21231,7 +21231,7 @@
         </is>
       </c>
       <c r="P331">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/coinbase/2026-04-04/69976de0ce78e77b4fdbc4d7/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/coinbase/2026-04-04/69976de0ce78e77b4fdbc4d7/resume.md")</f>
+        <f>HYPERLINK("by_company/coinbase/2026-04-04/69976de0ce78e77b4fdbc4d7/resume.md","data/deliverables/resume_portfolio/by_company/coinbase/2026-04-04/69976de0ce78e77b4fdbc4d7/resume.md")</f>
       </c>
       <c r="Q331"/>
       <c r="R331">
@@ -21297,7 +21297,7 @@
         </is>
       </c>
       <c r="P332">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/perplexity/2026-04-04/69469b187d506e3808f1ef06/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/perplexity/2026-04-04/69469b187d506e3808f1ef06/resume.md")</f>
+        <f>HYPERLINK("by_company/perplexity/2026-04-04/69469b187d506e3808f1ef06/resume.md","data/deliverables/resume_portfolio/by_company/perplexity/2026-04-04/69469b187d506e3808f1ef06/resume.md")</f>
       </c>
       <c r="Q332"/>
       <c r="R332">
@@ -21363,7 +21363,7 @@
         </is>
       </c>
       <c r="P333">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fireblocks/2026-04-04/6997741fce78e77b4fdbcb82/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fireblocks/2026-04-04/6997741fce78e77b4fdbcb82/resume.md")</f>
+        <f>HYPERLINK("by_company/fireblocks/2026-04-04/6997741fce78e77b4fdbcb82/resume.md","data/deliverables/resume_portfolio/by_company/fireblocks/2026-04-04/6997741fce78e77b4fdbcb82/resume.md")</f>
       </c>
       <c r="Q333"/>
       <c r="R333">
@@ -21429,7 +21429,7 @@
         </is>
       </c>
       <c r="P334">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mercari-us/2026-04-04/69c2df1794007a2195dee428/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mercari-us/2026-04-04/69c2df1794007a2195dee428/resume.md")</f>
+        <f>HYPERLINK("by_company/mercari-us/2026-04-04/69c2df1794007a2195dee428/resume.md","data/deliverables/resume_portfolio/by_company/mercari-us/2026-04-04/69c2df1794007a2195dee428/resume.md")</f>
       </c>
       <c r="Q334"/>
       <c r="R334">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="P336">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mccarthy-holdings-inc/2026-04-04/697d28d83f57a3356966e7e4/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mccarthy-holdings-inc/2026-04-04/697d28d83f57a3356966e7e4/resume.md")</f>
+        <f>HYPERLINK("by_company/mccarthy-holdings-inc/2026-04-04/697d28d83f57a3356966e7e4/resume.md","data/deliverables/resume_portfolio/by_company/mccarthy-holdings-inc/2026-04-04/697d28d83f57a3356966e7e4/resume.md")</f>
       </c>
       <c r="Q336"/>
       <c r="R336">
@@ -21735,7 +21735,7 @@
         </is>
       </c>
       <c r="P339">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fm/2026-04-04/69b45cd13b74eb1e2c819632/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fm/2026-04-04/69b45cd13b74eb1e2c819632/resume.md")</f>
+        <f>HYPERLINK("by_company/fm/2026-04-04/69b45cd13b74eb1e2c819632/resume.md","data/deliverables/resume_portfolio/by_company/fm/2026-04-04/69b45cd13b74eb1e2c819632/resume.md")</f>
       </c>
       <c r="Q339"/>
       <c r="R339">
@@ -21801,7 +21801,7 @@
         </is>
       </c>
       <c r="P340">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/notion/2026-04-04/6926667a27bf2f41a2c45d86/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/notion/2026-04-04/6926667a27bf2f41a2c45d86/resume.md")</f>
+        <f>HYPERLINK("by_company/notion/2026-04-04/6926667a27bf2f41a2c45d86/resume.md","data/deliverables/resume_portfolio/by_company/notion/2026-04-04/6926667a27bf2f41a2c45d86/resume.md")</f>
       </c>
       <c r="Q340"/>
       <c r="R340">
@@ -21925,7 +21925,7 @@
         </is>
       </c>
       <c r="P342">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/edwards-lifesciences/2026-04-04/69a276990da45516f16bc595/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/edwards-lifesciences/2026-04-04/69a276990da45516f16bc595/resume.md")</f>
+        <f>HYPERLINK("by_company/edwards-lifesciences/2026-04-04/69a276990da45516f16bc595/resume.md","data/deliverables/resume_portfolio/by_company/edwards-lifesciences/2026-04-04/69a276990da45516f16bc595/resume.md")</f>
       </c>
       <c r="Q342"/>
       <c r="R342">
@@ -22115,7 +22115,7 @@
         </is>
       </c>
       <c r="P345">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/openai/2026-04-04/6960242d7ebc25398eb61402/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/openai/2026-04-04/6960242d7ebc25398eb61402/resume.md")</f>
+        <f>HYPERLINK("by_company/openai/2026-04-04/6960242d7ebc25398eb61402/resume.md","data/deliverables/resume_portfolio/by_company/openai/2026-04-04/6960242d7ebc25398eb61402/resume.md")</f>
       </c>
       <c r="Q345"/>
       <c r="R345">
@@ -22181,7 +22181,7 @@
         </is>
       </c>
       <c r="P346">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/betterup/2026-04-04/698fb0e20cc8ea15f1da4a50/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/betterup/2026-04-04/698fb0e20cc8ea15f1da4a50/resume.md")</f>
+        <f>HYPERLINK("by_company/betterup/2026-04-04/698fb0e20cc8ea15f1da4a50/resume.md","data/deliverables/resume_portfolio/by_company/betterup/2026-04-04/698fb0e20cc8ea15f1da4a50/resume.md")</f>
       </c>
       <c r="Q346"/>
       <c r="R346">
@@ -22311,7 +22311,7 @@
         </is>
       </c>
       <c r="P348">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/western-governors-university/2026-04-04/69d1107454f00230c6d183df/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/western-governors-university/2026-04-04/69d1107454f00230c6d183df/resume.md")</f>
+        <f>HYPERLINK("by_company/western-governors-university/2026-04-04/69d1107454f00230c6d183df/resume.md","data/deliverables/resume_portfolio/by_company/western-governors-university/2026-04-04/69d1107454f00230c6d183df/resume.md")</f>
       </c>
       <c r="Q348"/>
       <c r="R348">
@@ -22443,7 +22443,7 @@
         </is>
       </c>
       <c r="P350">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/waymo/2026-04-04/6998f2d681476f6176b15d0b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/waymo/2026-04-04/6998f2d681476f6176b15d0b/resume.md")</f>
+        <f>HYPERLINK("by_company/waymo/2026-04-04/6998f2d681476f6176b15d0b/resume.md","data/deliverables/resume_portfolio/by_company/waymo/2026-04-04/6998f2d681476f6176b15d0b/resume.md")</f>
       </c>
       <c r="Q350"/>
       <c r="R350">
@@ -22633,7 +22633,7 @@
         </is>
       </c>
       <c r="P353">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/waymo/2026-04-04/69b47ca73b74eb1e2c81d2c4/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/waymo/2026-04-04/69b47ca73b74eb1e2c81d2c4/resume.md")</f>
+        <f>HYPERLINK("by_company/waymo/2026-04-04/69b47ca73b74eb1e2c81d2c4/resume.md","data/deliverables/resume_portfolio/by_company/waymo/2026-04-04/69b47ca73b74eb1e2c81d2c4/resume.md")</f>
       </c>
       <c r="Q353"/>
       <c r="R353">
@@ -22699,7 +22699,7 @@
         </is>
       </c>
       <c r="P354">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/baker-tilly-us/2026-04-04/69b4714f5697383741394881/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/baker-tilly-us/2026-04-04/69b4714f5697383741394881/resume.md")</f>
+        <f>HYPERLINK("by_company/baker-tilly-us/2026-04-04/69b4714f5697383741394881/resume.md","data/deliverables/resume_portfolio/by_company/baker-tilly-us/2026-04-04/69b4714f5697383741394881/resume.md")</f>
       </c>
       <c r="Q354"/>
       <c r="R354">
@@ -22831,7 +22831,7 @@
         </is>
       </c>
       <c r="P356">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/waymo/2026-04-04/69993ed9e0bddb6acac8578f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/waymo/2026-04-04/69993ed9e0bddb6acac8578f/resume.md")</f>
+        <f>HYPERLINK("by_company/waymo/2026-04-04/69993ed9e0bddb6acac8578f/resume.md","data/deliverables/resume_portfolio/by_company/waymo/2026-04-04/69993ed9e0bddb6acac8578f/resume.md")</f>
       </c>
       <c r="Q356"/>
       <c r="R356">
@@ -22905,7 +22905,7 @@
         </is>
       </c>
       <c r="P357">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-04/689c195979a9f9666253640d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-04/689c195979a9f9666253640d/resume.md")</f>
+        <f>HYPERLINK("by_company/applied-intuition/2026-04-04/689c195979a9f9666253640d/resume.md","data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-04/689c195979a9f9666253640d/resume.md")</f>
       </c>
       <c r="Q357"/>
       <c r="R357">
@@ -23029,7 +23029,7 @@
         </is>
       </c>
       <c r="P359">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intuit/2026-04-04/69d1214ecdb525785fbb098a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intuit/2026-04-04/69d1214ecdb525785fbb098a/resume.md")</f>
+        <f>HYPERLINK("by_company/intuit/2026-04-04/69d1214ecdb525785fbb098a/resume.md","data/deliverables/resume_portfolio/by_company/intuit/2026-04-04/69d1214ecdb525785fbb098a/resume.md")</f>
       </c>
       <c r="Q359"/>
       <c r="R359">
@@ -23153,7 +23153,7 @@
         </is>
       </c>
       <c r="P361">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-04/67ee3a40d1d82e0181df716b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-04/67ee3a40d1d82e0181df716b/resume.md")</f>
+        <f>HYPERLINK("by_company/applied-intuition/2026-04-04/67ee3a40d1d82e0181df716b/resume.md","data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-04/67ee3a40d1d82e0181df716b/resume.md")</f>
       </c>
       <c r="Q361"/>
       <c r="R361">
@@ -23219,7 +23219,7 @@
         </is>
       </c>
       <c r="P362">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-04/69d10b2e891d7b11cfce1849/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-04/69d10b2e891d7b11cfce1849/resume.md")</f>
+        <f>HYPERLINK("by_company/microsoft/2026-04-04/69d10b2e891d7b11cfce1849/resume.md","data/deliverables/resume_portfolio/by_company/microsoft/2026-04-04/69d10b2e891d7b11cfce1849/resume.md")</f>
       </c>
       <c r="Q362"/>
       <c r="R362">
@@ -23401,7 +23401,7 @@
         </is>
       </c>
       <c r="P365">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-04/69d10affcdb525785fbb063b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-04/69d10affcdb525785fbb063b/resume.md")</f>
+        <f>HYPERLINK("by_company/microsoft/2026-04-04/69d10affcdb525785fbb063b/resume.md","data/deliverables/resume_portfolio/by_company/microsoft/2026-04-04/69d10affcdb525785fbb063b/resume.md")</f>
       </c>
       <c r="Q365"/>
       <c r="R365">
@@ -23525,7 +23525,7 @@
         </is>
       </c>
       <c r="P367">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cognition/2026-04-04/692baeac4c474121999ce0a1/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cognition/2026-04-04/692baeac4c474121999ce0a1/resume.md")</f>
+        <f>HYPERLINK("by_company/cognition/2026-04-04/692baeac4c474121999ce0a1/resume.md","data/deliverables/resume_portfolio/by_company/cognition/2026-04-04/692baeac4c474121999ce0a1/resume.md")</f>
       </c>
       <c r="Q367"/>
       <c r="R367">
@@ -23591,7 +23591,7 @@
         </is>
       </c>
       <c r="P368">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-04/68cd5f0ce23def7af55b9117/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-04/68cd5f0ce23def7af55b9117/resume.md")</f>
+        <f>HYPERLINK("by_company/applied-intuition/2026-04-04/68cd5f0ce23def7af55b9117/resume.md","data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-04/68cd5f0ce23def7af55b9117/resume.md")</f>
       </c>
       <c r="Q368"/>
       <c r="R368">
@@ -23789,7 +23789,7 @@
         </is>
       </c>
       <c r="P371">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cleo/2026-04-04/697d2e7e3f57a3356966f6de/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cleo/2026-04-04/697d2e7e3f57a3356966f6de/resume.md")</f>
+        <f>HYPERLINK("by_company/cleo/2026-04-04/697d2e7e3f57a3356966f6de/resume.md","data/deliverables/resume_portfolio/by_company/cleo/2026-04-04/697d2e7e3f57a3356966f6de/resume.md")</f>
       </c>
       <c r="Q371"/>
       <c r="R371">
@@ -23921,7 +23921,7 @@
         </is>
       </c>
       <c r="P373">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/veterans-united-home-loans/2026-04-04/69a3bdb6b600907a9629bd6d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/veterans-united-home-loans/2026-04-04/69a3bdb6b600907a9629bd6d/resume.md")</f>
+        <f>HYPERLINK("by_company/veterans-united-home-loans/2026-04-04/69a3bdb6b600907a9629bd6d/resume.md","data/deliverables/resume_portfolio/by_company/veterans-united-home-loans/2026-04-04/69a3bdb6b600907a9629bd6d/resume.md")</f>
       </c>
       <c r="Q373"/>
       <c r="R373">
@@ -23987,7 +23987,7 @@
         </is>
       </c>
       <c r="P374">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cargurus/2026-04-04/69435a3c50bbaf76505539ff/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cargurus/2026-04-04/69435a3c50bbaf76505539ff/resume.md")</f>
+        <f>HYPERLINK("by_company/cargurus/2026-04-04/69435a3c50bbaf76505539ff/resume.md","data/deliverables/resume_portfolio/by_company/cargurus/2026-04-04/69435a3c50bbaf76505539ff/resume.md")</f>
       </c>
       <c r="Q374"/>
       <c r="R374">
@@ -24111,7 +24111,7 @@
         </is>
       </c>
       <c r="P376">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/komodo-health/2026-04-04/69600c33a1bbea1d9a7ad533/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/komodo-health/2026-04-04/69600c33a1bbea1d9a7ad533/resume.md")</f>
+        <f>HYPERLINK("by_company/komodo-health/2026-04-04/69600c33a1bbea1d9a7ad533/resume.md","data/deliverables/resume_portfolio/by_company/komodo-health/2026-04-04/69600c33a1bbea1d9a7ad533/resume.md")</f>
       </c>
       <c r="Q376"/>
       <c r="R376">
@@ -24235,7 +24235,7 @@
         </is>
       </c>
       <c r="P378">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/m3-usa/2026-04-04/69b46cad06c1ba00c545da43/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/m3-usa/2026-04-04/69b46cad06c1ba00c545da43/resume.md")</f>
+        <f>HYPERLINK("by_company/m3-usa/2026-04-04/69b46cad06c1ba00c545da43/resume.md","data/deliverables/resume_portfolio/by_company/m3-usa/2026-04-04/69b46cad06c1ba00c545da43/resume.md")</f>
       </c>
       <c r="Q378"/>
       <c r="R378">
@@ -24301,7 +24301,7 @@
         </is>
       </c>
       <c r="P379">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/neuralink/2026-04-04/68cc48387342c7623ae6207b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/neuralink/2026-04-04/68cc48387342c7623ae6207b/resume.md")</f>
+        <f>HYPERLINK("by_company/neuralink/2026-04-04/68cc48387342c7623ae6207b/resume.md","data/deliverables/resume_portfolio/by_company/neuralink/2026-04-04/68cc48387342c7623ae6207b/resume.md")</f>
       </c>
       <c r="Q379"/>
       <c r="R379">
@@ -24425,7 +24425,7 @@
         </is>
       </c>
       <c r="P381">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/reddit-inc/2026-04-04/69af49ca749500645093ccfe/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/reddit-inc/2026-04-04/69af49ca749500645093ccfe/resume.md")</f>
+        <f>HYPERLINK("by_company/reddit-inc/2026-04-04/69af49ca749500645093ccfe/resume.md","data/deliverables/resume_portfolio/by_company/reddit-inc/2026-04-04/69af49ca749500645093ccfe/resume.md")</f>
       </c>
       <c r="Q381"/>
       <c r="R381">
@@ -24607,7 +24607,7 @@
         </is>
       </c>
       <c r="P384">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kla/2026-04-04/6997d94381476f6176b0108a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kla/2026-04-04/6997d94381476f6176b0108a/resume.md")</f>
+        <f>HYPERLINK("by_company/kla/2026-04-04/6997d94381476f6176b0108a/resume.md","data/deliverables/resume_portfolio/by_company/kla/2026-04-04/6997d94381476f6176b0108a/resume.md")</f>
       </c>
       <c r="Q384"/>
       <c r="R384">
@@ -24673,7 +24673,7 @@
         </is>
       </c>
       <c r="P385">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-04/69d100ef891d7b11cfce12ba/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-04/69d100ef891d7b11cfce12ba/resume.md")</f>
+        <f>HYPERLINK("by_company/ss-c-technologies/2026-04-04/69d100ef891d7b11cfce12ba/resume.md","data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-04/69d100ef891d7b11cfce12ba/resume.md")</f>
       </c>
       <c r="Q385"/>
       <c r="R385">
@@ -24747,7 +24747,7 @@
         </is>
       </c>
       <c r="P386">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/verkada/2026-04-04/68b5dc29f4e41a61efd91631/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/verkada/2026-04-04/68b5dc29f4e41a61efd91631/resume.md")</f>
+        <f>HYPERLINK("by_company/verkada/2026-04-04/68b5dc29f4e41a61efd91631/resume.md","data/deliverables/resume_portfolio/by_company/verkada/2026-04-04/68b5dc29f4e41a61efd91631/resume.md")</f>
       </c>
       <c r="Q386"/>
       <c r="R386">
@@ -24813,7 +24813,7 @@
         </is>
       </c>
       <c r="P387">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/siemens-energy/2026-04-04/69b190c2548f140066e764c8/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/siemens-energy/2026-04-04/69b190c2548f140066e764c8/resume.md")</f>
+        <f>HYPERLINK("by_company/siemens-energy/2026-04-04/69b190c2548f140066e764c8/resume.md","data/deliverables/resume_portfolio/by_company/siemens-energy/2026-04-04/69b190c2548f140066e764c8/resume.md")</f>
       </c>
       <c r="Q387"/>
       <c r="R387">
@@ -24879,7 +24879,7 @@
         </is>
       </c>
       <c r="P388">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cisco/2026-04-04/69d100c1cdb525785fbafdfe/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cisco/2026-04-04/69d100c1cdb525785fbafdfe/resume.md")</f>
+        <f>HYPERLINK("by_company/cisco/2026-04-04/69d100c1cdb525785fbafdfe/resume.md","data/deliverables/resume_portfolio/by_company/cisco/2026-04-04/69d100c1cdb525785fbafdfe/resume.md")</f>
       </c>
       <c r="Q388"/>
       <c r="R388">
@@ -24945,7 +24945,7 @@
         </is>
       </c>
       <c r="P389">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/oscilar/2026-04-04/69a71e892672cb0acb4b8b43/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/oscilar/2026-04-04/69a71e892672cb0acb4b8b43/resume.md")</f>
+        <f>HYPERLINK("by_company/oscilar/2026-04-04/69a71e892672cb0acb4b8b43/resume.md","data/deliverables/resume_portfolio/by_company/oscilar/2026-04-04/69a71e892672cb0acb4b8b43/resume.md")</f>
       </c>
       <c r="Q389"/>
       <c r="R389">
@@ -25011,7 +25011,7 @@
         </is>
       </c>
       <c r="P390">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cvs-health/2026-04-04/69d0ff2a0b098b7a6707f1b6/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cvs-health/2026-04-04/69d0ff2a0b098b7a6707f1b6/resume.md")</f>
+        <f>HYPERLINK("by_company/cvs-health/2026-04-04/69d0ff2a0b098b7a6707f1b6/resume.md","data/deliverables/resume_portfolio/by_company/cvs-health/2026-04-04/69d0ff2a0b098b7a6707f1b6/resume.md")</f>
       </c>
       <c r="Q390"/>
       <c r="R390">
@@ -25077,7 +25077,7 @@
         </is>
       </c>
       <c r="P391">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-04/69d0ff1554f00230c6d17d6a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-04/69d0ff1554f00230c6d17d6a/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon-web-services-aws/2026-04-04/69d0ff1554f00230c6d17d6a/resume.md","data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-04/69d0ff1554f00230c6d17d6a/resume.md")</f>
       </c>
       <c r="Q391"/>
       <c r="R391">
@@ -25325,7 +25325,7 @@
         </is>
       </c>
       <c r="P395">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nuro/2026-04-04/6997d0d8e0bddb6acac69ae5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nuro/2026-04-04/6997d0d8e0bddb6acac69ae5/resume.md")</f>
+        <f>HYPERLINK("by_company/nuro/2026-04-04/6997d0d8e0bddb6acac69ae5/resume.md","data/deliverables/resume_portfolio/by_company/nuro/2026-04-04/6997d0d8e0bddb6acac69ae5/resume.md")</f>
       </c>
       <c r="Q395"/>
       <c r="R395">
@@ -25391,7 +25391,7 @@
         </is>
       </c>
       <c r="P396">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/lincare/2026-04-04/69d0ee14891d7b11cfce0d6b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/lincare/2026-04-04/69d0ee14891d7b11cfce0d6b/resume.md")</f>
+        <f>HYPERLINK("by_company/lincare/2026-04-04/69d0ee14891d7b11cfce0d6b/resume.md","data/deliverables/resume_portfolio/by_company/lincare/2026-04-04/69d0ee14891d7b11cfce0d6b/resume.md")</f>
       </c>
       <c r="Q396"/>
       <c r="R396">
@@ -25457,7 +25457,7 @@
         </is>
       </c>
       <c r="P397">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tiktok/2026-04-04/6924f47f38cd5478a8d6088f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tiktok/2026-04-04/6924f47f38cd5478a8d6088f/resume.md")</f>
+        <f>HYPERLINK("by_company/tiktok/2026-04-04/6924f47f38cd5478a8d6088f/resume.md","data/deliverables/resume_portfolio/by_company/tiktok/2026-04-04/6924f47f38cd5478a8d6088f/resume.md")</f>
       </c>
       <c r="Q397"/>
       <c r="R397">
@@ -25523,7 +25523,7 @@
         </is>
       </c>
       <c r="P398">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/medpace/2026-04-04/69604aaba1bbea1d9a7b2e09/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/medpace/2026-04-04/69604aaba1bbea1d9a7b2e09/resume.md")</f>
+        <f>HYPERLINK("by_company/medpace/2026-04-04/69604aaba1bbea1d9a7b2e09/resume.md","data/deliverables/resume_portfolio/by_company/medpace/2026-04-04/69604aaba1bbea1d9a7b2e09/resume.md")</f>
       </c>
       <c r="Q398"/>
       <c r="R398">
@@ -25589,7 +25589,7 @@
         </is>
       </c>
       <c r="P399">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/origami-risk/2026-04-04/69b4ebc33b74eb1e2c8269c2/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/origami-risk/2026-04-04/69b4ebc33b74eb1e2c8269c2/resume.md")</f>
+        <f>HYPERLINK("by_company/origami-risk/2026-04-04/69b4ebc33b74eb1e2c8269c2/resume.md","data/deliverables/resume_portfolio/by_company/origami-risk/2026-04-04/69b4ebc33b74eb1e2c8269c2/resume.md")</f>
       </c>
       <c r="Q399"/>
       <c r="R399">
@@ -25655,7 +25655,7 @@
         </is>
       </c>
       <c r="P400">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mercury-insurance/2026-04-04/697d6be43f57a33569675193/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mercury-insurance/2026-04-04/697d6be43f57a33569675193/resume.md")</f>
+        <f>HYPERLINK("by_company/mercury-insurance/2026-04-04/697d6be43f57a33569675193/resume.md","data/deliverables/resume_portfolio/by_company/mercury-insurance/2026-04-04/697d6be43f57a33569675193/resume.md")</f>
       </c>
       <c r="Q400"/>
       <c r="R400">
@@ -25721,7 +25721,7 @@
         </is>
       </c>
       <c r="P401">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/medpace/2026-04-04/6960462aa112b402660f13a3/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/medpace/2026-04-04/6960462aa112b402660f13a3/resume.md")</f>
+        <f>HYPERLINK("by_company/medpace/2026-04-04/6960462aa112b402660f13a3/resume.md","data/deliverables/resume_portfolio/by_company/medpace/2026-04-04/6960462aa112b402660f13a3/resume.md")</f>
       </c>
       <c r="Q401"/>
       <c r="R401">
@@ -25787,7 +25787,7 @@
         </is>
       </c>
       <c r="P402">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/stubhub/2026-04-04/69991e67ce78e77b4fddc635/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/stubhub/2026-04-04/69991e67ce78e77b4fddc635/resume.md")</f>
+        <f>HYPERLINK("by_company/stubhub/2026-04-04/69991e67ce78e77b4fddc635/resume.md","data/deliverables/resume_portfolio/by_company/stubhub/2026-04-04/69991e67ce78e77b4fddc635/resume.md")</f>
       </c>
       <c r="Q402"/>
       <c r="R402">
@@ -25975,7 +25975,7 @@
         </is>
       </c>
       <c r="P405">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mercury-insurance/2026-04-04/69743267206da320f49e535a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mercury-insurance/2026-04-04/69743267206da320f49e535a/resume.md")</f>
+        <f>HYPERLINK("by_company/mercury-insurance/2026-04-04/69743267206da320f49e535a/resume.md","data/deliverables/resume_portfolio/by_company/mercury-insurance/2026-04-04/69743267206da320f49e535a/resume.md")</f>
       </c>
       <c r="Q405"/>
       <c r="R405">
@@ -26041,7 +26041,7 @@
         </is>
       </c>
       <c r="P406">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-04/6998f6e581476f6176b163b2/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-04/6998f6e581476f6176b163b2/resume.md")</f>
+        <f>HYPERLINK("by_company/paypal/2026-04-04/6998f6e581476f6176b163b2/resume.md","data/deliverables/resume_portfolio/by_company/paypal/2026-04-04/6998f6e581476f6176b163b2/resume.md")</f>
       </c>
       <c r="Q406"/>
       <c r="R406">
@@ -26173,7 +26173,7 @@
         </is>
       </c>
       <c r="P408">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-04/6998fa1c81476f6176b1692e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-04/6998fa1c81476f6176b1692e/resume.md")</f>
+        <f>HYPERLINK("by_company/paypal/2026-04-04/6998fa1c81476f6176b1692e/resume.md","data/deliverables/resume_portfolio/by_company/paypal/2026-04-04/6998fa1c81476f6176b1692e/resume.md")</f>
       </c>
       <c r="Q408"/>
       <c r="R408">
@@ -26427,7 +26427,7 @@
         </is>
       </c>
       <c r="P412">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mercury-insurance/2026-04-04/69b6438d56973837413b8622/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mercury-insurance/2026-04-04/69b6438d56973837413b8622/resume.md")</f>
+        <f>HYPERLINK("by_company/mercury-insurance/2026-04-04/69b6438d56973837413b8622/resume.md","data/deliverables/resume_portfolio/by_company/mercury-insurance/2026-04-04/69b6438d56973837413b8622/resume.md")</f>
       </c>
       <c r="Q412"/>
       <c r="R412">
@@ -26493,7 +26493,7 @@
         </is>
       </c>
       <c r="P413">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/84-51/2026-04-04/69b4c322569738374139b2e1/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/84-51/2026-04-04/69b4c322569738374139b2e1/resume.md")</f>
+        <f>HYPERLINK("by_company/84-51/2026-04-04/69b4c322569738374139b2e1/resume.md","data/deliverables/resume_portfolio/by_company/84-51/2026-04-04/69b4c322569738374139b2e1/resume.md")</f>
       </c>
       <c r="Q413"/>
       <c r="R413">
@@ -26559,7 +26559,7 @@
         </is>
       </c>
       <c r="P414">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-04/69bf74dd7798f73e35e44625/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-04/69bf74dd7798f73e35e44625/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-04/69bf74dd7798f73e35e44625/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-04/69bf74dd7798f73e35e44625/resume.md")</f>
       </c>
       <c r="Q414"/>
       <c r="R414">
@@ -26805,7 +26805,7 @@
         </is>
       </c>
       <c r="P418">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nelnet/2026-04-04/69965483ce78e77b4fda5856/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nelnet/2026-04-04/69965483ce78e77b4fda5856/resume.md")</f>
+        <f>HYPERLINK("by_company/nelnet/2026-04-04/69965483ce78e77b4fda5856/resume.md","data/deliverables/resume_portfolio/by_company/nelnet/2026-04-04/69965483ce78e77b4fda5856/resume.md")</f>
       </c>
       <c r="Q418"/>
       <c r="R418">
@@ -26871,7 +26871,7 @@
         </is>
       </c>
       <c r="P419">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-04/6961d3e4f3f4cd132506d312/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-04/6961d3e4f3f4cd132506d312/resume.md")</f>
+        <f>HYPERLINK("by_company/adobe/2026-04-04/6961d3e4f3f4cd132506d312/resume.md","data/deliverables/resume_portfolio/by_company/adobe/2026-04-04/6961d3e4f3f4cd132506d312/resume.md")</f>
       </c>
       <c r="Q419"/>
       <c r="R419">
@@ -26937,7 +26937,7 @@
         </is>
       </c>
       <c r="P420">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-04/69b3e4a006c1ba00c5450b57/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-04/69b3e4a006c1ba00c5450b57/resume.md")</f>
+        <f>HYPERLINK("by_company/adobe/2026-04-04/69b3e4a006c1ba00c5450b57/resume.md","data/deliverables/resume_portfolio/by_company/adobe/2026-04-04/69b3e4a006c1ba00c5450b57/resume.md")</f>
       </c>
       <c r="Q420"/>
       <c r="R420">
@@ -27069,7 +27069,7 @@
         </is>
       </c>
       <c r="P422">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/meltwater/2026-04-04/69d0a0f5891d7b11cfcdd7d1/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/meltwater/2026-04-04/69d0a0f5891d7b11cfcdd7d1/resume.md")</f>
+        <f>HYPERLINK("by_company/meltwater/2026-04-04/69d0a0f5891d7b11cfcdd7d1/resume.md","data/deliverables/resume_portfolio/by_company/meltwater/2026-04-04/69d0a0f5891d7b11cfcdd7d1/resume.md")</f>
       </c>
       <c r="Q422"/>
       <c r="R422">
@@ -27263,7 +27263,7 @@
         </is>
       </c>
       <c r="P425">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nvidia/2026-04-03/69d084b954f00230c6d12eef/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nvidia/2026-04-03/69d084b954f00230c6d12eef/resume.md")</f>
+        <f>HYPERLINK("by_company/nvidia/2026-04-03/69d084b954f00230c6d12eef/resume.md","data/deliverables/resume_portfolio/by_company/nvidia/2026-04-03/69d084b954f00230c6d12eef/resume.md")</f>
       </c>
       <c r="Q425"/>
       <c r="R425">
@@ -27337,7 +27337,7 @@
         </is>
       </c>
       <c r="P426">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nvidia/2026-04-03/69d08495cdb525785fbab3c5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nvidia/2026-04-03/69d08495cdb525785fbab3c5/resume.md")</f>
+        <f>HYPERLINK("by_company/nvidia/2026-04-03/69d08495cdb525785fbab3c5/resume.md","data/deliverables/resume_portfolio/by_company/nvidia/2026-04-03/69d08495cdb525785fbab3c5/resume.md")</f>
       </c>
       <c r="Q426"/>
       <c r="R426">
@@ -27519,7 +27519,7 @@
         </is>
       </c>
       <c r="P429">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/parafin/2026-04-03/69d0831d54f00230c6d12c87/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/parafin/2026-04-03/69d0831d54f00230c6d12c87/resume.md")</f>
+        <f>HYPERLINK("by_company/parafin/2026-04-03/69d0831d54f00230c6d12c87/resume.md","data/deliverables/resume_portfolio/by_company/parafin/2026-04-03/69d0831d54f00230c6d12c87/resume.md")</f>
       </c>
       <c r="Q429"/>
       <c r="R429">
@@ -27585,7 +27585,7 @@
         </is>
       </c>
       <c r="P430">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/lennar/2026-04-03/69d08006cdb525785fbab0eb/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/lennar/2026-04-03/69d08006cdb525785fbab0eb/resume.md")</f>
+        <f>HYPERLINK("by_company/lennar/2026-04-03/69d08006cdb525785fbab0eb/resume.md","data/deliverables/resume_portfolio/by_company/lennar/2026-04-03/69d08006cdb525785fbab0eb/resume.md")</f>
       </c>
       <c r="Q430"/>
       <c r="R430">
@@ -27651,7 +27651,7 @@
         </is>
       </c>
       <c r="P431">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/apple/2026-04-03/69d07fb3cfdc6132f943bfdf/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/apple/2026-04-03/69d07fb3cfdc6132f943bfdf/resume.md")</f>
+        <f>HYPERLINK("by_company/apple/2026-04-03/69d07fb3cfdc6132f943bfdf/resume.md","data/deliverables/resume_portfolio/by_company/apple/2026-04-03/69d07fb3cfdc6132f943bfdf/resume.md")</f>
       </c>
       <c r="Q431"/>
       <c r="R431">
@@ -27717,7 +27717,7 @@
         </is>
       </c>
       <c r="P432">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/apple/2026-04-03/69d07fb3cfdc6132f943bfde/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/apple/2026-04-03/69d07fb3cfdc6132f943bfde/resume.md")</f>
+        <f>HYPERLINK("by_company/apple/2026-04-03/69d07fb3cfdc6132f943bfde/resume.md","data/deliverables/resume_portfolio/by_company/apple/2026-04-03/69d07fb3cfdc6132f943bfde/resume.md")</f>
       </c>
       <c r="Q432"/>
       <c r="R432">
@@ -27849,7 +27849,7 @@
         </is>
       </c>
       <c r="P434">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jam-city/2026-04-03/69d07cf7cfdc6132f943bf33/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jam-city/2026-04-03/69d07cf7cfdc6132f943bf33/resume.md")</f>
+        <f>HYPERLINK("by_company/jam-city/2026-04-03/69d07cf7cfdc6132f943bf33/resume.md","data/deliverables/resume_portfolio/by_company/jam-city/2026-04-03/69d07cf7cfdc6132f943bf33/resume.md")</f>
       </c>
       <c r="Q434"/>
       <c r="R434">
@@ -27973,7 +27973,7 @@
         </is>
       </c>
       <c r="P436">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cisco/2026-04-03/69d07b90cfdc6132f943be1d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cisco/2026-04-03/69d07b90cfdc6132f943be1d/resume.md")</f>
+        <f>HYPERLINK("by_company/cisco/2026-04-03/69d07b90cfdc6132f943be1d/resume.md","data/deliverables/resume_portfolio/by_company/cisco/2026-04-03/69d07b90cfdc6132f943be1d/resume.md")</f>
       </c>
       <c r="Q436"/>
       <c r="R436">
@@ -28155,7 +28155,7 @@
         </is>
       </c>
       <c r="P439">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cresta/2026-04-03/684c951cba4db2b7720240a9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cresta/2026-04-03/684c951cba4db2b7720240a9/resume.md")</f>
+        <f>HYPERLINK("by_company/cresta/2026-04-03/684c951cba4db2b7720240a9/resume.md","data/deliverables/resume_portfolio/by_company/cresta/2026-04-03/684c951cba4db2b7720240a9/resume.md")</f>
       </c>
       <c r="Q439"/>
       <c r="R439">
@@ -28295,7 +28295,7 @@
         </is>
       </c>
       <c r="P441">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-03/69d075c9366bb95ba551e7fe/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-03/69d075c9366bb95ba551e7fe/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-03/69d075c9366bb95ba551e7fe/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-03/69d075c9366bb95ba551e7fe/resume.md")</f>
       </c>
       <c r="Q441"/>
       <c r="R441">
@@ -28361,7 +28361,7 @@
         </is>
       </c>
       <c r="P442">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/profound/2026-04-03/69d075bacfdc6132f943b758/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/profound/2026-04-03/69d075bacfdc6132f943b758/resume.md")</f>
+        <f>HYPERLINK("by_company/profound/2026-04-03/69d075bacfdc6132f943b758/resume.md","data/deliverables/resume_portfolio/by_company/profound/2026-04-03/69d075bacfdc6132f943b758/resume.md")</f>
       </c>
       <c r="Q442"/>
       <c r="R442">
@@ -28559,7 +28559,7 @@
         </is>
       </c>
       <c r="P445">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/booz-allen-hamilton/2026-04-03/69d0734c0b098b7a67079835/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/booz-allen-hamilton/2026-04-03/69d0734c0b098b7a67079835/resume.md")</f>
+        <f>HYPERLINK("by_company/booz-allen-hamilton/2026-04-03/69d0734c0b098b7a67079835/resume.md","data/deliverables/resume_portfolio/by_company/booz-allen-hamilton/2026-04-03/69d0734c0b098b7a67079835/resume.md")</f>
       </c>
       <c r="Q445"/>
       <c r="R445">
@@ -28691,7 +28691,7 @@
         </is>
       </c>
       <c r="P447">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/u-s-bank/2026-04-03/69d071e6891d7b11cfcdb7b1/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/u-s-bank/2026-04-03/69d071e6891d7b11cfcdb7b1/resume.md")</f>
+        <f>HYPERLINK("by_company/u-s-bank/2026-04-03/69d071e6891d7b11cfcdb7b1/resume.md","data/deliverables/resume_portfolio/by_company/u-s-bank/2026-04-03/69d071e6891d7b11cfcdb7b1/resume.md")</f>
       </c>
       <c r="Q447"/>
       <c r="R447">
@@ -29055,7 +29055,7 @@
         </is>
       </c>
       <c r="P453">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/extensiv/2026-04-03/69d064f2891d7b11cfcdb1dd/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/extensiv/2026-04-03/69d064f2891d7b11cfcdb1dd/resume.md")</f>
+        <f>HYPERLINK("by_company/extensiv/2026-04-03/69d064f2891d7b11cfcdb1dd/resume.md","data/deliverables/resume_portfolio/by_company/extensiv/2026-04-03/69d064f2891d7b11cfcdb1dd/resume.md")</f>
       </c>
       <c r="Q453"/>
       <c r="R453">
@@ -29179,7 +29179,7 @@
         </is>
       </c>
       <c r="P455">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/meltwater/2026-04-03/69d062a3cdb525785fbaa061/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/meltwater/2026-04-03/69d062a3cdb525785fbaa061/resume.md")</f>
+        <f>HYPERLINK("by_company/meltwater/2026-04-03/69d062a3cdb525785fbaa061/resume.md","data/deliverables/resume_portfolio/by_company/meltwater/2026-04-03/69d062a3cdb525785fbaa061/resume.md")</f>
       </c>
       <c r="Q455"/>
       <c r="R455">
@@ -29303,7 +29303,7 @@
         </is>
       </c>
       <c r="P457">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-03/69d05e6ecfdc6132f943aa06/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-03/69d05e6ecfdc6132f943aa06/resume.md")</f>
+        <f>HYPERLINK("by_company/microsoft/2026-04-03/69d05e6ecfdc6132f943aa06/resume.md","data/deliverables/resume_portfolio/by_company/microsoft/2026-04-03/69d05e6ecfdc6132f943aa06/resume.md")</f>
       </c>
       <c r="Q457"/>
       <c r="R457">
@@ -29543,7 +29543,7 @@
         </is>
       </c>
       <c r="P461">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tealium/2026-04-03/69d05a280b098b7a67078a44/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tealium/2026-04-03/69d05a280b098b7a67078a44/resume.md")</f>
+        <f>HYPERLINK("by_company/tealium/2026-04-03/69d05a280b098b7a67078a44/resume.md","data/deliverables/resume_portfolio/by_company/tealium/2026-04-03/69d05a280b098b7a67078a44/resume.md")</f>
       </c>
       <c r="Q461"/>
       <c r="R461">
@@ -29609,7 +29609,7 @@
         </is>
       </c>
       <c r="P462">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/equifax/2026-04-03/69d059d1891d7b11cfcdaba2/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/equifax/2026-04-03/69d059d1891d7b11cfcdaba2/resume.md")</f>
+        <f>HYPERLINK("by_company/equifax/2026-04-03/69d059d1891d7b11cfcdaba2/resume.md","data/deliverables/resume_portfolio/by_company/equifax/2026-04-03/69d059d1891d7b11cfcdaba2/resume.md")</f>
       </c>
       <c r="Q462"/>
       <c r="R462">
@@ -29675,7 +29675,7 @@
         </is>
       </c>
       <c r="P463">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/equifax/2026-04-03/69d059b854f00230c6d1150f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/equifax/2026-04-03/69d059b854f00230c6d1150f/resume.md")</f>
+        <f>HYPERLINK("by_company/equifax/2026-04-03/69d059b854f00230c6d1150f/resume.md","data/deliverables/resume_portfolio/by_company/equifax/2026-04-03/69d059b854f00230c6d1150f/resume.md")</f>
       </c>
       <c r="Q463"/>
       <c r="R463">
@@ -29821,7 +29821,7 @@
         </is>
       </c>
       <c r="P465">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/69d05887cfdc6132f943a843/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/69d05887cfdc6132f943a843/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon/2026-04-03/69d05887cfdc6132f943a843/resume.md","data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/69d05887cfdc6132f943a843/resume.md")</f>
       </c>
       <c r="Q465"/>
       <c r="R465">
@@ -29895,7 +29895,7 @@
         </is>
       </c>
       <c r="P466">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/simplisafe/2026-04-03/69a5dca40da45516f16e9b94/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/simplisafe/2026-04-03/69a5dca40da45516f16e9b94/resume.md")</f>
+        <f>HYPERLINK("by_company/simplisafe/2026-04-03/69a5dca40da45516f16e9b94/resume.md","data/deliverables/resume_portfolio/by_company/simplisafe/2026-04-03/69a5dca40da45516f16e9b94/resume.md")</f>
       </c>
       <c r="Q466"/>
       <c r="R466">
@@ -29961,7 +29961,7 @@
         </is>
       </c>
       <c r="P467">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/aditi-consulting/2026-04-03/69d08314cfdc6132f943c13f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/aditi-consulting/2026-04-03/69d08314cfdc6132f943c13f/resume.md")</f>
+        <f>HYPERLINK("by_company/aditi-consulting/2026-04-03/69d08314cfdc6132f943c13f/resume.md","data/deliverables/resume_portfolio/by_company/aditi-consulting/2026-04-03/69d08314cfdc6132f943c13f/resume.md")</f>
       </c>
       <c r="Q467"/>
       <c r="R467">
@@ -30027,7 +30027,7 @@
         </is>
       </c>
       <c r="P468">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-03/69d050a3cfdc6132f943a6ce/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-03/69d050a3cfdc6132f943a6ce/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon-web-services-aws/2026-04-03/69d050a3cfdc6132f943a6ce/resume.md","data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-03/69d050a3cfdc6132f943a6ce/resume.md")</f>
       </c>
       <c r="Q468"/>
       <c r="R468">
@@ -30523,7 +30523,7 @@
         </is>
       </c>
       <c r="P476">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/quest-global/2026-04-03/69d04bcc891d7b11cfcda824/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/quest-global/2026-04-03/69d04bcc891d7b11cfcda824/resume.md")</f>
+        <f>HYPERLINK("by_company/quest-global/2026-04-03/69d04bcc891d7b11cfcda824/resume.md","data/deliverables/resume_portfolio/by_company/quest-global/2026-04-03/69d04bcc891d7b11cfcda824/resume.md")</f>
       </c>
       <c r="Q476"/>
       <c r="R476">
@@ -30597,7 +30597,7 @@
         </is>
       </c>
       <c r="P477">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/zensar-technologies/2026-04-03/69d04a79cfdc6132f943a52e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/zensar-technologies/2026-04-03/69d04a79cfdc6132f943a52e/resume.md")</f>
+        <f>HYPERLINK("by_company/zensar-technologies/2026-04-03/69d04a79cfdc6132f943a52e/resume.md","data/deliverables/resume_portfolio/by_company/zensar-technologies/2026-04-03/69d04a79cfdc6132f943a52e/resume.md")</f>
       </c>
       <c r="Q477"/>
       <c r="R477">
@@ -30663,7 +30663,7 @@
         </is>
       </c>
       <c r="P478">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/unitx/2026-04-03/69d04a620b098b7a6707862b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/unitx/2026-04-03/69d04a620b098b7a6707862b/resume.md")</f>
+        <f>HYPERLINK("by_company/unitx/2026-04-03/69d04a620b098b7a6707862b/resume.md","data/deliverables/resume_portfolio/by_company/unitx/2026-04-03/69d04a620b098b7a6707862b/resume.md")</f>
       </c>
       <c r="Q478"/>
       <c r="R478">
@@ -30729,7 +30729,7 @@
         </is>
       </c>
       <c r="P479">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/magnite/2026-04-03/69d048f4366bb95ba551d5a0/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/magnite/2026-04-03/69d048f4366bb95ba551d5a0/resume.md")</f>
+        <f>HYPERLINK("by_company/magnite/2026-04-03/69d048f4366bb95ba551d5a0/resume.md","data/deliverables/resume_portfolio/by_company/magnite/2026-04-03/69d048f4366bb95ba551d5a0/resume.md")</f>
       </c>
       <c r="Q479"/>
       <c r="R479">
@@ -30795,7 +30795,7 @@
         </is>
       </c>
       <c r="P480">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/deloitte/2026-04-03/69d047d4891d7b11cfcda7a5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/deloitte/2026-04-03/69d047d4891d7b11cfcda7a5/resume.md")</f>
+        <f>HYPERLINK("by_company/deloitte/2026-04-03/69d047d4891d7b11cfcda7a5/resume.md","data/deliverables/resume_portfolio/by_company/deloitte/2026-04-03/69d047d4891d7b11cfcda7a5/resume.md")</f>
       </c>
       <c r="Q480"/>
       <c r="R480">
@@ -30919,7 +30919,7 @@
         </is>
       </c>
       <c r="P482">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/idexx/2026-04-03/69d047a4cfdc6132f943a491/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/idexx/2026-04-03/69d047a4cfdc6132f943a491/resume.md")</f>
+        <f>HYPERLINK("by_company/idexx/2026-04-03/69d047a4cfdc6132f943a491/resume.md","data/deliverables/resume_portfolio/by_company/idexx/2026-04-03/69d047a4cfdc6132f943a491/resume.md")</f>
       </c>
       <c r="Q482"/>
       <c r="R482">
@@ -30985,7 +30985,7 @@
         </is>
       </c>
       <c r="P483">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/bridge-legal/2026-04-03/69d04794cdb525785fba9546/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/bridge-legal/2026-04-03/69d04794cdb525785fba9546/resume.md")</f>
+        <f>HYPERLINK("by_company/bridge-legal/2026-04-03/69d04794cdb525785fba9546/resume.md","data/deliverables/resume_portfolio/by_company/bridge-legal/2026-04-03/69d04794cdb525785fba9546/resume.md")</f>
       </c>
       <c r="Q483"/>
       <c r="R483">
@@ -31059,7 +31059,7 @@
         </is>
       </c>
       <c r="P484">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mercury-insurance/2026-04-03/69d04708cfdc6132f943a411/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mercury-insurance/2026-04-03/69d04708cfdc6132f943a411/resume.md")</f>
+        <f>HYPERLINK("by_company/mercury-insurance/2026-04-03/69d04708cfdc6132f943a411/resume.md","data/deliverables/resume_portfolio/by_company/mercury-insurance/2026-04-03/69d04708cfdc6132f943a411/resume.md")</f>
       </c>
       <c r="Q484"/>
       <c r="R484">
@@ -31191,7 +31191,7 @@
         </is>
       </c>
       <c r="P486">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/uber/2026-04-03/69d0466d891d7b11cfcda469/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/uber/2026-04-03/69d0466d891d7b11cfcda469/resume.md")</f>
+        <f>HYPERLINK("by_company/uber/2026-04-03/69d0466d891d7b11cfcda469/resume.md","data/deliverables/resume_portfolio/by_company/uber/2026-04-03/69d0466d891d7b11cfcda469/resume.md")</f>
       </c>
       <c r="Q486"/>
       <c r="R486">
@@ -31257,7 +31257,7 @@
         </is>
       </c>
       <c r="P487">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/uber/2026-04-03/69d04662cfdc6132f943a069/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/uber/2026-04-03/69d04662cfdc6132f943a069/resume.md")</f>
+        <f>HYPERLINK("by_company/uber/2026-04-03/69d04662cfdc6132f943a069/resume.md","data/deliverables/resume_portfolio/by_company/uber/2026-04-03/69d04662cfdc6132f943a069/resume.md")</f>
       </c>
       <c r="Q487"/>
       <c r="R487">
@@ -31387,7 +31387,7 @@
         </is>
       </c>
       <c r="P489">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tata-consultancy-services/2026-04-03/69d06472cfdc6132f943b05d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tata-consultancy-services/2026-04-03/69d06472cfdc6132f943b05d/resume.md")</f>
+        <f>HYPERLINK("by_company/tata-consultancy-services/2026-04-03/69d06472cfdc6132f943b05d/resume.md","data/deliverables/resume_portfolio/by_company/tata-consultancy-services/2026-04-03/69d06472cfdc6132f943b05d/resume.md")</f>
       </c>
       <c r="Q489"/>
       <c r="R489">
@@ -31453,7 +31453,7 @@
         </is>
       </c>
       <c r="P490">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fullsteam/2026-04-03/69d0461b891d7b11cfcda1fc/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fullsteam/2026-04-03/69d0461b891d7b11cfcda1fc/resume.md")</f>
+        <f>HYPERLINK("by_company/fullsteam/2026-04-03/69d0461b891d7b11cfcda1fc/resume.md","data/deliverables/resume_portfolio/by_company/fullsteam/2026-04-03/69d0461b891d7b11cfcda1fc/resume.md")</f>
       </c>
       <c r="Q490"/>
       <c r="R490">
@@ -31519,7 +31519,7 @@
         </is>
       </c>
       <c r="P491">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-03/69d046190b098b7a67077f8c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-03/69d046190b098b7a67077f8c/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-03/69d046190b098b7a67077f8c/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-03/69d046190b098b7a67077f8c/resume.md")</f>
       </c>
       <c r="Q491"/>
       <c r="R491">
@@ -31709,7 +31709,7 @@
         </is>
       </c>
       <c r="P494">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/grid/2026-04-03/69d040ad54f00230c6d109a4/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/grid/2026-04-03/69d040ad54f00230c6d109a4/resume.md")</f>
+        <f>HYPERLINK("by_company/grid/2026-04-03/69d040ad54f00230c6d109a4/resume.md","data/deliverables/resume_portfolio/by_company/grid/2026-04-03/69d040ad54f00230c6d109a4/resume.md")</f>
       </c>
       <c r="Q494"/>
       <c r="R494">
@@ -31775,7 +31775,7 @@
         </is>
       </c>
       <c r="P495">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/university-of-kentucky/2026-04-03/69d03c2454f00230c6d107e8/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/university-of-kentucky/2026-04-03/69d03c2454f00230c6d107e8/resume.md")</f>
+        <f>HYPERLINK("by_company/university-of-kentucky/2026-04-03/69d03c2454f00230c6d107e8/resume.md","data/deliverables/resume_portfolio/by_company/university-of-kentucky/2026-04-03/69d03c2454f00230c6d107e8/resume.md")</f>
       </c>
       <c r="Q495"/>
       <c r="R495">
@@ -31841,7 +31841,7 @@
         </is>
       </c>
       <c r="P496">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/q1-technologies-inc/2026-04-03/69cdd689cfdc6132f942014f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/q1-technologies-inc/2026-04-03/69cdd689cfdc6132f942014f/resume.md")</f>
+        <f>HYPERLINK("by_company/q1-technologies-inc/2026-04-03/69cdd689cfdc6132f942014f/resume.md","data/deliverables/resume_portfolio/by_company/q1-technologies-inc/2026-04-03/69cdd689cfdc6132f942014f/resume.md")</f>
       </c>
       <c r="Q496"/>
       <c r="R496">
@@ -31907,7 +31907,7 @@
         </is>
       </c>
       <c r="P497">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/rk-infotech-llc-e-verified-company/2026-04-03/699714ab81476f6176af2ee7/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/rk-infotech-llc-e-verified-company/2026-04-03/699714ab81476f6176af2ee7/resume.md")</f>
+        <f>HYPERLINK("by_company/rk-infotech-llc-e-verified-company/2026-04-03/699714ab81476f6176af2ee7/resume.md","data/deliverables/resume_portfolio/by_company/rk-infotech-llc-e-verified-company/2026-04-03/699714ab81476f6176af2ee7/resume.md")</f>
       </c>
       <c r="Q497"/>
       <c r="R497">
@@ -31973,7 +31973,7 @@
         </is>
       </c>
       <c r="P498">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nvidia/2026-04-03/69d03718cdb525785fba8a3a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nvidia/2026-04-03/69d03718cdb525785fba8a3a/resume.md")</f>
+        <f>HYPERLINK("by_company/nvidia/2026-04-03/69d03718cdb525785fba8a3a/resume.md","data/deliverables/resume_portfolio/by_company/nvidia/2026-04-03/69d03718cdb525785fba8a3a/resume.md")</f>
       </c>
       <c r="Q498"/>
       <c r="R498">
@@ -32039,7 +32039,7 @@
         </is>
       </c>
       <c r="P499">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/analytic-partners/2026-04-03/69d0346a54f00230c6d10595/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/analytic-partners/2026-04-03/69d0346a54f00230c6d10595/resume.md")</f>
+        <f>HYPERLINK("by_company/analytic-partners/2026-04-03/69d0346a54f00230c6d10595/resume.md","data/deliverables/resume_portfolio/by_company/analytic-partners/2026-04-03/69d0346a54f00230c6d10595/resume.md")</f>
       </c>
       <c r="Q499"/>
       <c r="R499">
@@ -32105,7 +32105,7 @@
         </is>
       </c>
       <c r="P500">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fullsteam/2026-04-03/69d0345a0b098b7a67077a14/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fullsteam/2026-04-03/69d0345a0b098b7a67077a14/resume.md")</f>
+        <f>HYPERLINK("by_company/fullsteam/2026-04-03/69d0345a0b098b7a67077a14/resume.md","data/deliverables/resume_portfolio/by_company/fullsteam/2026-04-03/69d0345a0b098b7a67077a14/resume.md")</f>
       </c>
       <c r="Q500"/>
       <c r="R500">
@@ -32179,7 +32179,7 @@
         </is>
       </c>
       <c r="P501">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/honeywell/2026-04-03/69d0341a891d7b11cfcd9c30/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/honeywell/2026-04-03/69d0341a891d7b11cfcd9c30/resume.md")</f>
+        <f>HYPERLINK("by_company/honeywell/2026-04-03/69d0341a891d7b11cfcd9c30/resume.md","data/deliverables/resume_portfolio/by_company/honeywell/2026-04-03/69d0341a891d7b11cfcd9c30/resume.md")</f>
       </c>
       <c r="Q501"/>
       <c r="R501">
@@ -32245,7 +32245,7 @@
         </is>
       </c>
       <c r="P502">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fullsteam/2026-04-03/69d03409cdb525785fba898f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fullsteam/2026-04-03/69d03409cdb525785fba898f/resume.md")</f>
+        <f>HYPERLINK("by_company/fullsteam/2026-04-03/69d03409cdb525785fba898f/resume.md","data/deliverables/resume_portfolio/by_company/fullsteam/2026-04-03/69d03409cdb525785fba898f/resume.md")</f>
       </c>
       <c r="Q502"/>
       <c r="R502">
@@ -32311,7 +32311,7 @@
         </is>
       </c>
       <c r="P503">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cisco/2026-04-03/69d031cdcfdc6132f9439695/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cisco/2026-04-03/69d031cdcfdc6132f9439695/resume.md")</f>
+        <f>HYPERLINK("by_company/cisco/2026-04-03/69d031cdcfdc6132f9439695/resume.md","data/deliverables/resume_portfolio/by_company/cisco/2026-04-03/69d031cdcfdc6132f9439695/resume.md")</f>
       </c>
       <c r="Q503"/>
       <c r="R503">
@@ -32377,7 +32377,7 @@
         </is>
       </c>
       <c r="P504">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cisco/2026-04-03/69d031cdcfdc6132f9439693/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cisco/2026-04-03/69d031cdcfdc6132f9439693/resume.md")</f>
+        <f>HYPERLINK("by_company/cisco/2026-04-03/69d031cdcfdc6132f9439693/resume.md","data/deliverables/resume_portfolio/by_company/cisco/2026-04-03/69d031cdcfdc6132f9439693/resume.md")</f>
       </c>
       <c r="Q504"/>
       <c r="R504">
@@ -32443,7 +32443,7 @@
         </is>
       </c>
       <c r="P505">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/equifax/2026-04-03/69d0319f54f00230c6d1036f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/equifax/2026-04-03/69d0319f54f00230c6d1036f/resume.md")</f>
+        <f>HYPERLINK("by_company/equifax/2026-04-03/69d0319f54f00230c6d1036f/resume.md","data/deliverables/resume_portfolio/by_company/equifax/2026-04-03/69d0319f54f00230c6d1036f/resume.md")</f>
       </c>
       <c r="Q505"/>
       <c r="R505">
@@ -32625,7 +32625,7 @@
         </is>
       </c>
       <c r="P508">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gei-consultants-inc/2026-04-03/69d02a1bcfdc6132f9438e58/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gei-consultants-inc/2026-04-03/69d02a1bcfdc6132f9438e58/resume.md")</f>
+        <f>HYPERLINK("by_company/gei-consultants-inc/2026-04-03/69d02a1bcfdc6132f9438e58/resume.md","data/deliverables/resume_portfolio/by_company/gei-consultants-inc/2026-04-03/69d02a1bcfdc6132f9438e58/resume.md")</f>
       </c>
       <c r="Q508"/>
       <c r="R508">
@@ -32691,7 +32691,7 @@
         </is>
       </c>
       <c r="P509">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/coderabbit/2026-04-03/69d02a08cdb525785fba7ed5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/coderabbit/2026-04-03/69d02a08cdb525785fba7ed5/resume.md")</f>
+        <f>HYPERLINK("by_company/coderabbit/2026-04-03/69d02a08cdb525785fba7ed5/resume.md","data/deliverables/resume_portfolio/by_company/coderabbit/2026-04-03/69d02a08cdb525785fba7ed5/resume.md")</f>
       </c>
       <c r="Q509"/>
       <c r="R509">
@@ -32757,7 +32757,7 @@
         </is>
       </c>
       <c r="P510">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/equifax/2026-04-03/69d029ad0b098b7a67076d09/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/equifax/2026-04-03/69d029ad0b098b7a67076d09/resume.md")</f>
+        <f>HYPERLINK("by_company/equifax/2026-04-03/69d029ad0b098b7a67076d09/resume.md","data/deliverables/resume_portfolio/by_company/equifax/2026-04-03/69d029ad0b098b7a67076d09/resume.md")</f>
       </c>
       <c r="Q510"/>
       <c r="R510">
@@ -32881,7 +32881,7 @@
         </is>
       </c>
       <c r="P512">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ebay/2026-04-03/69d027810b098b7a67076cc3/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ebay/2026-04-03/69d027810b098b7a67076cc3/resume.md")</f>
+        <f>HYPERLINK("by_company/ebay/2026-04-03/69d027810b098b7a67076cc3/resume.md","data/deliverables/resume_portfolio/by_company/ebay/2026-04-03/69d027810b098b7a67076cc3/resume.md")</f>
       </c>
       <c r="Q512"/>
       <c r="R512">
@@ -33237,7 +33237,7 @@
         </is>
       </c>
       <c r="P518">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/wns/2026-04-03/69d0214fcfdc6132f9438798/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/wns/2026-04-03/69d0214fcfdc6132f9438798/resume.md")</f>
+        <f>HYPERLINK("by_company/wns/2026-04-03/69d0214fcfdc6132f9438798/resume.md","data/deliverables/resume_portfolio/by_company/wns/2026-04-03/69d0214fcfdc6132f9438798/resume.md")</f>
       </c>
       <c r="Q518"/>
       <c r="R518">
@@ -33361,7 +33361,7 @@
         </is>
       </c>
       <c r="P520">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/environmental-science-associates/2026-04-03/69d01ff0366bb95ba551b7ae/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/environmental-science-associates/2026-04-03/69d01ff0366bb95ba551b7ae/resume.md")</f>
+        <f>HYPERLINK("by_company/environmental-science-associates/2026-04-03/69d01ff0366bb95ba551b7ae/resume.md","data/deliverables/resume_portfolio/by_company/environmental-science-associates/2026-04-03/69d01ff0366bb95ba551b7ae/resume.md")</f>
       </c>
       <c r="Q520"/>
       <c r="R520">
@@ -33427,7 +33427,7 @@
         </is>
       </c>
       <c r="P521">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/piper-companies/2026-04-03/69d01f6ecdb525785fba7762/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/piper-companies/2026-04-03/69d01f6ecdb525785fba7762/resume.md")</f>
+        <f>HYPERLINK("by_company/piper-companies/2026-04-03/69d01f6ecdb525785fba7762/resume.md","data/deliverables/resume_portfolio/by_company/piper-companies/2026-04-03/69d01f6ecdb525785fba7762/resume.md")</f>
       </c>
       <c r="Q521"/>
       <c r="R521">
@@ -33493,7 +33493,7 @@
         </is>
       </c>
       <c r="P522">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/goldman-sachs/2026-04-03/69c8ae57aa3c2c1995e1fc81/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/goldman-sachs/2026-04-03/69c8ae57aa3c2c1995e1fc81/resume.md")</f>
+        <f>HYPERLINK("by_company/goldman-sachs/2026-04-03/69c8ae57aa3c2c1995e1fc81/resume.md","data/deliverables/resume_portfolio/by_company/goldman-sachs/2026-04-03/69c8ae57aa3c2c1995e1fc81/resume.md")</f>
       </c>
       <c r="Q522"/>
       <c r="R522">
@@ -33559,7 +33559,7 @@
         </is>
       </c>
       <c r="P523">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jerry/2026-04-03/69d01acc891d7b11cfcd89bd/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jerry/2026-04-03/69d01acc891d7b11cfcd89bd/resume.md")</f>
+        <f>HYPERLINK("by_company/jerry/2026-04-03/69d01acc891d7b11cfcd89bd/resume.md","data/deliverables/resume_portfolio/by_company/jerry/2026-04-03/69d01acc891d7b11cfcd89bd/resume.md")</f>
       </c>
       <c r="Q523"/>
       <c r="R523">
@@ -33625,7 +33625,7 @@
         </is>
       </c>
       <c r="P524">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/johnson-controls/2026-04-03/69d01979366bb95ba551b554/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/johnson-controls/2026-04-03/69d01979366bb95ba551b554/resume.md")</f>
+        <f>HYPERLINK("by_company/johnson-controls/2026-04-03/69d01979366bb95ba551b554/resume.md","data/deliverables/resume_portfolio/by_company/johnson-controls/2026-04-03/69d01979366bb95ba551b554/resume.md")</f>
       </c>
       <c r="Q524"/>
       <c r="R524">
@@ -33691,7 +33691,7 @@
         </is>
       </c>
       <c r="P525">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hyr-global-source-inc/2026-04-03/69d01586cdb525785fba7472/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hyr-global-source-inc/2026-04-03/69d01586cdb525785fba7472/resume.md")</f>
+        <f>HYPERLINK("by_company/hyr-global-source-inc/2026-04-03/69d01586cdb525785fba7472/resume.md","data/deliverables/resume_portfolio/by_company/hyr-global-source-inc/2026-04-03/69d01586cdb525785fba7472/resume.md")</f>
       </c>
       <c r="Q525"/>
       <c r="R525">
@@ -33757,7 +33757,7 @@
         </is>
       </c>
       <c r="P526">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/beaconfire-inc/2026-04-03/69d0145c891d7b11cfcd8788/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/beaconfire-inc/2026-04-03/69d0145c891d7b11cfcd8788/resume.md")</f>
+        <f>HYPERLINK("by_company/beaconfire-inc/2026-04-03/69d0145c891d7b11cfcd8788/resume.md","data/deliverables/resume_portfolio/by_company/beaconfire-inc/2026-04-03/69d0145c891d7b11cfcd8788/resume.md")</f>
       </c>
       <c r="Q526"/>
       <c r="R526">
@@ -33997,7 +33997,7 @@
         </is>
       </c>
       <c r="P530">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hone-health/2026-04-03/69d0143bcfdc6132f9438326/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hone-health/2026-04-03/69d0143bcfdc6132f9438326/resume.md")</f>
+        <f>HYPERLINK("by_company/hone-health/2026-04-03/69d0143bcfdc6132f9438326/resume.md","data/deliverables/resume_portfolio/by_company/hone-health/2026-04-03/69d0143bcfdc6132f9438326/resume.md")</f>
       </c>
       <c r="Q530"/>
       <c r="R530">
@@ -34063,7 +34063,7 @@
         </is>
       </c>
       <c r="P531">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/one-inc/2026-04-03/69d013ae366bb95ba551b3a9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/one-inc/2026-04-03/69d013ae366bb95ba551b3a9/resume.md")</f>
+        <f>HYPERLINK("by_company/one-inc/2026-04-03/69d013ae366bb95ba551b3a9/resume.md","data/deliverables/resume_portfolio/by_company/one-inc/2026-04-03/69d013ae366bb95ba551b3a9/resume.md")</f>
       </c>
       <c r="Q531"/>
       <c r="R531">
@@ -34137,7 +34137,7 @@
         </is>
       </c>
       <c r="P532">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/honeywell/2026-04-03/69d01378366bb95ba551b25b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/honeywell/2026-04-03/69d01378366bb95ba551b25b/resume.md")</f>
+        <f>HYPERLINK("by_company/honeywell/2026-04-03/69d01378366bb95ba551b25b/resume.md","data/deliverables/resume_portfolio/by_company/honeywell/2026-04-03/69d01378366bb95ba551b25b/resume.md")</f>
       </c>
       <c r="Q532"/>
       <c r="R532">
@@ -34405,7 +34405,7 @@
         </is>
       </c>
       <c r="P536">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-03/69d0134b891d7b11cfcd85ea/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-03/69d0134b891d7b11cfcd85ea/resume.md")</f>
+        <f>HYPERLINK("by_company/google/2026-04-03/69d0134b891d7b11cfcd85ea/resume.md","data/deliverables/resume_portfolio/by_company/google/2026-04-03/69d0134b891d7b11cfcd85ea/resume.md")</f>
       </c>
       <c r="Q536"/>
       <c r="R536">
@@ -34529,7 +34529,7 @@
         </is>
       </c>
       <c r="P538">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/waystar/2026-04-03/69d01115366bb95ba551b1b9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/waystar/2026-04-03/69d01115366bb95ba551b1b9/resume.md")</f>
+        <f>HYPERLINK("by_company/waystar/2026-04-03/69d01115366bb95ba551b1b9/resume.md","data/deliverables/resume_portfolio/by_company/waystar/2026-04-03/69d01115366bb95ba551b1b9/resume.md")</f>
       </c>
       <c r="Q538"/>
       <c r="R538">
@@ -34653,7 +34653,7 @@
         </is>
       </c>
       <c r="P540">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tiktok/2026-04-03/69d01101891d7b11cfcd8514/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tiktok/2026-04-03/69d01101891d7b11cfcd8514/resume.md")</f>
+        <f>HYPERLINK("by_company/tiktok/2026-04-03/69d01101891d7b11cfcd8514/resume.md","data/deliverables/resume_portfolio/by_company/tiktok/2026-04-03/69d01101891d7b11cfcd8514/resume.md")</f>
       </c>
       <c r="Q540"/>
       <c r="R540">
@@ -34719,7 +34719,7 @@
         </is>
       </c>
       <c r="P541">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cognizant/2026-04-03/69ccc1e6891d7b11cfcb3440/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cognizant/2026-04-03/69ccc1e6891d7b11cfcb3440/resume.md")</f>
+        <f>HYPERLINK("by_company/cognizant/2026-04-03/69ccc1e6891d7b11cfcb3440/resume.md","data/deliverables/resume_portfolio/by_company/cognizant/2026-04-03/69ccc1e6891d7b11cfcb3440/resume.md")</f>
       </c>
       <c r="Q541"/>
       <c r="R541">
@@ -34793,7 +34793,7 @@
         </is>
       </c>
       <c r="P542">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/dataminr/2026-04-03/68d4127b17554c2d9eef5cdc/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/dataminr/2026-04-03/68d4127b17554c2d9eef5cdc/resume.md")</f>
+        <f>HYPERLINK("by_company/dataminr/2026-04-03/68d4127b17554c2d9eef5cdc/resume.md","data/deliverables/resume_portfolio/by_company/dataminr/2026-04-03/68d4127b17554c2d9eef5cdc/resume.md")</f>
       </c>
       <c r="Q542"/>
       <c r="R542">
@@ -34859,7 +34859,7 @@
         </is>
       </c>
       <c r="P543">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/bmc-software/2026-04-03/69d00c99cfdc6132f9437d58/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/bmc-software/2026-04-03/69d00c99cfdc6132f9437d58/resume.md")</f>
+        <f>HYPERLINK("by_company/bmc-software/2026-04-03/69d00c99cfdc6132f9437d58/resume.md","data/deliverables/resume_portfolio/by_company/bmc-software/2026-04-03/69d00c99cfdc6132f9437d58/resume.md")</f>
       </c>
       <c r="Q543"/>
       <c r="R543">
@@ -34999,7 +34999,7 @@
         </is>
       </c>
       <c r="P545">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/69d00c2ccdb525785fba6b0b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/69d00c2ccdb525785fba6b0b/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon/2026-04-03/69d00c2ccdb525785fba6b0b/resume.md","data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/69d00c2ccdb525785fba6b0b/resume.md")</f>
       </c>
       <c r="Q545"/>
       <c r="R545">
@@ -35189,7 +35189,7 @@
         </is>
       </c>
       <c r="P548">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/69d00c26cdb525785fba6ae9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/69d00c26cdb525785fba6ae9/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon/2026-04-03/69d00c26cdb525785fba6ae9/resume.md","data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/69d00c26cdb525785fba6ae9/resume.md")</f>
       </c>
       <c r="Q548"/>
       <c r="R548">
@@ -35263,7 +35263,7 @@
         </is>
       </c>
       <c r="P549">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/69d00c26cdb525785fba6ae4/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/69d00c26cdb525785fba6ae4/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon/2026-04-03/69d00c26cdb525785fba6ae4/resume.md","data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/69d00c26cdb525785fba6ae4/resume.md")</f>
       </c>
       <c r="Q549"/>
       <c r="R549">
@@ -35329,7 +35329,7 @@
         </is>
       </c>
       <c r="P550">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/wex/2026-04-03/69b37e5aa8ac8e70ff67c5ae/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/wex/2026-04-03/69b37e5aa8ac8e70ff67c5ae/resume.md")</f>
+        <f>HYPERLINK("by_company/wex/2026-04-03/69b37e5aa8ac8e70ff67c5ae/resume.md","data/deliverables/resume_portfolio/by_company/wex/2026-04-03/69b37e5aa8ac8e70ff67c5ae/resume.md")</f>
       </c>
       <c r="Q550"/>
       <c r="R550">
@@ -35511,7 +35511,7 @@
         </is>
       </c>
       <c r="P553">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/wex/2026-04-03/6997ea56e0bddb6acac6cec8/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/wex/2026-04-03/6997ea56e0bddb6acac6cec8/resume.md")</f>
+        <f>HYPERLINK("by_company/wex/2026-04-03/6997ea56e0bddb6acac6cec8/resume.md","data/deliverables/resume_portfolio/by_company/wex/2026-04-03/6997ea56e0bddb6acac6cec8/resume.md")</f>
       </c>
       <c r="Q553"/>
       <c r="R553">
@@ -35577,7 +35577,7 @@
         </is>
       </c>
       <c r="P554">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mastercard/2026-04-03/69b343a4ad360c0340a8691d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mastercard/2026-04-03/69b343a4ad360c0340a8691d/resume.md")</f>
+        <f>HYPERLINK("by_company/mastercard/2026-04-03/69b343a4ad360c0340a8691d/resume.md","data/deliverables/resume_portfolio/by_company/mastercard/2026-04-03/69b343a4ad360c0340a8691d/resume.md")</f>
       </c>
       <c r="Q554"/>
       <c r="R554">
@@ -35643,7 +35643,7 @@
         </is>
       </c>
       <c r="P555">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/burlington-stores-inc/2026-04-03/69c8bb0c1b5ad028873950ef/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/burlington-stores-inc/2026-04-03/69c8bb0c1b5ad028873950ef/resume.md")</f>
+        <f>HYPERLINK("by_company/burlington-stores-inc/2026-04-03/69c8bb0c1b5ad028873950ef/resume.md","data/deliverables/resume_portfolio/by_company/burlington-stores-inc/2026-04-03/69c8bb0c1b5ad028873950ef/resume.md")</f>
       </c>
       <c r="Q555"/>
       <c r="R555">
@@ -35709,7 +35709,7 @@
         </is>
       </c>
       <c r="P556">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/capital-one/2026-04-03/69d0062c0b098b7a67075a8c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/capital-one/2026-04-03/69d0062c0b098b7a67075a8c/resume.md")</f>
+        <f>HYPERLINK("by_company/capital-one/2026-04-03/69d0062c0b098b7a67075a8c/resume.md","data/deliverables/resume_portfolio/by_company/capital-one/2026-04-03/69d0062c0b098b7a67075a8c/resume.md")</f>
       </c>
       <c r="Q556"/>
       <c r="R556">
@@ -35839,7 +35839,7 @@
         </is>
       </c>
       <c r="P558">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/capital-one/2026-04-03/69b40e205697383741389d3f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/capital-one/2026-04-03/69b40e205697383741389d3f/resume.md")</f>
+        <f>HYPERLINK("by_company/capital-one/2026-04-03/69b40e205697383741389d3f/resume.md","data/deliverables/resume_portfolio/by_company/capital-one/2026-04-03/69b40e205697383741389d3f/resume.md")</f>
       </c>
       <c r="Q558"/>
       <c r="R558">
@@ -35905,7 +35905,7 @@
         </is>
       </c>
       <c r="P559">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/environmental-science-associates/2026-04-03/69d005e6cdb525785fba69cc/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/environmental-science-associates/2026-04-03/69d005e6cdb525785fba69cc/resume.md")</f>
+        <f>HYPERLINK("by_company/environmental-science-associates/2026-04-03/69d005e6cdb525785fba69cc/resume.md","data/deliverables/resume_portfolio/by_company/environmental-science-associates/2026-04-03/69d005e6cdb525785fba69cc/resume.md")</f>
       </c>
       <c r="Q559"/>
       <c r="R559">
@@ -36101,7 +36101,7 @@
         </is>
       </c>
       <c r="P562">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/brain-corp/2026-04-03/69d00574cfdc6132f9437911/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/brain-corp/2026-04-03/69d00574cfdc6132f9437911/resume.md")</f>
+        <f>HYPERLINK("by_company/brain-corp/2026-04-03/69d00574cfdc6132f9437911/resume.md","data/deliverables/resume_portfolio/by_company/brain-corp/2026-04-03/69d00574cfdc6132f9437911/resume.md")</f>
       </c>
       <c r="Q562"/>
       <c r="R562">
@@ -36225,7 +36225,7 @@
         </is>
       </c>
       <c r="P564">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cargill/2026-04-03/69d004bdcdb525785fba6998/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cargill/2026-04-03/69d004bdcdb525785fba6998/resume.md")</f>
+        <f>HYPERLINK("by_company/cargill/2026-04-03/69d004bdcdb525785fba6998/resume.md","data/deliverables/resume_portfolio/by_company/cargill/2026-04-03/69d004bdcdb525785fba6998/resume.md")</f>
       </c>
       <c r="Q564"/>
       <c r="R564">
@@ -36291,7 +36291,7 @@
         </is>
       </c>
       <c r="P565">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/capital-one/2026-04-03/697bc02b1423772304ebec89/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/capital-one/2026-04-03/697bc02b1423772304ebec89/resume.md")</f>
+        <f>HYPERLINK("by_company/capital-one/2026-04-03/697bc02b1423772304ebec89/resume.md","data/deliverables/resume_portfolio/by_company/capital-one/2026-04-03/697bc02b1423772304ebec89/resume.md")</f>
       </c>
       <c r="Q565"/>
       <c r="R565">
@@ -36357,7 +36357,7 @@
         </is>
       </c>
       <c r="P566">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/citi/2026-04-03/69b3356fad360c0340a85b5f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/citi/2026-04-03/69b3356fad360c0340a85b5f/resume.md")</f>
+        <f>HYPERLINK("by_company/citi/2026-04-03/69b3356fad360c0340a85b5f/resume.md","data/deliverables/resume_portfolio/by_company/citi/2026-04-03/69b3356fad360c0340a85b5f/resume.md")</f>
       </c>
       <c r="Q566"/>
       <c r="R566">
@@ -36605,7 +36605,7 @@
         </is>
       </c>
       <c r="P570">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/lennar/2026-04-03/69d0019b891d7b11cfcd7acd/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/lennar/2026-04-03/69d0019b891d7b11cfcd7acd/resume.md")</f>
+        <f>HYPERLINK("by_company/lennar/2026-04-03/69d0019b891d7b11cfcd7acd/resume.md","data/deliverables/resume_portfolio/by_company/lennar/2026-04-03/69d0019b891d7b11cfcd7acd/resume.md")</f>
       </c>
       <c r="Q570"/>
       <c r="R570">
@@ -36679,7 +36679,7 @@
         </is>
       </c>
       <c r="P571">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-03/69d0019acdb525785fba682a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-03/69d0019acdb525785fba682a/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-03/69d0019acdb525785fba682a/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-03/69d0019acdb525785fba682a/resume.md")</f>
       </c>
       <c r="Q571"/>
       <c r="R571">
@@ -36745,7 +36745,7 @@
         </is>
       </c>
       <c r="P572">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gordon-food-service/2026-04-03/69d00192cdb525785fba6807/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gordon-food-service/2026-04-03/69d00192cdb525785fba6807/resume.md")</f>
+        <f>HYPERLINK("by_company/gordon-food-service/2026-04-03/69d00192cdb525785fba6807/resume.md","data/deliverables/resume_portfolio/by_company/gordon-food-service/2026-04-03/69d00192cdb525785fba6807/resume.md")</f>
       </c>
       <c r="Q572"/>
       <c r="R572">
@@ -36927,7 +36927,7 @@
         </is>
       </c>
       <c r="P575">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/wakefern-food-corp/2026-04-03/69bdadd34828227293ffeec8/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/wakefern-food-corp/2026-04-03/69bdadd34828227293ffeec8/resume.md")</f>
+        <f>HYPERLINK("by_company/wakefern-food-corp/2026-04-03/69bdadd34828227293ffeec8/resume.md","data/deliverables/resume_portfolio/by_company/wakefern-food-corp/2026-04-03/69bdadd34828227293ffeec8/resume.md")</f>
       </c>
       <c r="Q575"/>
       <c r="R575">
@@ -36993,7 +36993,7 @@
         </is>
       </c>
       <c r="P576">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/npr/2026-04-03/69978d1581476f6176afa31e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/npr/2026-04-03/69978d1581476f6176afa31e/resume.md")</f>
+        <f>HYPERLINK("by_company/npr/2026-04-03/69978d1581476f6176afa31e/resume.md","data/deliverables/resume_portfolio/by_company/npr/2026-04-03/69978d1581476f6176afa31e/resume.md")</f>
       </c>
       <c r="Q576"/>
       <c r="R576">
@@ -37117,7 +37117,7 @@
         </is>
       </c>
       <c r="P578">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/idexx-livestock-diagnostics/2026-04-03/69cffd9dcfdc6132f943764b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/idexx-livestock-diagnostics/2026-04-03/69cffd9dcfdc6132f943764b/resume.md")</f>
+        <f>HYPERLINK("by_company/idexx-livestock-diagnostics/2026-04-03/69cffd9dcfdc6132f943764b/resume.md","data/deliverables/resume_portfolio/by_company/idexx-livestock-diagnostics/2026-04-03/69cffd9dcfdc6132f943764b/resume.md")</f>
       </c>
       <c r="Q578"/>
       <c r="R578">
@@ -37315,7 +37315,7 @@
         </is>
       </c>
       <c r="P581">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nvidia/2026-04-03/69b379f7ae2a534885eae713/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nvidia/2026-04-03/69b379f7ae2a534885eae713/resume.md")</f>
+        <f>HYPERLINK("by_company/nvidia/2026-04-03/69b379f7ae2a534885eae713/resume.md","data/deliverables/resume_portfolio/by_company/nvidia/2026-04-03/69b379f7ae2a534885eae713/resume.md")</f>
       </c>
       <c r="Q581"/>
       <c r="R581">
@@ -37447,7 +37447,7 @@
         </is>
       </c>
       <c r="P583">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/genentech/2026-04-03/69851a268da7a612045f739d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/genentech/2026-04-03/69851a268da7a612045f739d/resume.md")</f>
+        <f>HYPERLINK("by_company/genentech/2026-04-03/69851a268da7a612045f739d/resume.md","data/deliverables/resume_portfolio/by_company/genentech/2026-04-03/69851a268da7a612045f739d/resume.md")</f>
       </c>
       <c r="Q583"/>
       <c r="R583">
@@ -37629,7 +37629,7 @@
         </is>
       </c>
       <c r="P586">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mass-general-brigham/2026-04-03/69cff8c054f00230c6d0e106/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mass-general-brigham/2026-04-03/69cff8c054f00230c6d0e106/resume.md")</f>
+        <f>HYPERLINK("by_company/mass-general-brigham/2026-04-03/69cff8c054f00230c6d0e106/resume.md","data/deliverables/resume_portfolio/by_company/mass-general-brigham/2026-04-03/69cff8c054f00230c6d0e106/resume.md")</f>
       </c>
       <c r="Q586"/>
       <c r="R586">
@@ -37811,7 +37811,7 @@
         </is>
       </c>
       <c r="P589">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/transunion/2026-04-03/69cff85dcfdc6132f943741f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/transunion/2026-04-03/69cff85dcfdc6132f943741f/resume.md")</f>
+        <f>HYPERLINK("by_company/transunion/2026-04-03/69cff85dcfdc6132f943741f/resume.md","data/deliverables/resume_portfolio/by_company/transunion/2026-04-03/69cff85dcfdc6132f943741f/resume.md")</f>
       </c>
       <c r="Q589"/>
       <c r="R589">
@@ -37993,7 +37993,7 @@
         </is>
       </c>
       <c r="P592">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/zendesk/2026-04-03/69cff443891d7b11cfcd760a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/zendesk/2026-04-03/69cff443891d7b11cfcd760a/resume.md")</f>
+        <f>HYPERLINK("by_company/zendesk/2026-04-03/69cff443891d7b11cfcd760a/resume.md","data/deliverables/resume_portfolio/by_company/zendesk/2026-04-03/69cff443891d7b11cfcd760a/resume.md")</f>
       </c>
       <c r="Q592"/>
       <c r="R592">
@@ -38059,7 +38059,7 @@
         </is>
       </c>
       <c r="P593">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/united-states-cold-storage-inc/2026-04-03/69cff439366bb95ba551a29b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/united-states-cold-storage-inc/2026-04-03/69cff439366bb95ba551a29b/resume.md")</f>
+        <f>HYPERLINK("by_company/united-states-cold-storage-inc/2026-04-03/69cff439366bb95ba551a29b/resume.md","data/deliverables/resume_portfolio/by_company/united-states-cold-storage-inc/2026-04-03/69cff439366bb95ba551a29b/resume.md")</f>
       </c>
       <c r="Q593"/>
       <c r="R593">
@@ -38183,7 +38183,7 @@
         </is>
       </c>
       <c r="P595">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/honeywell/2026-04-03/69cff1a0cdb525785fba5d3e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/honeywell/2026-04-03/69cff1a0cdb525785fba5d3e/resume.md")</f>
+        <f>HYPERLINK("by_company/honeywell/2026-04-03/69cff1a0cdb525785fba5d3e/resume.md","data/deliverables/resume_portfolio/by_company/honeywell/2026-04-03/69cff1a0cdb525785fba5d3e/resume.md")</f>
       </c>
       <c r="Q595"/>
       <c r="R595">
@@ -38249,7 +38249,7 @@
         </is>
       </c>
       <c r="P596">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sharkninja/2026-04-03/697c7d75137a051025658402/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sharkninja/2026-04-03/697c7d75137a051025658402/resume.md")</f>
+        <f>HYPERLINK("by_company/sharkninja/2026-04-03/697c7d75137a051025658402/resume.md","data/deliverables/resume_portfolio/by_company/sharkninja/2026-04-03/697c7d75137a051025658402/resume.md")</f>
       </c>
       <c r="Q596"/>
       <c r="R596">
@@ -38315,7 +38315,7 @@
         </is>
       </c>
       <c r="P597">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/phoenix-staff-inc/2026-04-03/69cff11acfdc6132f9436bd3/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/phoenix-staff-inc/2026-04-03/69cff11acfdc6132f9436bd3/resume.md")</f>
+        <f>HYPERLINK("by_company/phoenix-staff-inc/2026-04-03/69cff11acfdc6132f9436bd3/resume.md","data/deliverables/resume_portfolio/by_company/phoenix-staff-inc/2026-04-03/69cff11acfdc6132f9436bd3/resume.md")</f>
       </c>
       <c r="Q597"/>
       <c r="R597">
@@ -38381,7 +38381,7 @@
         </is>
       </c>
       <c r="P598">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/outdoorsy/2026-04-03/69cff01954f00230c6d0d7a8/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/outdoorsy/2026-04-03/69cff01954f00230c6d0d7a8/resume.md")</f>
+        <f>HYPERLINK("by_company/outdoorsy/2026-04-03/69cff01954f00230c6d0d7a8/resume.md","data/deliverables/resume_portfolio/by_company/outdoorsy/2026-04-03/69cff01954f00230c6d0d7a8/resume.md")</f>
       </c>
       <c r="Q598"/>
       <c r="R598">
@@ -38505,7 +38505,7 @@
         </is>
       </c>
       <c r="P600">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/wex/2026-04-03/69b37e71ad360c0340a8a739/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/wex/2026-04-03/69b37e71ad360c0340a8a739/resume.md")</f>
+        <f>HYPERLINK("by_company/wex/2026-04-03/69b37e71ad360c0340a8a739/resume.md","data/deliverables/resume_portfolio/by_company/wex/2026-04-03/69b37e71ad360c0340a8a739/resume.md")</f>
       </c>
       <c r="Q600"/>
       <c r="R600">
@@ -38579,7 +38579,7 @@
         </is>
       </c>
       <c r="P601">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/palantir-technologies/2026-04-03/68ca457c9f583c3191e3f28b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/palantir-technologies/2026-04-03/68ca457c9f583c3191e3f28b/resume.md")</f>
+        <f>HYPERLINK("by_company/palantir-technologies/2026-04-03/68ca457c9f583c3191e3f28b/resume.md","data/deliverables/resume_portfolio/by_company/palantir-technologies/2026-04-03/68ca457c9f583c3191e3f28b/resume.md")</f>
       </c>
       <c r="Q601"/>
       <c r="R601">
@@ -38653,7 +38653,7 @@
         </is>
       </c>
       <c r="P602">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/vercel/2026-04-03/69979140e0bddb6acac6411d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/vercel/2026-04-03/69979140e0bddb6acac6411d/resume.md")</f>
+        <f>HYPERLINK("by_company/vercel/2026-04-03/69979140e0bddb6acac6411d/resume.md","data/deliverables/resume_portfolio/by_company/vercel/2026-04-03/69979140e0bddb6acac6411d/resume.md")</f>
       </c>
       <c r="Q602"/>
       <c r="R602">
@@ -38785,7 +38785,7 @@
         </is>
       </c>
       <c r="P604">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/msci-inc/2026-04-03/6996555981476f6176ae1e6d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/msci-inc/2026-04-03/6996555981476f6176ae1e6d/resume.md")</f>
+        <f>HYPERLINK("by_company/msci-inc/2026-04-03/6996555981476f6176ae1e6d/resume.md","data/deliverables/resume_portfolio/by_company/msci-inc/2026-04-03/6996555981476f6176ae1e6d/resume.md")</f>
       </c>
       <c r="Q604"/>
       <c r="R604">
@@ -38851,7 +38851,7 @@
         </is>
       </c>
       <c r="P605">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-03/69b3676da8ac8e70ff679ea4/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-03/69b3676da8ac8e70ff679ea4/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon-web-services-aws/2026-04-03/69b3676da8ac8e70ff679ea4/resume.md","data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-03/69b3676da8ac8e70ff679ea4/resume.md")</f>
       </c>
       <c r="Q605"/>
       <c r="R605">
@@ -38989,7 +38989,7 @@
         </is>
       </c>
       <c r="P607">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/brex/2026-04-03/692f6457ef4b48533d144d7f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/brex/2026-04-03/692f6457ef4b48533d144d7f/resume.md")</f>
+        <f>HYPERLINK("by_company/brex/2026-04-03/692f6457ef4b48533d144d7f/resume.md","data/deliverables/resume_portfolio/by_company/brex/2026-04-03/692f6457ef4b48533d144d7f/resume.md")</f>
       </c>
       <c r="Q607"/>
       <c r="R607">
@@ -39055,7 +39055,7 @@
         </is>
       </c>
       <c r="P608">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/givecampus/2026-04-03/69cfe9b2891d7b11cfcd6b4c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/givecampus/2026-04-03/69cfe9b2891d7b11cfcd6b4c/resume.md")</f>
+        <f>HYPERLINK("by_company/givecampus/2026-04-03/69cfe9b2891d7b11cfcd6b4c/resume.md","data/deliverables/resume_portfolio/by_company/givecampus/2026-04-03/69cfe9b2891d7b11cfcd6b4c/resume.md")</f>
       </c>
       <c r="Q608"/>
       <c r="R608">
@@ -39121,7 +39121,7 @@
         </is>
       </c>
       <c r="P609">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cresta/2026-04-03/698e867a78b4502f12a55d92/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cresta/2026-04-03/698e867a78b4502f12a55d92/resume.md")</f>
+        <f>HYPERLINK("by_company/cresta/2026-04-03/698e867a78b4502f12a55d92/resume.md","data/deliverables/resume_portfolio/by_company/cresta/2026-04-03/698e867a78b4502f12a55d92/resume.md")</f>
       </c>
       <c r="Q609"/>
       <c r="R609">
@@ -39195,7 +39195,7 @@
         </is>
       </c>
       <c r="P610">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/aderant/2026-04-03/69cfe88d891d7b11cfcd6b08/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/aderant/2026-04-03/69cfe88d891d7b11cfcd6b08/resume.md")</f>
+        <f>HYPERLINK("by_company/aderant/2026-04-03/69cfe88d891d7b11cfcd6b08/resume.md","data/deliverables/resume_portfolio/by_company/aderant/2026-04-03/69cfe88d891d7b11cfcd6b08/resume.md")</f>
       </c>
       <c r="Q610"/>
       <c r="R610">
@@ -39269,7 +39269,7 @@
         </is>
       </c>
       <c r="P611">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/infojini-inc/2026-04-03/69cfe85e366bb95ba55197d9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/infojini-inc/2026-04-03/69cfe85e366bb95ba55197d9/resume.md")</f>
+        <f>HYPERLINK("by_company/infojini-inc/2026-04-03/69cfe85e366bb95ba55197d9/resume.md","data/deliverables/resume_portfolio/by_company/infojini-inc/2026-04-03/69cfe85e366bb95ba55197d9/resume.md")</f>
       </c>
       <c r="Q611"/>
       <c r="R611">
@@ -39335,7 +39335,7 @@
         </is>
       </c>
       <c r="P612">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cohere/2026-04-03/69278675d47de4798ecde00b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cohere/2026-04-03/69278675d47de4798ecde00b/resume.md")</f>
+        <f>HYPERLINK("by_company/cohere/2026-04-03/69278675d47de4798ecde00b/resume.md","data/deliverables/resume_portfolio/by_company/cohere/2026-04-03/69278675d47de4798ecde00b/resume.md")</f>
       </c>
       <c r="Q612"/>
       <c r="R612">
@@ -39401,7 +39401,7 @@
         </is>
       </c>
       <c r="P613">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-03/6997d181ce78e77b4fdc3d29/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-03/6997d181ce78e77b4fdc3d29/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon-web-services-aws/2026-04-03/6997d181ce78e77b4fdc3d29/resume.md","data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-03/6997d181ce78e77b4fdc3d29/resume.md")</f>
       </c>
       <c r="Q613"/>
       <c r="R613">
@@ -39467,7 +39467,7 @@
         </is>
       </c>
       <c r="P614">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/appian/2026-04-03/69c4e578d5a1016e98dc540d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/appian/2026-04-03/69c4e578d5a1016e98dc540d/resume.md")</f>
+        <f>HYPERLINK("by_company/appian/2026-04-03/69c4e578d5a1016e98dc540d/resume.md","data/deliverables/resume_portfolio/by_company/appian/2026-04-03/69c4e578d5a1016e98dc540d/resume.md")</f>
       </c>
       <c r="Q614"/>
       <c r="R614">
@@ -39591,7 +39591,7 @@
         </is>
       </c>
       <c r="P616">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/harbor/2026-04-03/69cfe44c891d7b11cfcd68f4/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/harbor/2026-04-03/69cfe44c891d7b11cfcd68f4/resume.md")</f>
+        <f>HYPERLINK("by_company/harbor/2026-04-03/69cfe44c891d7b11cfcd68f4/resume.md","data/deliverables/resume_portfolio/by_company/harbor/2026-04-03/69cfe44c891d7b11cfcd68f4/resume.md")</f>
       </c>
       <c r="Q616"/>
       <c r="R616">
@@ -39657,7 +39657,7 @@
         </is>
       </c>
       <c r="P617">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/lone-pine-capital-llc/2026-04-03/69b327d2ae2a534885ea8a38/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/lone-pine-capital-llc/2026-04-03/69b327d2ae2a534885ea8a38/resume.md")</f>
+        <f>HYPERLINK("by_company/lone-pine-capital-llc/2026-04-03/69b327d2ae2a534885ea8a38/resume.md","data/deliverables/resume_portfolio/by_company/lone-pine-capital-llc/2026-04-03/69b327d2ae2a534885ea8a38/resume.md")</f>
       </c>
       <c r="Q617"/>
       <c r="R617">
@@ -39723,7 +39723,7 @@
         </is>
       </c>
       <c r="P618">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/charles-schwab/2026-04-03/69cfdfd9cfdc6132f9436518/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/charles-schwab/2026-04-03/69cfdfd9cfdc6132f9436518/resume.md")</f>
+        <f>HYPERLINK("by_company/charles-schwab/2026-04-03/69cfdfd9cfdc6132f9436518/resume.md","data/deliverables/resume_portfolio/by_company/charles-schwab/2026-04-03/69cfdfd9cfdc6132f9436518/resume.md")</f>
       </c>
       <c r="Q618"/>
       <c r="R618">
@@ -39789,7 +39789,7 @@
         </is>
       </c>
       <c r="P619">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/onemagnify/2026-04-03/697aa65af6fc293b0a2c8f2d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/onemagnify/2026-04-03/697aa65af6fc293b0a2c8f2d/resume.md")</f>
+        <f>HYPERLINK("by_company/onemagnify/2026-04-03/697aa65af6fc293b0a2c8f2d/resume.md","data/deliverables/resume_portfolio/by_company/onemagnify/2026-04-03/697aa65af6fc293b0a2c8f2d/resume.md")</f>
       </c>
       <c r="Q619"/>
       <c r="R619">
@@ -39971,7 +39971,7 @@
         </is>
       </c>
       <c r="P622">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/spok/2026-04-03/69cfdc7b891d7b11cfcd677c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/spok/2026-04-03/69cfdc7b891d7b11cfcd677c/resume.md")</f>
+        <f>HYPERLINK("by_company/spok/2026-04-03/69cfdc7b891d7b11cfcd677c/resume.md","data/deliverables/resume_portfolio/by_company/spok/2026-04-03/69cfdc7b891d7b11cfcd677c/resume.md")</f>
       </c>
       <c r="Q622"/>
       <c r="R622">
@@ -40161,7 +40161,7 @@
         </is>
       </c>
       <c r="P625">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nlb-services/2026-04-03/69cff888cfdc6132f9437438/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nlb-services/2026-04-03/69cff888cfdc6132f9437438/resume.md")</f>
+        <f>HYPERLINK("by_company/nlb-services/2026-04-03/69cff888cfdc6132f9437438/resume.md","data/deliverables/resume_portfolio/by_company/nlb-services/2026-04-03/69cff888cfdc6132f9437438/resume.md")</f>
       </c>
       <c r="Q625"/>
       <c r="R625">
@@ -40227,7 +40227,7 @@
         </is>
       </c>
       <c r="P626">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gray-swan/2026-04-03/69cfd7e2cfdc6132f943630e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gray-swan/2026-04-03/69cfd7e2cfdc6132f943630e/resume.md")</f>
+        <f>HYPERLINK("by_company/gray-swan/2026-04-03/69cfd7e2cfdc6132f943630e/resume.md","data/deliverables/resume_portfolio/by_company/gray-swan/2026-04-03/69cfd7e2cfdc6132f943630e/resume.md")</f>
       </c>
       <c r="Q626"/>
       <c r="R626">
@@ -40293,7 +40293,7 @@
         </is>
       </c>
       <c r="P627">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gei-consultants-inc/2026-04-03/69cfd7d40b098b7a67074433/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gei-consultants-inc/2026-04-03/69cfd7d40b098b7a67074433/resume.md")</f>
+        <f>HYPERLINK("by_company/gei-consultants-inc/2026-04-03/69cfd7d40b098b7a67074433/resume.md","data/deliverables/resume_portfolio/by_company/gei-consultants-inc/2026-04-03/69cfd7d40b098b7a67074433/resume.md")</f>
       </c>
       <c r="Q627"/>
       <c r="R627">
@@ -40359,7 +40359,7 @@
         </is>
       </c>
       <c r="P628">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/two-sigma/2026-04-03/68ca505d06a34016008c67c7/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/two-sigma/2026-04-03/68ca505d06a34016008c67c7/resume.md")</f>
+        <f>HYPERLINK("by_company/two-sigma/2026-04-03/68ca505d06a34016008c67c7/resume.md","data/deliverables/resume_portfolio/by_company/two-sigma/2026-04-03/68ca505d06a34016008c67c7/resume.md")</f>
       </c>
       <c r="Q628"/>
       <c r="R628">
@@ -40483,7 +40483,7 @@
         </is>
       </c>
       <c r="P630">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/phantom/2026-04-03/69b30d8bae2a534885ea542a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/phantom/2026-04-03/69b30d8bae2a534885ea542a/resume.md")</f>
+        <f>HYPERLINK("by_company/phantom/2026-04-03/69b30d8bae2a534885ea542a/resume.md","data/deliverables/resume_portfolio/by_company/phantom/2026-04-03/69b30d8bae2a534885ea542a/resume.md")</f>
       </c>
       <c r="Q630"/>
       <c r="R630">
@@ -40615,7 +40615,7 @@
         </is>
       </c>
       <c r="P632">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-03/69cfd4aacdb525785fba4ec1/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-03/69cfd4aacdb525785fba4ec1/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-03/69cfd4aacdb525785fba4ec1/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-03/69cfd4aacdb525785fba4ec1/resume.md")</f>
       </c>
       <c r="Q632"/>
       <c r="R632">
@@ -40747,7 +40747,7 @@
         </is>
       </c>
       <c r="P634">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ceribell-ai-powered-point-of-care-eeg/2026-04-03/69a88d422580d3183f0091db/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ceribell-ai-powered-point-of-care-eeg/2026-04-03/69a88d422580d3183f0091db/resume.md")</f>
+        <f>HYPERLINK("by_company/ceribell-ai-powered-point-of-care-eeg/2026-04-03/69a88d422580d3183f0091db/resume.md","data/deliverables/resume_portfolio/by_company/ceribell-ai-powered-point-of-care-eeg/2026-04-03/69a88d422580d3183f0091db/resume.md")</f>
       </c>
       <c r="Q634"/>
       <c r="R634">
@@ -40813,7 +40813,7 @@
         </is>
       </c>
       <c r="P635">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/2k/2026-04-03/697ae2c817b11b1c2e41b353/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/2k/2026-04-03/697ae2c817b11b1c2e41b353/resume.md")</f>
+        <f>HYPERLINK("by_company/2k/2026-04-03/697ae2c817b11b1c2e41b353/resume.md","data/deliverables/resume_portfolio/by_company/2k/2026-04-03/697ae2c817b11b1c2e41b353/resume.md")</f>
       </c>
       <c r="Q635"/>
       <c r="R635">
@@ -40879,7 +40879,7 @@
         </is>
       </c>
       <c r="P636">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/coinbase/2026-04-03/69b9dac906c1ba00c54bfa0b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/coinbase/2026-04-03/69b9dac906c1ba00c54bfa0b/resume.md")</f>
+        <f>HYPERLINK("by_company/coinbase/2026-04-03/69b9dac906c1ba00c54bfa0b/resume.md","data/deliverables/resume_portfolio/by_company/coinbase/2026-04-03/69b9dac906c1ba00c54bfa0b/resume.md")</f>
       </c>
       <c r="Q636"/>
       <c r="R636">
@@ -41069,7 +41069,7 @@
         </is>
       </c>
       <c r="P639">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualcomm/2026-04-03/69cfcf74cdb525785fba4da5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualcomm/2026-04-03/69cfcf74cdb525785fba4da5/resume.md")</f>
+        <f>HYPERLINK("by_company/qualcomm/2026-04-03/69cfcf74cdb525785fba4da5/resume.md","data/deliverables/resume_portfolio/by_company/qualcomm/2026-04-03/69cfcf74cdb525785fba4da5/resume.md")</f>
       </c>
       <c r="Q639"/>
       <c r="R639">
@@ -41193,7 +41193,7 @@
         </is>
       </c>
       <c r="P641">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/edison-scientific/2026-04-03/69d00c59cdb525785fba6c67/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/edison-scientific/2026-04-03/69d00c59cdb525785fba6c67/resume.md")</f>
+        <f>HYPERLINK("by_company/edison-scientific/2026-04-03/69d00c59cdb525785fba6c67/resume.md","data/deliverables/resume_portfolio/by_company/edison-scientific/2026-04-03/69d00c59cdb525785fba6c67/resume.md")</f>
       </c>
       <c r="Q641"/>
       <c r="R641">
@@ -41259,7 +41259,7 @@
         </is>
       </c>
       <c r="P642">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/abnormal-ai/2026-04-03/69797a760791bc1d7230219d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/abnormal-ai/2026-04-03/69797a760791bc1d7230219d/resume.md")</f>
+        <f>HYPERLINK("by_company/abnormal-ai/2026-04-03/69797a760791bc1d7230219d/resume.md","data/deliverables/resume_portfolio/by_company/abnormal-ai/2026-04-03/69797a760791bc1d7230219d/resume.md")</f>
       </c>
       <c r="Q642"/>
       <c r="R642">
@@ -41325,7 +41325,7 @@
         </is>
       </c>
       <c r="P643">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fireblocks/2026-04-03/6925bcedd47de4798ecd1440/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fireblocks/2026-04-03/6925bcedd47de4798ecd1440/resume.md")</f>
+        <f>HYPERLINK("by_company/fireblocks/2026-04-03/6925bcedd47de4798ecd1440/resume.md","data/deliverables/resume_portfolio/by_company/fireblocks/2026-04-03/6925bcedd47de4798ecd1440/resume.md")</f>
       </c>
       <c r="Q643"/>
       <c r="R643">
@@ -41391,7 +41391,7 @@
         </is>
       </c>
       <c r="P644">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nash/2026-04-03/696e52bd350cf43803150e00/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nash/2026-04-03/696e52bd350cf43803150e00/resume.md")</f>
+        <f>HYPERLINK("by_company/nash/2026-04-03/696e52bd350cf43803150e00/resume.md","data/deliverables/resume_portfolio/by_company/nash/2026-04-03/696e52bd350cf43803150e00/resume.md")</f>
       </c>
       <c r="Q644"/>
       <c r="R644">
@@ -41457,7 +41457,7 @@
         </is>
       </c>
       <c r="P645">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-03/69cfcdc7366bb95ba5518cb0/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-03/69cfcdc7366bb95ba5518cb0/resume.md")</f>
+        <f>HYPERLINK("by_company/ss-c-technologies/2026-04-03/69cfcdc7366bb95ba5518cb0/resume.md","data/deliverables/resume_portfolio/by_company/ss-c-technologies/2026-04-03/69cfcdc7366bb95ba5518cb0/resume.md")</f>
       </c>
       <c r="Q645"/>
       <c r="R645">
@@ -41523,7 +41523,7 @@
         </is>
       </c>
       <c r="P646">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/notion/2026-04-03/69436cf150bbaf76505559e5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/notion/2026-04-03/69436cf150bbaf76505559e5/resume.md")</f>
+        <f>HYPERLINK("by_company/notion/2026-04-03/69436cf150bbaf76505559e5/resume.md","data/deliverables/resume_portfolio/by_company/notion/2026-04-03/69436cf150bbaf76505559e5/resume.md")</f>
       </c>
       <c r="Q646"/>
       <c r="R646">
@@ -41589,7 +41589,7 @@
         </is>
       </c>
       <c r="P647">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/quotewerks/2026-04-03/69b2f398ad360c0340a8031c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/quotewerks/2026-04-03/69b2f398ad360c0340a8031c/resume.md")</f>
+        <f>HYPERLINK("by_company/quotewerks/2026-04-03/69b2f398ad360c0340a8031c/resume.md","data/deliverables/resume_portfolio/by_company/quotewerks/2026-04-03/69b2f398ad360c0340a8031c/resume.md")</f>
       </c>
       <c r="Q647"/>
       <c r="R647">
@@ -41713,7 +41713,7 @@
         </is>
       </c>
       <c r="P649">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/render/2026-04-03/69969447ce78e77b4fdab252/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/render/2026-04-03/69969447ce78e77b4fdab252/resume.md")</f>
+        <f>HYPERLINK("by_company/render/2026-04-03/69969447ce78e77b4fdab252/resume.md","data/deliverables/resume_portfolio/by_company/render/2026-04-03/69969447ce78e77b4fdab252/resume.md")</f>
       </c>
       <c r="Q649"/>
       <c r="R649">
@@ -41837,7 +41837,7 @@
         </is>
       </c>
       <c r="P651">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/schrodinger/2026-04-03/69b327d1ae2a534885ea8a2f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/schrodinger/2026-04-03/69b327d1ae2a534885ea8a2f/resume.md")</f>
+        <f>HYPERLINK("by_company/schrodinger/2026-04-03/69b327d1ae2a534885ea8a2f/resume.md","data/deliverables/resume_portfolio/by_company/schrodinger/2026-04-03/69b327d1ae2a534885ea8a2f/resume.md")</f>
       </c>
       <c r="Q651"/>
       <c r="R651">
@@ -42027,7 +42027,7 @@
         </is>
       </c>
       <c r="P654">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/profound/2026-04-03/69cfc86e0b098b7a67073bac/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/profound/2026-04-03/69cfc86e0b098b7a67073bac/resume.md")</f>
+        <f>HYPERLINK("by_company/profound/2026-04-03/69cfc86e0b098b7a67073bac/resume.md","data/deliverables/resume_portfolio/by_company/profound/2026-04-03/69cfc86e0b098b7a67073bac/resume.md")</f>
       </c>
       <c r="Q654"/>
       <c r="R654">
@@ -42093,7 +42093,7 @@
         </is>
       </c>
       <c r="P655">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/profound/2026-04-03/69cfc830366bb95ba5518b62/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/profound/2026-04-03/69cfc830366bb95ba5518b62/resume.md")</f>
+        <f>HYPERLINK("by_company/profound/2026-04-03/69cfc830366bb95ba5518b62/resume.md","data/deliverables/resume_portfolio/by_company/profound/2026-04-03/69cfc830366bb95ba5518b62/resume.md")</f>
       </c>
       <c r="Q655"/>
       <c r="R655">
@@ -42367,7 +42367,7 @@
         </is>
       </c>
       <c r="P659">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/arteraai/2026-04-03/69be20c1b106024562838cb7/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/arteraai/2026-04-03/69be20c1b106024562838cb7/resume.md")</f>
+        <f>HYPERLINK("by_company/arteraai/2026-04-03/69be20c1b106024562838cb7/resume.md","data/deliverables/resume_portfolio/by_company/arteraai/2026-04-03/69be20c1b106024562838cb7/resume.md")</f>
       </c>
       <c r="Q659"/>
       <c r="R659">
@@ -42621,7 +42621,7 @@
         </is>
       </c>
       <c r="P663">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/braze/2026-04-03/68f02d4e78ba1621431e2f96/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/braze/2026-04-03/68f02d4e78ba1621431e2f96/resume.md")</f>
+        <f>HYPERLINK("by_company/braze/2026-04-03/68f02d4e78ba1621431e2f96/resume.md","data/deliverables/resume_portfolio/by_company/braze/2026-04-03/68f02d4e78ba1621431e2f96/resume.md")</f>
       </c>
       <c r="Q663"/>
       <c r="R663">
@@ -42687,7 +42687,7 @@
         </is>
       </c>
       <c r="P664">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mass-general-brigham/2026-04-03/69cfc3a4cdb525785fba4aff/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mass-general-brigham/2026-04-03/69cfc3a4cdb525785fba4aff/resume.md")</f>
+        <f>HYPERLINK("by_company/mass-general-brigham/2026-04-03/69cfc3a4cdb525785fba4aff/resume.md","data/deliverables/resume_portfolio/by_company/mass-general-brigham/2026-04-03/69cfc3a4cdb525785fba4aff/resume.md")</f>
       </c>
       <c r="Q664"/>
       <c r="R664">
@@ -42943,7 +42943,7 @@
         </is>
       </c>
       <c r="P668">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/6996d6d0ce78e77b4fdb0c7f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/6996d6d0ce78e77b4fdb0c7f/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon/2026-04-03/6996d6d0ce78e77b4fdb0c7f/resume.md","data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/6996d6d0ce78e77b4fdb0c7f/resume.md")</f>
       </c>
       <c r="Q668"/>
       <c r="R668">
@@ -43067,7 +43067,7 @@
         </is>
       </c>
       <c r="P670">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/langchain/2026-04-03/69b3e91c5697383741387f62/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/langchain/2026-04-03/69b3e91c5697383741387f62/resume.md")</f>
+        <f>HYPERLINK("by_company/langchain/2026-04-03/69b3e91c5697383741387f62/resume.md","data/deliverables/resume_portfolio/by_company/langchain/2026-04-03/69b3e91c5697383741387f62/resume.md")</f>
       </c>
       <c r="Q670"/>
       <c r="R670">
@@ -43199,7 +43199,7 @@
         </is>
       </c>
       <c r="P672">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sandboxaq/2026-04-03/692695aef0beb07232625cba/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sandboxaq/2026-04-03/692695aef0beb07232625cba/resume.md")</f>
+        <f>HYPERLINK("by_company/sandboxaq/2026-04-03/692695aef0beb07232625cba/resume.md","data/deliverables/resume_portfolio/by_company/sandboxaq/2026-04-03/692695aef0beb07232625cba/resume.md")</f>
       </c>
       <c r="Q672"/>
       <c r="R672">
@@ -43323,7 +43323,7 @@
         </is>
       </c>
       <c r="P674">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/roblox/2026-04-03/69253d8bd47de4798ecceb43/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/roblox/2026-04-03/69253d8bd47de4798ecceb43/resume.md")</f>
+        <f>HYPERLINK("by_company/roblox/2026-04-03/69253d8bd47de4798ecceb43/resume.md","data/deliverables/resume_portfolio/by_company/roblox/2026-04-03/69253d8bd47de4798ecceb43/resume.md")</f>
       </c>
       <c r="Q674"/>
       <c r="R674">
@@ -43447,7 +43447,7 @@
         </is>
       </c>
       <c r="P676">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cargill/2026-04-03/69cfb988891d7b11cfcd5af6/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cargill/2026-04-03/69cfb988891d7b11cfcd5af6/resume.md")</f>
+        <f>HYPERLINK("by_company/cargill/2026-04-03/69cfb988891d7b11cfcd5af6/resume.md","data/deliverables/resume_portfolio/by_company/cargill/2026-04-03/69cfb988891d7b11cfcd5af6/resume.md")</f>
       </c>
       <c r="Q676"/>
       <c r="R676">
@@ -43571,7 +43571,7 @@
         </is>
       </c>
       <c r="P678">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-03/69cfb8c10b098b7a67073920/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-03/69cfb8c10b098b7a67073920/resume.md")</f>
+        <f>HYPERLINK("by_company/microsoft/2026-04-03/69cfb8c10b098b7a67073920/resume.md","data/deliverables/resume_portfolio/by_company/microsoft/2026-04-03/69cfb8c10b098b7a67073920/resume.md")</f>
       </c>
       <c r="Q678"/>
       <c r="R678">
@@ -43935,7 +43935,7 @@
         </is>
       </c>
       <c r="P684">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-03/69b2b893ad360c0340a79c07/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-03/69b2b893ad360c0340a79c07/resume.md")</f>
+        <f>HYPERLINK("by_company/google/2026-04-03/69b2b893ad360c0340a79c07/resume.md","data/deliverables/resume_portfolio/by_company/google/2026-04-03/69b2b893ad360c0340a79c07/resume.md")</f>
       </c>
       <c r="Q684"/>
       <c r="R684">
@@ -44059,7 +44059,7 @@
         </is>
       </c>
       <c r="P686">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/clarivate/2026-04-03/695fc28ea112b402660e6dc7/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/clarivate/2026-04-03/695fc28ea112b402660e6dc7/resume.md")</f>
+        <f>HYPERLINK("by_company/clarivate/2026-04-03/695fc28ea112b402660e6dc7/resume.md","data/deliverables/resume_portfolio/by_company/clarivate/2026-04-03/695fc28ea112b402660e6dc7/resume.md")</f>
       </c>
       <c r="Q686"/>
       <c r="R686">
@@ -44125,7 +44125,7 @@
         </is>
       </c>
       <c r="P687">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/latitude-ai/2026-04-03/69a3bdb2b600907a9629bd3e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/latitude-ai/2026-04-03/69a3bdb2b600907a9629bd3e/resume.md")</f>
+        <f>HYPERLINK("by_company/latitude-ai/2026-04-03/69a3bdb2b600907a9629bd3e/resume.md","data/deliverables/resume_portfolio/by_company/latitude-ai/2026-04-03/69a3bdb2b600907a9629bd3e/resume.md")</f>
       </c>
       <c r="Q687"/>
       <c r="R687">
@@ -44191,7 +44191,7 @@
         </is>
       </c>
       <c r="P688">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/zipline/2026-04-03/6941779414ee092a69ffa1e4/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/zipline/2026-04-03/6941779414ee092a69ffa1e4/resume.md")</f>
+        <f>HYPERLINK("by_company/zipline/2026-04-03/6941779414ee092a69ffa1e4/resume.md","data/deliverables/resume_portfolio/by_company/zipline/2026-04-03/6941779414ee092a69ffa1e4/resume.md")</f>
       </c>
       <c r="Q688"/>
       <c r="R688">
@@ -44315,7 +44315,7 @@
         </is>
       </c>
       <c r="P690">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/micron-technology/2026-04-03/69cfb54e891d7b11cfcd5524/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/micron-technology/2026-04-03/69cfb54e891d7b11cfcd5524/resume.md")</f>
+        <f>HYPERLINK("by_company/micron-technology/2026-04-03/69cfb54e891d7b11cfcd5524/resume.md","data/deliverables/resume_portfolio/by_company/micron-technology/2026-04-03/69cfb54e891d7b11cfcd5524/resume.md")</f>
       </c>
       <c r="Q690"/>
       <c r="R690">
@@ -44453,7 +44453,7 @@
         </is>
       </c>
       <c r="P692">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/northwestern-university/2026-04-03/69cf2b52cdb525785fb9f285/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/northwestern-university/2026-04-03/69cf2b52cdb525785fb9f285/resume.md")</f>
+        <f>HYPERLINK("by_company/northwestern-university/2026-04-03/69cf2b52cdb525785fb9f285/resume.md","data/deliverables/resume_portfolio/by_company/northwestern-university/2026-04-03/69cf2b52cdb525785fb9f285/resume.md")</f>
       </c>
       <c r="Q692"/>
       <c r="R692">
@@ -44657,7 +44657,7 @@
         </is>
       </c>
       <c r="P695">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sezzle/2026-04-03/6917535b3ea85638ae1c9c1c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sezzle/2026-04-03/6917535b3ea85638ae1c9c1c/resume.md")</f>
+        <f>HYPERLINK("by_company/sezzle/2026-04-03/6917535b3ea85638ae1c9c1c/resume.md","data/deliverables/resume_portfolio/by_company/sezzle/2026-04-03/6917535b3ea85638ae1c9c1c/resume.md")</f>
       </c>
       <c r="Q695"/>
       <c r="R695">
@@ -44859,7 +44859,7 @@
         </is>
       </c>
       <c r="P698">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/69cfb2a20b098b7a67073316/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/69cfb2a20b098b7a67073316/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon/2026-04-03/69cfb2a20b098b7a67073316/resume.md","data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/69cfb2a20b098b7a67073316/resume.md")</f>
       </c>
       <c r="Q698"/>
       <c r="R698">
@@ -45049,7 +45049,7 @@
         </is>
       </c>
       <c r="P701">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-03/69b2e781ad360c0340a7f6e0/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-03/69b2e781ad360c0340a7f6e0/resume.md")</f>
+        <f>HYPERLINK("by_company/google/2026-04-03/69b2e781ad360c0340a7f6e0/resume.md","data/deliverables/resume_portfolio/by_company/google/2026-04-03/69b2e781ad360c0340a7f6e0/resume.md")</f>
       </c>
       <c r="Q701"/>
       <c r="R701">
@@ -45115,7 +45115,7 @@
         </is>
       </c>
       <c r="P702">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/chime/2026-04-03/69b32561ad360c0340a8446e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/chime/2026-04-03/69b32561ad360c0340a8446e/resume.md")</f>
+        <f>HYPERLINK("by_company/chime/2026-04-03/69b32561ad360c0340a8446e/resume.md","data/deliverables/resume_portfolio/by_company/chime/2026-04-03/69b32561ad360c0340a8446e/resume.md")</f>
       </c>
       <c r="Q702"/>
       <c r="R702">
@@ -45305,7 +45305,7 @@
         </is>
       </c>
       <c r="P705">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nvidia/2026-04-03/69cf8f82366bb95ba55176e0/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nvidia/2026-04-03/69cf8f82366bb95ba55176e0/resume.md")</f>
+        <f>HYPERLINK("by_company/nvidia/2026-04-03/69cf8f82366bb95ba55176e0/resume.md","data/deliverables/resume_portfolio/by_company/nvidia/2026-04-03/69cf8f82366bb95ba55176e0/resume.md")</f>
       </c>
       <c r="Q705"/>
       <c r="R705">
@@ -45487,7 +45487,7 @@
         </is>
       </c>
       <c r="P708">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hewlett-packard-enterprise/2026-04-03/69cfa32a891d7b11cfcd500d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hewlett-packard-enterprise/2026-04-03/69cfa32a891d7b11cfcd500d/resume.md")</f>
+        <f>HYPERLINK("by_company/hewlett-packard-enterprise/2026-04-03/69cfa32a891d7b11cfcd500d/resume.md","data/deliverables/resume_portfolio/by_company/hewlett-packard-enterprise/2026-04-03/69cfa32a891d7b11cfcd500d/resume.md")</f>
       </c>
       <c r="Q708"/>
       <c r="R708">
@@ -45553,7 +45553,7 @@
         </is>
       </c>
       <c r="P709">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/relativity/2026-04-03/69b31d67a8ac8e70ff674507/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/relativity/2026-04-03/69b31d67a8ac8e70ff674507/resume.md")</f>
+        <f>HYPERLINK("by_company/relativity/2026-04-03/69b31d67a8ac8e70ff674507/resume.md","data/deliverables/resume_portfolio/by_company/relativity/2026-04-03/69b31d67a8ac8e70ff674507/resume.md")</f>
       </c>
       <c r="Q709"/>
       <c r="R709">
@@ -45619,7 +45619,7 @@
         </is>
       </c>
       <c r="P710">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/84-51/2026-04-03/6997510f81476f6176af789a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/84-51/2026-04-03/6997510f81476f6176af789a/resume.md")</f>
+        <f>HYPERLINK("by_company/84-51/2026-04-03/6997510f81476f6176af789a/resume.md","data/deliverables/resume_portfolio/by_company/84-51/2026-04-03/6997510f81476f6176af789a/resume.md")</f>
       </c>
       <c r="Q710"/>
       <c r="R710">
@@ -45807,7 +45807,7 @@
         </is>
       </c>
       <c r="P713">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fireworks-ai/2026-04-03/690b9b4d4a1b456627b10c18/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fireworks-ai/2026-04-03/690b9b4d4a1b456627b10c18/resume.md")</f>
+        <f>HYPERLINK("by_company/fireworks-ai/2026-04-03/690b9b4d4a1b456627b10c18/resume.md","data/deliverables/resume_portfolio/by_company/fireworks-ai/2026-04-03/690b9b4d4a1b456627b10c18/resume.md")</f>
       </c>
       <c r="Q713"/>
       <c r="R713">
@@ -45881,7 +45881,7 @@
         </is>
       </c>
       <c r="P714">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-03/69c6753cb773006330b709d0/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-03/69c6753cb773006330b709d0/resume.md")</f>
+        <f>HYPERLINK("by_company/google/2026-04-03/69c6753cb773006330b709d0/resume.md","data/deliverables/resume_portfolio/by_company/google/2026-04-03/69c6753cb773006330b709d0/resume.md")</f>
       </c>
       <c r="Q714"/>
       <c r="R714">
@@ -45947,7 +45947,7 @@
         </is>
       </c>
       <c r="P715">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/xylem/2026-04-03/697b171e17b11b1c2e42138a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/xylem/2026-04-03/697b171e17b11b1c2e42138a/resume.md")</f>
+        <f>HYPERLINK("by_company/xylem/2026-04-03/697b171e17b11b1c2e42138a/resume.md","data/deliverables/resume_portfolio/by_company/xylem/2026-04-03/697b171e17b11b1c2e42138a/resume.md")</f>
       </c>
       <c r="Q715"/>
       <c r="R715">
@@ -46071,7 +46071,7 @@
         </is>
       </c>
       <c r="P717">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-03/69b34093ad360c0340a8672f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-03/69b34093ad360c0340a8672f/resume.md")</f>
+        <f>HYPERLINK("by_company/adobe/2026-04-03/69b34093ad360c0340a8672f/resume.md","data/deliverables/resume_portfolio/by_company/adobe/2026-04-03/69b34093ad360c0340a8672f/resume.md")</f>
       </c>
       <c r="Q717"/>
       <c r="R717">
@@ -46137,7 +46137,7 @@
         </is>
       </c>
       <c r="P718">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mercury-insurance/2026-04-03/6959cd899f1b381eb27280cb/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mercury-insurance/2026-04-03/6959cd899f1b381eb27280cb/resume.md")</f>
+        <f>HYPERLINK("by_company/mercury-insurance/2026-04-03/6959cd899f1b381eb27280cb/resume.md","data/deliverables/resume_portfolio/by_company/mercury-insurance/2026-04-03/6959cd899f1b381eb27280cb/resume.md")</f>
       </c>
       <c r="Q718"/>
       <c r="R718">
@@ -46203,7 +46203,7 @@
         </is>
       </c>
       <c r="P719">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-03/6996e41681476f6176aedac8/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-03/6996e41681476f6176aedac8/resume.md")</f>
+        <f>HYPERLINK("by_company/adobe/2026-04-03/6996e41681476f6176aedac8/resume.md","data/deliverables/resume_portfolio/by_company/adobe/2026-04-03/6996e41681476f6176aedac8/resume.md")</f>
       </c>
       <c r="Q719"/>
       <c r="R719">
@@ -46269,7 +46269,7 @@
         </is>
       </c>
       <c r="P720">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/spoton/2026-04-03/69967c75e0bddb6acac4f66f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/spoton/2026-04-03/69967c75e0bddb6acac4f66f/resume.md")</f>
+        <f>HYPERLINK("by_company/spoton/2026-04-03/69967c75e0bddb6acac4f66f/resume.md","data/deliverables/resume_portfolio/by_company/spoton/2026-04-03/69967c75e0bddb6acac4f66f/resume.md")</f>
       </c>
       <c r="Q720"/>
       <c r="R720">
@@ -46343,7 +46343,7 @@
         </is>
       </c>
       <c r="P721">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/zoox/2026-04-03/687852d5866a435525ab86a8/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/zoox/2026-04-03/687852d5866a435525ab86a8/resume.md")</f>
+        <f>HYPERLINK("by_company/zoox/2026-04-03/687852d5866a435525ab86a8/resume.md","data/deliverables/resume_portfolio/by_company/zoox/2026-04-03/687852d5866a435525ab86a8/resume.md")</f>
       </c>
       <c r="Q721"/>
       <c r="R721">
@@ -46409,7 +46409,7 @@
         </is>
       </c>
       <c r="P722">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-03/69b344d5a8ac8e70ff6783a5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-03/69b344d5a8ac8e70ff6783a5/resume.md")</f>
+        <f>HYPERLINK("by_company/adobe/2026-04-03/69b344d5a8ac8e70ff6783a5/resume.md","data/deliverables/resume_portfolio/by_company/adobe/2026-04-03/69b344d5a8ac8e70ff6783a5/resume.md")</f>
       </c>
       <c r="Q722"/>
       <c r="R722">
@@ -46475,7 +46475,7 @@
         </is>
       </c>
       <c r="P723">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-03/69b33996a8ac8e70ff677c54/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-03/69b33996a8ac8e70ff677c54/resume.md")</f>
+        <f>HYPERLINK("by_company/adobe/2026-04-03/69b33996a8ac8e70ff677c54/resume.md","data/deliverables/resume_portfolio/by_company/adobe/2026-04-03/69b33996a8ac8e70ff677c54/resume.md")</f>
       </c>
       <c r="Q723"/>
       <c r="R723">
@@ -46541,7 +46541,7 @@
         </is>
       </c>
       <c r="P724">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/medpace/2026-04-03/6960421da1bbea1d9a7b2818/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/medpace/2026-04-03/6960421da1bbea1d9a7b2818/resume.md")</f>
+        <f>HYPERLINK("by_company/medpace/2026-04-03/6960421da1bbea1d9a7b2818/resume.md","data/deliverables/resume_portfolio/by_company/medpace/2026-04-03/6960421da1bbea1d9a7b2818/resume.md")</f>
       </c>
       <c r="Q724"/>
       <c r="R724">
@@ -46607,7 +46607,7 @@
         </is>
       </c>
       <c r="P725">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/zoox/2026-04-03/6863482375a7d35fe59d54c3/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/zoox/2026-04-03/6863482375a7d35fe59d54c3/resume.md")</f>
+        <f>HYPERLINK("by_company/zoox/2026-04-03/6863482375a7d35fe59d54c3/resume.md","data/deliverables/resume_portfolio/by_company/zoox/2026-04-03/6863482375a7d35fe59d54c3/resume.md")</f>
       </c>
       <c r="Q725"/>
       <c r="R725">
@@ -46673,7 +46673,7 @@
         </is>
       </c>
       <c r="P726">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/artefact/2026-04-03/698e5711f64d441a16508b91/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/artefact/2026-04-03/698e5711f64d441a16508b91/resume.md")</f>
+        <f>HYPERLINK("by_company/artefact/2026-04-03/698e5711f64d441a16508b91/resume.md","data/deliverables/resume_portfolio/by_company/artefact/2026-04-03/698e5711f64d441a16508b91/resume.md")</f>
       </c>
       <c r="Q726"/>
       <c r="R726">
@@ -46805,7 +46805,7 @@
         </is>
       </c>
       <c r="P728">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-03/697b738f1136d179eeeef5ea/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-03/697b738f1136d179eeeef5ea/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-03/697b738f1136d179eeeef5ea/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-03/697b738f1136d179eeeef5ea/resume.md")</f>
       </c>
       <c r="Q728"/>
       <c r="R728">
@@ -46929,7 +46929,7 @@
         </is>
       </c>
       <c r="P730">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ametek/2026-04-03/69a06d6e81476f6176baaab6/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ametek/2026-04-03/69a06d6e81476f6176baaab6/resume.md")</f>
+        <f>HYPERLINK("by_company/ametek/2026-04-03/69a06d6e81476f6176baaab6/resume.md","data/deliverables/resume_portfolio/by_company/ametek/2026-04-03/69a06d6e81476f6176baaab6/resume.md")</f>
       </c>
       <c r="Q730"/>
       <c r="R730">
@@ -46995,7 +46995,7 @@
         </is>
       </c>
       <c r="P731">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/certara/2026-04-03/69a654ece567421f425754f1/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/certara/2026-04-03/69a654ece567421f425754f1/resume.md")</f>
+        <f>HYPERLINK("by_company/certara/2026-04-03/69a654ece567421f425754f1/resume.md","data/deliverables/resume_portfolio/by_company/certara/2026-04-03/69a654ece567421f425754f1/resume.md")</f>
       </c>
       <c r="Q731"/>
       <c r="R731">
@@ -47069,7 +47069,7 @@
         </is>
       </c>
       <c r="P732">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/generac/2026-04-03/69cf8fbecfdc6132f94345a1/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/generac/2026-04-03/69cf8fbecfdc6132f94345a1/resume.md")</f>
+        <f>HYPERLINK("by_company/generac/2026-04-03/69cf8fbecfdc6132f94345a1/resume.md","data/deliverables/resume_portfolio/by_company/generac/2026-04-03/69cf8fbecfdc6132f94345a1/resume.md")</f>
       </c>
       <c r="Q732"/>
       <c r="R732">
@@ -47135,7 +47135,7 @@
         </is>
       </c>
       <c r="P733">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gilead-sciences/2026-04-03/69978a70ce78e77b4fdbd908/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gilead-sciences/2026-04-03/69978a70ce78e77b4fdbd908/resume.md")</f>
+        <f>HYPERLINK("by_company/gilead-sciences/2026-04-03/69978a70ce78e77b4fdbd908/resume.md","data/deliverables/resume_portfolio/by_company/gilead-sciences/2026-04-03/69978a70ce78e77b4fdbd908/resume.md")</f>
       </c>
       <c r="Q733"/>
       <c r="R733">
@@ -47201,7 +47201,7 @@
         </is>
       </c>
       <c r="P734">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/waystar/2026-04-03/69c61b6f1b5ad0288737d73d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/waystar/2026-04-03/69c61b6f1b5ad0288737d73d/resume.md")</f>
+        <f>HYPERLINK("by_company/waystar/2026-04-03/69c61b6f1b5ad0288737d73d/resume.md","data/deliverables/resume_portfolio/by_company/waystar/2026-04-03/69c61b6f1b5ad0288737d73d/resume.md")</f>
       </c>
       <c r="Q734"/>
       <c r="R734">
@@ -47325,7 +47325,7 @@
         </is>
       </c>
       <c r="P736">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/doordash/2026-04-03/67ee0e8efb35b3b96ba75e2b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/doordash/2026-04-03/67ee0e8efb35b3b96ba75e2b/resume.md")</f>
+        <f>HYPERLINK("by_company/doordash/2026-04-03/67ee0e8efb35b3b96ba75e2b/resume.md","data/deliverables/resume_portfolio/by_company/doordash/2026-04-03/67ee0e8efb35b3b96ba75e2b/resume.md")</f>
       </c>
       <c r="Q736"/>
       <c r="R736">
@@ -47391,7 +47391,7 @@
         </is>
       </c>
       <c r="P737">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sharkninja/2026-04-03/69cf880ccdb525785fba35fe/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sharkninja/2026-04-03/69cf880ccdb525785fba35fe/resume.md")</f>
+        <f>HYPERLINK("by_company/sharkninja/2026-04-03/69cf880ccdb525785fba35fe/resume.md","data/deliverables/resume_portfolio/by_company/sharkninja/2026-04-03/69cf880ccdb525785fba35fe/resume.md")</f>
       </c>
       <c r="Q737"/>
       <c r="R737">
@@ -47457,7 +47457,7 @@
         </is>
       </c>
       <c r="P738">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nordstrom/2026-04-03/69cf87c254f00230c6d0afa9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nordstrom/2026-04-03/69cf87c254f00230c6d0afa9/resume.md")</f>
+        <f>HYPERLINK("by_company/nordstrom/2026-04-03/69cf87c254f00230c6d0afa9/resume.md","data/deliverables/resume_portfolio/by_company/nordstrom/2026-04-03/69cf87c254f00230c6d0afa9/resume.md")</f>
       </c>
       <c r="Q738"/>
       <c r="R738">
@@ -47587,7 +47587,7 @@
         </is>
       </c>
       <c r="P740">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gartner/2026-04-03/69ab43917e1fab39d382dc0b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gartner/2026-04-03/69ab43917e1fab39d382dc0b/resume.md")</f>
+        <f>HYPERLINK("by_company/gartner/2026-04-03/69ab43917e1fab39d382dc0b/resume.md","data/deliverables/resume_portfolio/by_company/gartner/2026-04-03/69ab43917e1fab39d382dc0b/resume.md")</f>
       </c>
       <c r="Q740"/>
       <c r="R740">
@@ -47653,7 +47653,7 @@
         </is>
       </c>
       <c r="P741">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/healthequity/2026-04-03/6997e0cece78e77b4fdc5857/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/healthequity/2026-04-03/6997e0cece78e77b4fdc5857/resume.md")</f>
+        <f>HYPERLINK("by_company/healthequity/2026-04-03/6997e0cece78e77b4fdc5857/resume.md","data/deliverables/resume_portfolio/by_company/healthequity/2026-04-03/6997e0cece78e77b4fdc5857/resume.md")</f>
       </c>
       <c r="Q741"/>
       <c r="R741">
@@ -47719,7 +47719,7 @@
         </is>
       </c>
       <c r="P742">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/doordash/2026-04-03/66a819dc6347bb7b60365ac3/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/doordash/2026-04-03/66a819dc6347bb7b60365ac3/resume.md")</f>
+        <f>HYPERLINK("by_company/doordash/2026-04-03/66a819dc6347bb7b60365ac3/resume.md","data/deliverables/resume_portfolio/by_company/doordash/2026-04-03/66a819dc6347bb7b60365ac3/resume.md")</f>
       </c>
       <c r="Q742"/>
       <c r="R742">
@@ -47843,7 +47843,7 @@
         </is>
       </c>
       <c r="P744">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/zendesk/2026-04-03/69cf642754f00230c6d096cb/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/zendesk/2026-04-03/69cf642754f00230c6d096cb/resume.md")</f>
+        <f>HYPERLINK("by_company/zendesk/2026-04-03/69cf642754f00230c6d096cb/resume.md","data/deliverables/resume_portfolio/by_company/zendesk/2026-04-03/69cf642754f00230c6d096cb/resume.md")</f>
       </c>
       <c r="Q744"/>
       <c r="R744">
@@ -47917,7 +47917,7 @@
         </is>
       </c>
       <c r="P745">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/69cf517ecdb525785fba14b7/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/69cf517ecdb525785fba14b7/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon/2026-04-03/69cf517ecdb525785fba14b7/resume.md","data/deliverables/resume_portfolio/by_company/amazon/2026-04-03/69cf517ecdb525785fba14b7/resume.md")</f>
       </c>
       <c r="Q745"/>
       <c r="R745">
@@ -48057,7 +48057,7 @@
         </is>
       </c>
       <c r="P747">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/uber/2026-04-03/69cf4cc3cdb525785fba1377/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/uber/2026-04-03/69cf4cc3cdb525785fba1377/resume.md")</f>
+        <f>HYPERLINK("by_company/uber/2026-04-03/69cf4cc3cdb525785fba1377/resume.md","data/deliverables/resume_portfolio/by_company/uber/2026-04-03/69cf4cc3cdb525785fba1377/resume.md")</f>
       </c>
       <c r="Q747"/>
       <c r="R747">
@@ -48123,7 +48123,7 @@
         </is>
       </c>
       <c r="P748">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/thermo-fisher-scientific/2026-04-02/69cf42f1398fb071abf8e4d0/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/thermo-fisher-scientific/2026-04-02/69cf42f1398fb071abf8e4d0/resume.md")</f>
+        <f>HYPERLINK("by_company/thermo-fisher-scientific/2026-04-02/69cf42f1398fb071abf8e4d0/resume.md","data/deliverables/resume_portfolio/by_company/thermo-fisher-scientific/2026-04-02/69cf42f1398fb071abf8e4d0/resume.md")</f>
       </c>
       <c r="Q748"/>
       <c r="R748">
@@ -48189,7 +48189,7 @@
         </is>
       </c>
       <c r="P749">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/apple/2026-04-02/69cf3064891d7b11cfcd0cb8/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/apple/2026-04-02/69cf3064891d7b11cfcd0cb8/resume.md")</f>
+        <f>HYPERLINK("by_company/apple/2026-04-02/69cf3064891d7b11cfcd0cb8/resume.md","data/deliverables/resume_portfolio/by_company/apple/2026-04-02/69cf3064891d7b11cfcd0cb8/resume.md")</f>
       </c>
       <c r="Q749"/>
       <c r="R749">
@@ -48255,7 +48255,7 @@
         </is>
       </c>
       <c r="P750">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nordstrom/2026-04-02/69cf2b35398fb071abf8cb0d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nordstrom/2026-04-02/69cf2b35398fb071abf8cb0d/resume.md")</f>
+        <f>HYPERLINK("by_company/nordstrom/2026-04-02/69cf2b35398fb071abf8cb0d/resume.md","data/deliverables/resume_portfolio/by_company/nordstrom/2026-04-02/69cf2b35398fb071abf8cb0d/resume.md")</f>
       </c>
       <c r="Q750"/>
       <c r="R750">
@@ -48321,7 +48321,7 @@
         </is>
       </c>
       <c r="P751">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/thomson-reuters/2026-04-02/69cf246ccfdc6132f942fe07/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/thomson-reuters/2026-04-02/69cf246ccfdc6132f942fe07/resume.md")</f>
+        <f>HYPERLINK("by_company/thomson-reuters/2026-04-02/69cf246ccfdc6132f942fe07/resume.md","data/deliverables/resume_portfolio/by_company/thomson-reuters/2026-04-02/69cf246ccfdc6132f942fe07/resume.md")</f>
       </c>
       <c r="Q751"/>
       <c r="R751">
@@ -48503,7 +48503,7 @@
         </is>
       </c>
       <c r="P754">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/informatica/2026-04-02/69cf1b52891d7b11cfcd00b6/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/informatica/2026-04-02/69cf1b52891d7b11cfcd00b6/resume.md")</f>
+        <f>HYPERLINK("by_company/informatica/2026-04-02/69cf1b52891d7b11cfcd00b6/resume.md","data/deliverables/resume_portfolio/by_company/informatica/2026-04-02/69cf1b52891d7b11cfcd00b6/resume.md")</f>
       </c>
       <c r="Q754"/>
       <c r="R754">
@@ -48693,7 +48693,7 @@
         </is>
       </c>
       <c r="P757">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/arxada/2026-04-02/69cf1aef366bb95ba5512bc7/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/arxada/2026-04-02/69cf1aef366bb95ba5512bc7/resume.md")</f>
+        <f>HYPERLINK("by_company/arxada/2026-04-02/69cf1aef366bb95ba5512bc7/resume.md","data/deliverables/resume_portfolio/by_company/arxada/2026-04-02/69cf1aef366bb95ba5512bc7/resume.md")</f>
       </c>
       <c r="Q757"/>
       <c r="R757">
@@ -48759,7 +48759,7 @@
         </is>
       </c>
       <c r="P758">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/phenom/2026-04-02/69cf1ae8cdb525785fb9ec17/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/phenom/2026-04-02/69cf1ae8cdb525785fb9ec17/resume.md")</f>
+        <f>HYPERLINK("by_company/phenom/2026-04-02/69cf1ae8cdb525785fb9ec17/resume.md","data/deliverables/resume_portfolio/by_company/phenom/2026-04-02/69cf1ae8cdb525785fb9ec17/resume.md")</f>
       </c>
       <c r="Q758"/>
       <c r="R758">
@@ -48955,7 +48955,7 @@
         </is>
       </c>
       <c r="P761">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/avive-solutions-inc/2026-04-02/69cf16be54f00230c6d066d1/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/avive-solutions-inc/2026-04-02/69cf16be54f00230c6d066d1/resume.md")</f>
+        <f>HYPERLINK("by_company/avive-solutions-inc/2026-04-02/69cf16be54f00230c6d066d1/resume.md","data/deliverables/resume_portfolio/by_company/avive-solutions-inc/2026-04-02/69cf16be54f00230c6d066d1/resume.md")</f>
       </c>
       <c r="Q761"/>
       <c r="R761">
@@ -49021,7 +49021,7 @@
         </is>
       </c>
       <c r="P762">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/chainguard/2026-04-02/69cf16b754f00230c6d066cf/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/chainguard/2026-04-02/69cf16b754f00230c6d066cf/resume.md")</f>
+        <f>HYPERLINK("by_company/chainguard/2026-04-02/69cf16b754f00230c6d066cf/resume.md","data/deliverables/resume_portfolio/by_company/chainguard/2026-04-02/69cf16b754f00230c6d066cf/resume.md")</f>
       </c>
       <c r="Q762"/>
       <c r="R762">
@@ -49087,7 +49087,7 @@
         </is>
       </c>
       <c r="P763">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/avive-solutions-inc/2026-04-02/69cf15abcdb525785fb9ea2b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/avive-solutions-inc/2026-04-02/69cf15abcdb525785fb9ea2b/resume.md")</f>
+        <f>HYPERLINK("by_company/avive-solutions-inc/2026-04-02/69cf15abcdb525785fb9ea2b/resume.md","data/deliverables/resume_portfolio/by_company/avive-solutions-inc/2026-04-02/69cf15abcdb525785fb9ea2b/resume.md")</f>
       </c>
       <c r="Q763"/>
       <c r="R763">
@@ -49211,7 +49211,7 @@
         </is>
       </c>
       <c r="P765">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/leidos/2026-04-02/69cf157e54f00230c6d06678/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/leidos/2026-04-02/69cf157e54f00230c6d06678/resume.md")</f>
+        <f>HYPERLINK("by_company/leidos/2026-04-02/69cf157e54f00230c6d06678/resume.md","data/deliverables/resume_portfolio/by_company/leidos/2026-04-02/69cf157e54f00230c6d06678/resume.md")</f>
       </c>
       <c r="Q765"/>
       <c r="R765">
@@ -49451,7 +49451,7 @@
         </is>
       </c>
       <c r="P769">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/trimedx/2026-04-02/69cf12e4891d7b11cfccfd93/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/trimedx/2026-04-02/69cf12e4891d7b11cfccfd93/resume.md")</f>
+        <f>HYPERLINK("by_company/trimedx/2026-04-02/69cf12e4891d7b11cfccfd93/resume.md","data/deliverables/resume_portfolio/by_company/trimedx/2026-04-02/69cf12e4891d7b11cfccfd93/resume.md")</f>
       </c>
       <c r="Q769"/>
       <c r="R769">
@@ -49583,7 +49583,7 @@
         </is>
       </c>
       <c r="P771">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/leidos/2026-04-02/69cf10f1398fb071abf8c27c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/leidos/2026-04-02/69cf10f1398fb071abf8c27c/resume.md")</f>
+        <f>HYPERLINK("by_company/leidos/2026-04-02/69cf10f1398fb071abf8c27c/resume.md","data/deliverables/resume_portfolio/by_company/leidos/2026-04-02/69cf10f1398fb071abf8c27c/resume.md")</f>
       </c>
       <c r="Q771"/>
       <c r="R771">
@@ -49649,7 +49649,7 @@
         </is>
       </c>
       <c r="P772">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-02/69cf0f7954f00230c6d064d7/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-02/69cf0f7954f00230c6d064d7/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon-web-services-aws/2026-04-02/69cf0f7954f00230c6d064d7/resume.md","data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-02/69cf0f7954f00230c6d064d7/resume.md")</f>
       </c>
       <c r="Q772"/>
       <c r="R772">
@@ -49715,7 +49715,7 @@
         </is>
       </c>
       <c r="P773">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/effectual/2026-04-02/69cf0f74891d7b11cfccfd10/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/effectual/2026-04-02/69cf0f74891d7b11cfccfd10/resume.md")</f>
+        <f>HYPERLINK("by_company/effectual/2026-04-02/69cf0f74891d7b11cfccfd10/resume.md","data/deliverables/resume_portfolio/by_company/effectual/2026-04-02/69cf0f74891d7b11cfccfd10/resume.md")</f>
       </c>
       <c r="Q773"/>
       <c r="R773">
@@ -49781,7 +49781,7 @@
         </is>
       </c>
       <c r="P774">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/doit/2026-04-02/69cf0f47891d7b11cfccfc1a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/doit/2026-04-02/69cf0f47891d7b11cfccfc1a/resume.md")</f>
+        <f>HYPERLINK("by_company/doit/2026-04-02/69cf0f47891d7b11cfccfc1a/resume.md","data/deliverables/resume_portfolio/by_company/doit/2026-04-02/69cf0f47891d7b11cfccfc1a/resume.md")</f>
       </c>
       <c r="Q774"/>
       <c r="R774">
@@ -50029,7 +50029,7 @@
         </is>
       </c>
       <c r="P778">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/pacific-life/2026-04-02/69cf09a0cfdc6132f942ef9a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/pacific-life/2026-04-02/69cf09a0cfdc6132f942ef9a/resume.md")</f>
+        <f>HYPERLINK("by_company/pacific-life/2026-04-02/69cf09a0cfdc6132f942ef9a/resume.md","data/deliverables/resume_portfolio/by_company/pacific-life/2026-04-02/69cf09a0cfdc6132f942ef9a/resume.md")</f>
       </c>
       <c r="Q778"/>
       <c r="R778">
@@ -50153,7 +50153,7 @@
         </is>
       </c>
       <c r="P780">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/barracuda/2026-04-02/69cf068acfdc6132f942eed3/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/barracuda/2026-04-02/69cf068acfdc6132f942eed3/resume.md")</f>
+        <f>HYPERLINK("by_company/barracuda/2026-04-02/69cf068acfdc6132f942eed3/resume.md","data/deliverables/resume_portfolio/by_company/barracuda/2026-04-02/69cf068acfdc6132f942eed3/resume.md")</f>
       </c>
       <c r="Q780"/>
       <c r="R780">
@@ -50219,7 +50219,7 @@
         </is>
       </c>
       <c r="P781">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/the-walt-disney-company/2026-04-02/69cf04ec891d7b11cfccf4fb/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/the-walt-disney-company/2026-04-02/69cf04ec891d7b11cfccf4fb/resume.md")</f>
+        <f>HYPERLINK("by_company/the-walt-disney-company/2026-04-02/69cf04ec891d7b11cfccf4fb/resume.md","data/deliverables/resume_portfolio/by_company/the-walt-disney-company/2026-04-02/69cf04ec891d7b11cfccf4fb/resume.md")</f>
       </c>
       <c r="Q781"/>
       <c r="R781">
@@ -50343,7 +50343,7 @@
         </is>
       </c>
       <c r="P783">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/whsmith-north-america/2026-04-02/69cf03e654f00230c6d05ca5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/whsmith-north-america/2026-04-02/69cf03e654f00230c6d05ca5/resume.md")</f>
+        <f>HYPERLINK("by_company/whsmith-north-america/2026-04-02/69cf03e654f00230c6d05ca5/resume.md","data/deliverables/resume_portfolio/by_company/whsmith-north-america/2026-04-02/69cf03e654f00230c6d05ca5/resume.md")</f>
       </c>
       <c r="Q783"/>
       <c r="R783">
@@ -50409,7 +50409,7 @@
         </is>
       </c>
       <c r="P784">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/marquette-university/2026-04-02/69cf03d3cfdc6132f942ee22/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/marquette-university/2026-04-02/69cf03d3cfdc6132f942ee22/resume.md")</f>
+        <f>HYPERLINK("by_company/marquette-university/2026-04-02/69cf03d3cfdc6132f942ee22/resume.md","data/deliverables/resume_portfolio/by_company/marquette-university/2026-04-02/69cf03d3cfdc6132f942ee22/resume.md")</f>
       </c>
       <c r="Q784"/>
       <c r="R784">
@@ -50483,7 +50483,7 @@
         </is>
       </c>
       <c r="P785">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tetramem-accelerate-the-world/2026-04-02/69cf034a398fb071abf8b9d5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tetramem-accelerate-the-world/2026-04-02/69cf034a398fb071abf8b9d5/resume.md")</f>
+        <f>HYPERLINK("by_company/tetramem-accelerate-the-world/2026-04-02/69cf034a398fb071abf8b9d5/resume.md","data/deliverables/resume_portfolio/by_company/tetramem-accelerate-the-world/2026-04-02/69cf034a398fb071abf8b9d5/resume.md")</f>
       </c>
       <c r="Q785"/>
       <c r="R785">
@@ -50665,7 +50665,7 @@
         </is>
       </c>
       <c r="P788">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-02/69cefaec891d7b11cfccefe6/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-02/69cefaec891d7b11cfccefe6/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon-web-services-aws/2026-04-02/69cefaec891d7b11cfccefe6/resume.md","data/deliverables/resume_portfolio/by_company/amazon-web-services-aws/2026-04-02/69cefaec891d7b11cfccefe6/resume.md")</f>
       </c>
       <c r="Q788"/>
       <c r="R788">
@@ -50731,7 +50731,7 @@
         </is>
       </c>
       <c r="P789">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kforce-inc/2026-04-02/69cefaa7cdb525785fb9dbb0/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kforce-inc/2026-04-02/69cefaa7cdb525785fb9dbb0/resume.md")</f>
+        <f>HYPERLINK("by_company/kforce-inc/2026-04-02/69cefaa7cdb525785fb9dbb0/resume.md","data/deliverables/resume_portfolio/by_company/kforce-inc/2026-04-02/69cefaa7cdb525785fb9dbb0/resume.md")</f>
       </c>
       <c r="Q789"/>
       <c r="R789">
@@ -50797,7 +50797,7 @@
         </is>
       </c>
       <c r="P790">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fundview/2026-04-02/69cefa9bcdb525785fb9db59/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fundview/2026-04-02/69cefa9bcdb525785fb9db59/resume.md")</f>
+        <f>HYPERLINK("by_company/fundview/2026-04-02/69cefa9bcdb525785fb9db59/resume.md","data/deliverables/resume_portfolio/by_company/fundview/2026-04-02/69cefa9bcdb525785fb9db59/resume.md")</f>
       </c>
       <c r="Q790"/>
       <c r="R790">
@@ -50995,7 +50995,7 @@
         </is>
       </c>
       <c r="P793">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/geico/2026-04-02/69cefa7454f00230c6d0570e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/geico/2026-04-02/69cefa7454f00230c6d0570e/resume.md")</f>
+        <f>HYPERLINK("by_company/geico/2026-04-02/69cefa7454f00230c6d0570e/resume.md","data/deliverables/resume_portfolio/by_company/geico/2026-04-02/69cefa7454f00230c6d0570e/resume.md")</f>
       </c>
       <c r="Q793"/>
       <c r="R793">
@@ -51069,7 +51069,7 @@
         </is>
       </c>
       <c r="P794">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-02/69cef58acdb525785fb9d9f4/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-02/69cef58acdb525785fb9d9f4/resume.md")</f>
+        <f>HYPERLINK("by_company/google/2026-04-02/69cef58acdb525785fb9d9f4/resume.md","data/deliverables/resume_portfolio/by_company/google/2026-04-02/69cef58acdb525785fb9d9f4/resume.md")</f>
       </c>
       <c r="Q794"/>
       <c r="R794">
@@ -51193,7 +51193,7 @@
         </is>
       </c>
       <c r="P796">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mastercard/2026-04-02/69cef4d8398fb071abf8b390/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mastercard/2026-04-02/69cef4d8398fb071abf8b390/resume.md")</f>
+        <f>HYPERLINK("by_company/mastercard/2026-04-02/69cef4d8398fb071abf8b390/resume.md","data/deliverables/resume_portfolio/by_company/mastercard/2026-04-02/69cef4d8398fb071abf8b390/resume.md")</f>
       </c>
       <c r="Q796"/>
       <c r="R796">
@@ -51259,7 +51259,7 @@
         </is>
       </c>
       <c r="P797">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/pci-energy-solutions/2026-04-02/69cef3bd366bb95ba55118c9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/pci-energy-solutions/2026-04-02/69cef3bd366bb95ba55118c9/resume.md")</f>
+        <f>HYPERLINK("by_company/pci-energy-solutions/2026-04-02/69cef3bd366bb95ba55118c9/resume.md","data/deliverables/resume_portfolio/by_company/pci-energy-solutions/2026-04-02/69cef3bd366bb95ba55118c9/resume.md")</f>
       </c>
       <c r="Q797"/>
       <c r="R797">
@@ -51325,7 +51325,7 @@
         </is>
       </c>
       <c r="P798">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/linkedin/2026-04-02/69cef362398fb071abf8b1bb/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/linkedin/2026-04-02/69cef362398fb071abf8b1bb/resume.md")</f>
+        <f>HYPERLINK("by_company/linkedin/2026-04-02/69cef362398fb071abf8b1bb/resume.md","data/deliverables/resume_portfolio/by_company/linkedin/2026-04-02/69cef362398fb071abf8b1bb/resume.md")</f>
       </c>
       <c r="Q798"/>
       <c r="R798">
@@ -51391,7 +51391,7 @@
         </is>
       </c>
       <c r="P799">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/csg/2026-04-02/69cef33e398fb071abf8b0b1/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/csg/2026-04-02/69cef33e398fb071abf8b0b1/resume.md")</f>
+        <f>HYPERLINK("by_company/csg/2026-04-02/69cef33e398fb071abf8b0b1/resume.md","data/deliverables/resume_portfolio/by_company/csg/2026-04-02/69cef33e398fb071abf8b0b1/resume.md")</f>
       </c>
       <c r="Q799"/>
       <c r="R799">
@@ -51457,7 +51457,7 @@
         </is>
       </c>
       <c r="P800">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/uber/2026-04-02/69cef33654f00230c6d051a9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/uber/2026-04-02/69cef33654f00230c6d051a9/resume.md")</f>
+        <f>HYPERLINK("by_company/uber/2026-04-02/69cef33654f00230c6d051a9/resume.md","data/deliverables/resume_portfolio/by_company/uber/2026-04-02/69cef33654f00230c6d051a9/resume.md")</f>
       </c>
       <c r="Q800"/>
       <c r="R800">
@@ -51531,7 +51531,7 @@
         </is>
       </c>
       <c r="P801">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/uber/2026-04-02/69cef32d54f00230c6d05152/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/uber/2026-04-02/69cef32d54f00230c6d05152/resume.md")</f>
+        <f>HYPERLINK("by_company/uber/2026-04-02/69cef32d54f00230c6d05152/resume.md","data/deliverables/resume_portfolio/by_company/uber/2026-04-02/69cef32d54f00230c6d05152/resume.md")</f>
       </c>
       <c r="Q801"/>
       <c r="R801">
@@ -51677,7 +51677,7 @@
         </is>
       </c>
       <c r="P803">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-02/6972333747b64f4e963e75ea/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/google/2026-04-02/6972333747b64f4e963e75ea/resume.md")</f>
+        <f>HYPERLINK("by_company/google/2026-04-02/6972333747b64f4e963e75ea/resume.md","data/deliverables/resume_portfolio/by_company/google/2026-04-02/6972333747b64f4e963e75ea/resume.md")</f>
       </c>
       <c r="Q803"/>
       <c r="R803">
@@ -51883,7 +51883,7 @@
         </is>
       </c>
       <c r="P806">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/discord/2026-04-02/69ceefc154f00230c6d04e93/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/discord/2026-04-02/69ceefc154f00230c6d04e93/resume.md")</f>
+        <f>HYPERLINK("by_company/discord/2026-04-02/69ceefc154f00230c6d04e93/resume.md","data/deliverables/resume_portfolio/by_company/discord/2026-04-02/69ceefc154f00230c6d04e93/resume.md")</f>
       </c>
       <c r="Q806"/>
       <c r="R806">
@@ -51949,7 +51949,7 @@
         </is>
       </c>
       <c r="P807">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/distyl/2026-04-02/69992533e0bddb6acac82bf6/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/distyl/2026-04-02/69992533e0bddb6acac82bf6/resume.md")</f>
+        <f>HYPERLINK("by_company/distyl/2026-04-02/69992533e0bddb6acac82bf6/resume.md","data/deliverables/resume_portfolio/by_company/distyl/2026-04-02/69992533e0bddb6acac82bf6/resume.md")</f>
       </c>
       <c r="Q807"/>
       <c r="R807">
@@ -52203,7 +52203,7 @@
         </is>
       </c>
       <c r="P811">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/spark-foundry/2026-04-02/69ceee88398fb071abf8ac37/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/spark-foundry/2026-04-02/69ceee88398fb071abf8ac37/resume.md")</f>
+        <f>HYPERLINK("by_company/spark-foundry/2026-04-02/69ceee88398fb071abf8ac37/resume.md","data/deliverables/resume_portfolio/by_company/spark-foundry/2026-04-02/69ceee88398fb071abf8ac37/resume.md")</f>
       </c>
       <c r="Q811"/>
       <c r="R811">
@@ -52277,7 +52277,7 @@
         </is>
       </c>
       <c r="P812">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sumo-logic/2026-04-02/6974392337785856350e33b5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sumo-logic/2026-04-02/6974392337785856350e33b5/resume.md")</f>
+        <f>HYPERLINK("by_company/sumo-logic/2026-04-02/6974392337785856350e33b5/resume.md","data/deliverables/resume_portfolio/by_company/sumo-logic/2026-04-02/6974392337785856350e33b5/resume.md")</f>
       </c>
       <c r="Q812"/>
       <c r="R812">
@@ -52343,7 +52343,7 @@
         </is>
       </c>
       <c r="P813">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mongodb/2026-04-02/6986c6398ca8121a3a693ca4/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mongodb/2026-04-02/6986c6398ca8121a3a693ca4/resume.md")</f>
+        <f>HYPERLINK("by_company/mongodb/2026-04-02/6986c6398ca8121a3a693ca4/resume.md","data/deliverables/resume_portfolio/by_company/mongodb/2026-04-02/6986c6398ca8121a3a693ca4/resume.md")</f>
       </c>
       <c r="Q813"/>
       <c r="R813">
@@ -52483,7 +52483,7 @@
         </is>
       </c>
       <c r="P815">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualitest-acq/2026-04-02/69ceeabf54f00230c6d04cc9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualitest-acq/2026-04-02/69ceeabf54f00230c6d04cc9/resume.md")</f>
+        <f>HYPERLINK("by_company/qualitest-acq/2026-04-02/69ceeabf54f00230c6d04cc9/resume.md","data/deliverables/resume_portfolio/by_company/qualitest-acq/2026-04-02/69ceeabf54f00230c6d04cc9/resume.md")</f>
       </c>
       <c r="Q815"/>
       <c r="R815">
@@ -52607,7 +52607,7 @@
         </is>
       </c>
       <c r="P817">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/lucid-services-group/2026-04-02/69cee736366bb95ba5510ee9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/lucid-services-group/2026-04-02/69cee736366bb95ba5510ee9/resume.md")</f>
+        <f>HYPERLINK("by_company/lucid-services-group/2026-04-02/69cee736366bb95ba5510ee9/resume.md","data/deliverables/resume_portfolio/by_company/lucid-services-group/2026-04-02/69cee736366bb95ba5510ee9/resume.md")</f>
       </c>
       <c r="Q817"/>
       <c r="R817">
@@ -52739,7 +52739,7 @@
         </is>
       </c>
       <c r="P819">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/general-motors/2026-04-02/69cee70954f00230c6d04ba2/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/general-motors/2026-04-02/69cee70954f00230c6d04ba2/resume.md")</f>
+        <f>HYPERLINK("by_company/general-motors/2026-04-02/69cee70954f00230c6d04ba2/resume.md","data/deliverables/resume_portfolio/by_company/general-motors/2026-04-02/69cee70954f00230c6d04ba2/resume.md")</f>
       </c>
       <c r="Q819"/>
       <c r="R819">
@@ -52863,7 +52863,7 @@
         </is>
       </c>
       <c r="P821">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cloud-resources-llc/2026-04-02/69cf0660398fb071abf8baf4/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cloud-resources-llc/2026-04-02/69cf0660398fb071abf8baf4/resume.md")</f>
+        <f>HYPERLINK("by_company/cloud-resources-llc/2026-04-02/69cf0660398fb071abf8baf4/resume.md","data/deliverables/resume_portfolio/by_company/cloud-resources-llc/2026-04-02/69cf0660398fb071abf8baf4/resume.md")</f>
       </c>
       <c r="Q821"/>
       <c r="R821">
@@ -52929,7 +52929,7 @@
         </is>
       </c>
       <c r="P822">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/thomson-reuters/2026-04-02/69cee41e54f00230c6d047c8/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/thomson-reuters/2026-04-02/69cee41e54f00230c6d047c8/resume.md")</f>
+        <f>HYPERLINK("by_company/thomson-reuters/2026-04-02/69cee41e54f00230c6d047c8/resume.md","data/deliverables/resume_portfolio/by_company/thomson-reuters/2026-04-02/69cee41e54f00230c6d047c8/resume.md")</f>
       </c>
       <c r="Q822"/>
       <c r="R822">
@@ -52995,7 +52995,7 @@
         </is>
       </c>
       <c r="P823">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/wellington-management/2026-04-02/69cee312366bb95ba5510a90/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/wellington-management/2026-04-02/69cee312366bb95ba5510a90/resume.md")</f>
+        <f>HYPERLINK("by_company/wellington-management/2026-04-02/69cee312366bb95ba5510a90/resume.md","data/deliverables/resume_portfolio/by_company/wellington-management/2026-04-02/69cee312366bb95ba5510a90/resume.md")</f>
       </c>
       <c r="Q823"/>
       <c r="R823">
@@ -53119,7 +53119,7 @@
         </is>
       </c>
       <c r="P825">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/venmo/2026-04-02/69cee195cdb525785fb9c95b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/venmo/2026-04-02/69cee195cdb525785fb9c95b/resume.md")</f>
+        <f>HYPERLINK("by_company/venmo/2026-04-02/69cee195cdb525785fb9c95b/resume.md","data/deliverables/resume_portfolio/by_company/venmo/2026-04-02/69cee195cdb525785fb9c95b/resume.md")</f>
       </c>
       <c r="Q825"/>
       <c r="R825">
@@ -53185,7 +53185,7 @@
         </is>
       </c>
       <c r="P826">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/charles-schwab/2026-04-02/69cee192cfdc6132f942d759/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/charles-schwab/2026-04-02/69cee192cfdc6132f942d759/resume.md")</f>
+        <f>HYPERLINK("by_company/charles-schwab/2026-04-02/69cee192cfdc6132f942d759/resume.md","data/deliverables/resume_portfolio/by_company/charles-schwab/2026-04-02/69cee192cfdc6132f942d759/resume.md")</f>
       </c>
       <c r="Q826"/>
       <c r="R826">
@@ -53317,7 +53317,7 @@
         </is>
       </c>
       <c r="P828">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-02/69cee13c891d7b11cfccdb84/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-02/69cee13c891d7b11cfccdb84/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-02/69cee13c891d7b11cfccdb84/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-02/69cee13c891d7b11cfccdb84/resume.md")</f>
       </c>
       <c r="Q828"/>
       <c r="R828">
@@ -53383,7 +53383,7 @@
         </is>
       </c>
       <c r="P829">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kpmg-us/2026-04-02/69cee12dcdb525785fb9c778/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kpmg-us/2026-04-02/69cee12dcdb525785fb9c778/resume.md")</f>
+        <f>HYPERLINK("by_company/kpmg-us/2026-04-02/69cee12dcdb525785fb9c778/resume.md","data/deliverables/resume_portfolio/by_company/kpmg-us/2026-04-02/69cee12dcdb525785fb9c778/resume.md")</f>
       </c>
       <c r="Q829"/>
       <c r="R829">
@@ -53449,7 +53449,7 @@
         </is>
       </c>
       <c r="P830">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-02/69cee12854f00230c6d04385/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-02/69cee12854f00230c6d04385/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-02/69cee12854f00230c6d04385/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-02/69cee12854f00230c6d04385/resume.md")</f>
       </c>
       <c r="Q830"/>
       <c r="R830">
@@ -53573,7 +53573,7 @@
         </is>
       </c>
       <c r="P832">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/o3-technology-solutions/2026-04-02/69ceff69398fb071abf8b8c4/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/o3-technology-solutions/2026-04-02/69ceff69398fb071abf8b8c4/resume.md")</f>
+        <f>HYPERLINK("by_company/o3-technology-solutions/2026-04-02/69ceff69398fb071abf8b8c4/resume.md","data/deliverables/resume_portfolio/by_company/o3-technology-solutions/2026-04-02/69ceff69398fb071abf8b8c4/resume.md")</f>
       </c>
       <c r="Q832"/>
       <c r="R832">
@@ -53763,7 +53763,7 @@
         </is>
       </c>
       <c r="P835">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/yamaha-motor-corporation-usa/2026-04-02/69cede07cdb525785fb9c5ee/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/yamaha-motor-corporation-usa/2026-04-02/69cede07cdb525785fb9c5ee/resume.md")</f>
+        <f>HYPERLINK("by_company/yamaha-motor-corporation-usa/2026-04-02/69cede07cdb525785fb9c5ee/resume.md","data/deliverables/resume_portfolio/by_company/yamaha-motor-corporation-usa/2026-04-02/69cede07cdb525785fb9c5ee/resume.md")</f>
       </c>
       <c r="Q835"/>
       <c r="R835">
@@ -53829,7 +53829,7 @@
         </is>
       </c>
       <c r="P836">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/wealthcounsel-llc/2026-04-02/69ceddfecdb525785fb9c5e2/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/wealthcounsel-llc/2026-04-02/69ceddfecdb525785fb9c5e2/resume.md")</f>
+        <f>HYPERLINK("by_company/wealthcounsel-llc/2026-04-02/69ceddfecdb525785fb9c5e2/resume.md","data/deliverables/resume_portfolio/by_company/wealthcounsel-llc/2026-04-02/69ceddfecdb525785fb9c5e2/resume.md")</f>
       </c>
       <c r="Q836"/>
       <c r="R836">
@@ -53903,7 +53903,7 @@
         </is>
       </c>
       <c r="P837">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualitest/2026-04-02/69cedd5854f00230c6d0416e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualitest/2026-04-02/69cedd5854f00230c6d0416e/resume.md")</f>
+        <f>HYPERLINK("by_company/qualitest/2026-04-02/69cedd5854f00230c6d0416e/resume.md","data/deliverables/resume_portfolio/by_company/qualitest/2026-04-02/69cedd5854f00230c6d0416e/resume.md")</f>
       </c>
       <c r="Q837"/>
       <c r="R837">
@@ -53969,7 +53969,7 @@
         </is>
       </c>
       <c r="P838">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sleeper/2026-04-02/69cedd2f891d7b11cfccd910/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sleeper/2026-04-02/69cedd2f891d7b11cfccd910/resume.md")</f>
+        <f>HYPERLINK("by_company/sleeper/2026-04-02/69cedd2f891d7b11cfccd910/resume.md","data/deliverables/resume_portfolio/by_company/sleeper/2026-04-02/69cedd2f891d7b11cfccd910/resume.md")</f>
       </c>
       <c r="Q838"/>
       <c r="R838">
@@ -54035,7 +54035,7 @@
         </is>
       </c>
       <c r="P839">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gei-consultants-inc/2026-04-02/69ced93b891d7b11cfccd722/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gei-consultants-inc/2026-04-02/69ced93b891d7b11cfccd722/resume.md")</f>
+        <f>HYPERLINK("by_company/gei-consultants-inc/2026-04-02/69ced93b891d7b11cfccd722/resume.md","data/deliverables/resume_portfolio/by_company/gei-consultants-inc/2026-04-02/69ced93b891d7b11cfccd722/resume.md")</f>
       </c>
       <c r="Q839"/>
       <c r="R839">
@@ -54225,7 +54225,7 @@
         </is>
       </c>
       <c r="P842">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-02/69ced753398fb071abf896e5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-02/69ced753398fb071abf896e5/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon/2026-04-02/69ced753398fb071abf896e5/resume.md","data/deliverables/resume_portfolio/by_company/amazon/2026-04-02/69ced753398fb071abf896e5/resume.md")</f>
       </c>
       <c r="Q842"/>
       <c r="R842">
@@ -54349,7 +54349,7 @@
         </is>
       </c>
       <c r="P844">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/children-s-hospital-colorado/2026-04-02/69ceeb15398fb071abf8ab1a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/children-s-hospital-colorado/2026-04-02/69ceeb15398fb071abf8ab1a/resume.md")</f>
+        <f>HYPERLINK("by_company/children-s-hospital-colorado/2026-04-02/69ceeb15398fb071abf8ab1a/resume.md","data/deliverables/resume_portfolio/by_company/children-s-hospital-colorado/2026-04-02/69ceeb15398fb071abf8ab1a/resume.md")</f>
       </c>
       <c r="Q844"/>
       <c r="R844">
@@ -54415,7 +54415,7 @@
         </is>
       </c>
       <c r="P845">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/oati/2026-04-02/695d85baf5f3c43f38e25c48/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/oati/2026-04-02/695d85baf5f3c43f38e25c48/resume.md")</f>
+        <f>HYPERLINK("by_company/oati/2026-04-02/695d85baf5f3c43f38e25c48/resume.md","data/deliverables/resume_portfolio/by_company/oati/2026-04-02/695d85baf5f3c43f38e25c48/resume.md")</f>
       </c>
       <c r="Q845"/>
       <c r="R845">
@@ -54481,7 +54481,7 @@
         </is>
       </c>
       <c r="P846">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/quantiphi/2026-04-02/69c8dd02b773006330b8256e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/quantiphi/2026-04-02/69c8dd02b773006330b8256e/resume.md")</f>
+        <f>HYPERLINK("by_company/quantiphi/2026-04-02/69c8dd02b773006330b8256e/resume.md","data/deliverables/resume_portfolio/by_company/quantiphi/2026-04-02/69c8dd02b773006330b8256e/resume.md")</f>
       </c>
       <c r="Q846"/>
       <c r="R846">
@@ -54555,7 +54555,7 @@
         </is>
       </c>
       <c r="P847">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/affirm/2026-04-02/697665d1bc8e722e7b1afd8d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/affirm/2026-04-02/697665d1bc8e722e7b1afd8d/resume.md")</f>
+        <f>HYPERLINK("by_company/affirm/2026-04-02/697665d1bc8e722e7b1afd8d/resume.md","data/deliverables/resume_portfolio/by_company/affirm/2026-04-02/697665d1bc8e722e7b1afd8d/resume.md")</f>
       </c>
       <c r="Q847"/>
       <c r="R847">
@@ -54745,7 +54745,7 @@
         </is>
       </c>
       <c r="P850">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ericsson/2026-04-02/69cee3a4cfdc6132f942d986/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ericsson/2026-04-02/69cee3a4cfdc6132f942d986/resume.md")</f>
+        <f>HYPERLINK("by_company/ericsson/2026-04-02/69cee3a4cfdc6132f942d986/resume.md","data/deliverables/resume_portfolio/by_company/ericsson/2026-04-02/69cee3a4cfdc6132f942d986/resume.md")</f>
       </c>
       <c r="Q850"/>
       <c r="R850">
@@ -54811,7 +54811,7 @@
         </is>
       </c>
       <c r="P851">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/quantiphi/2026-04-02/698f5d8e0cc8ea15f1d9dfa1/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/quantiphi/2026-04-02/698f5d8e0cc8ea15f1d9dfa1/resume.md")</f>
+        <f>HYPERLINK("by_company/quantiphi/2026-04-02/698f5d8e0cc8ea15f1d9dfa1/resume.md","data/deliverables/resume_portfolio/by_company/quantiphi/2026-04-02/698f5d8e0cc8ea15f1d9dfa1/resume.md")</f>
       </c>
       <c r="Q851"/>
       <c r="R851">
@@ -54935,7 +54935,7 @@
         </is>
       </c>
       <c r="P853">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/crestron-electronics/2026-04-02/69cecea5cdb525785fb9b99f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/crestron-electronics/2026-04-02/69cecea5cdb525785fb9b99f/resume.md")</f>
+        <f>HYPERLINK("by_company/crestron-electronics/2026-04-02/69cecea5cdb525785fb9b99f/resume.md","data/deliverables/resume_portfolio/by_company/crestron-electronics/2026-04-02/69cecea5cdb525785fb9b99f/resume.md")</f>
       </c>
       <c r="Q853"/>
       <c r="R853">
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="P854">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/palantir-technologies/2026-04-02/69c4fe43d5a1016e98dc6966/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/palantir-technologies/2026-04-02/69c4fe43d5a1016e98dc6966/resume.md")</f>
+        <f>HYPERLINK("by_company/palantir-technologies/2026-04-02/69c4fe43d5a1016e98dc6966/resume.md","data/deliverables/resume_portfolio/by_company/palantir-technologies/2026-04-02/69c4fe43d5a1016e98dc6966/resume.md")</f>
       </c>
       <c r="Q854"/>
       <c r="R854">
@@ -55067,7 +55067,7 @@
         </is>
       </c>
       <c r="P855">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hcl-global-systems-inc/2026-04-02/69cf1865cfdc6132f942f8cb/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hcl-global-systems-inc/2026-04-02/69cf1865cfdc6132f942f8cb/resume.md")</f>
+        <f>HYPERLINK("by_company/hcl-global-systems-inc/2026-04-02/69cf1865cfdc6132f942f8cb/resume.md","data/deliverables/resume_portfolio/by_company/hcl-global-systems-inc/2026-04-02/69cf1865cfdc6132f942f8cb/resume.md")</f>
       </c>
       <c r="Q855"/>
       <c r="R855">
@@ -55133,7 +55133,7 @@
         </is>
       </c>
       <c r="P856">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/saferide-health/2026-04-02/69cec927cdb525785fb9b78b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/saferide-health/2026-04-02/69cec927cdb525785fb9b78b/resume.md")</f>
+        <f>HYPERLINK("by_company/saferide-health/2026-04-02/69cec927cdb525785fb9b78b/resume.md","data/deliverables/resume_portfolio/by_company/saferide-health/2026-04-02/69cec927cdb525785fb9b78b/resume.md")</f>
       </c>
       <c r="Q856"/>
       <c r="R856">
@@ -55199,7 +55199,7 @@
         </is>
       </c>
       <c r="P857">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/u-s-bank/2026-04-02/69cec8ed54f00230c6d0329f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/u-s-bank/2026-04-02/69cec8ed54f00230c6d0329f/resume.md")</f>
+        <f>HYPERLINK("by_company/u-s-bank/2026-04-02/69cec8ed54f00230c6d0329f/resume.md","data/deliverables/resume_portfolio/by_company/u-s-bank/2026-04-02/69cec8ed54f00230c6d0329f/resume.md")</f>
       </c>
       <c r="Q857"/>
       <c r="R857">
@@ -55273,7 +55273,7 @@
         </is>
       </c>
       <c r="P858">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/bloomberg/2026-04-02/69cedb88366bb95ba55103e5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/bloomberg/2026-04-02/69cedb88366bb95ba55103e5/resume.md")</f>
+        <f>HYPERLINK("by_company/bloomberg/2026-04-02/69cedb88366bb95ba55103e5/resume.md","data/deliverables/resume_portfolio/by_company/bloomberg/2026-04-02/69cedb88366bb95ba55103e5/resume.md")</f>
       </c>
       <c r="Q858"/>
       <c r="R858">
@@ -55339,7 +55339,7 @@
         </is>
       </c>
       <c r="P859">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/smc3/2026-04-02/69cec409cdb525785fb9b386/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/smc3/2026-04-02/69cec409cdb525785fb9b386/resume.md")</f>
+        <f>HYPERLINK("by_company/smc3/2026-04-02/69cec409cdb525785fb9b386/resume.md","data/deliverables/resume_portfolio/by_company/smc3/2026-04-02/69cec409cdb525785fb9b386/resume.md")</f>
       </c>
       <c r="Q859"/>
       <c r="R859">
@@ -55527,7 +55527,7 @@
         </is>
       </c>
       <c r="P862">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/goldman-sachs/2026-04-02/697ecd90abff4c399a9d6aaf/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/goldman-sachs/2026-04-02/697ecd90abff4c399a9d6aaf/resume.md")</f>
+        <f>HYPERLINK("by_company/goldman-sachs/2026-04-02/697ecd90abff4c399a9d6aaf/resume.md","data/deliverables/resume_portfolio/by_company/goldman-sachs/2026-04-02/697ecd90abff4c399a9d6aaf/resume.md")</f>
       </c>
       <c r="Q862"/>
       <c r="R862">
@@ -55593,7 +55593,7 @@
         </is>
       </c>
       <c r="P863">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cambia-health-solutions/2026-04-02/69cec152cdb525785fb9afc1/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cambia-health-solutions/2026-04-02/69cec152cdb525785fb9afc1/resume.md")</f>
+        <f>HYPERLINK("by_company/cambia-health-solutions/2026-04-02/69cec152cdb525785fb9afc1/resume.md","data/deliverables/resume_portfolio/by_company/cambia-health-solutions/2026-04-02/69cec152cdb525785fb9afc1/resume.md")</f>
       </c>
       <c r="Q863"/>
       <c r="R863">
@@ -55723,7 +55723,7 @@
         </is>
       </c>
       <c r="P865">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/wex/2026-04-02/6992b586e0bddb6acac0e42c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/wex/2026-04-02/6992b586e0bddb6acac0e42c/resume.md")</f>
+        <f>HYPERLINK("by_company/wex/2026-04-02/6992b586e0bddb6acac0e42c/resume.md","data/deliverables/resume_portfolio/by_company/wex/2026-04-02/6992b586e0bddb6acac0e42c/resume.md")</f>
       </c>
       <c r="Q865"/>
       <c r="R865">
@@ -55789,7 +55789,7 @@
         </is>
       </c>
       <c r="P866">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ironclad/2026-04-02/6965987fa112b40266139f4a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ironclad/2026-04-02/6965987fa112b40266139f4a/resume.md")</f>
+        <f>HYPERLINK("by_company/ironclad/2026-04-02/6965987fa112b40266139f4a/resume.md","data/deliverables/resume_portfolio/by_company/ironclad/2026-04-02/6965987fa112b40266139f4a/resume.md")</f>
       </c>
       <c r="Q866"/>
       <c r="R866">
@@ -55971,7 +55971,7 @@
         </is>
       </c>
       <c r="P869">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/6sense/2026-04-02/69cebc5ecdb525785fb9ae4f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/6sense/2026-04-02/69cebc5ecdb525785fb9ae4f/resume.md")</f>
+        <f>HYPERLINK("by_company/6sense/2026-04-02/69cebc5ecdb525785fb9ae4f/resume.md","data/deliverables/resume_portfolio/by_company/6sense/2026-04-02/69cebc5ecdb525785fb9ae4f/resume.md")</f>
       </c>
       <c r="Q869"/>
       <c r="R869">
@@ -56211,7 +56211,7 @@
         </is>
       </c>
       <c r="P873">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/freshdirect/2026-04-02/69ceb9e7cdb525785fb9a82a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/freshdirect/2026-04-02/69ceb9e7cdb525785fb9a82a/resume.md")</f>
+        <f>HYPERLINK("by_company/freshdirect/2026-04-02/69ceb9e7cdb525785fb9a82a/resume.md","data/deliverables/resume_portfolio/by_company/freshdirect/2026-04-02/69ceb9e7cdb525785fb9a82a/resume.md")</f>
       </c>
       <c r="Q873"/>
       <c r="R873">
@@ -56277,7 +56277,7 @@
         </is>
       </c>
       <c r="P874">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mastercard/2026-04-02/6994f5c7e0bddb6acac37ac9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/mastercard/2026-04-02/6994f5c7e0bddb6acac37ac9/resume.md")</f>
+        <f>HYPERLINK("by_company/mastercard/2026-04-02/6994f5c7e0bddb6acac37ac9/resume.md","data/deliverables/resume_portfolio/by_company/mastercard/2026-04-02/6994f5c7e0bddb6acac37ac9/resume.md")</f>
       </c>
       <c r="Q874"/>
       <c r="R874">
@@ -56343,7 +56343,7 @@
         </is>
       </c>
       <c r="P875">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/dayforce/2026-04-02/69b2e21eae2a534885ea22b4/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/dayforce/2026-04-02/69b2e21eae2a534885ea22b4/resume.md")</f>
+        <f>HYPERLINK("by_company/dayforce/2026-04-02/69b2e21eae2a534885ea22b4/resume.md","data/deliverables/resume_portfolio/by_company/dayforce/2026-04-02/69b2e21eae2a534885ea22b4/resume.md")</f>
       </c>
       <c r="Q875"/>
       <c r="R875">
@@ -56467,7 +56467,7 @@
         </is>
       </c>
       <c r="P877">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/photon/2026-04-02/69a78b921fc3d83b780948a8/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/photon/2026-04-02/69a78b921fc3d83b780948a8/resume.md")</f>
+        <f>HYPERLINK("by_company/photon/2026-04-02/69a78b921fc3d83b780948a8/resume.md","data/deliverables/resume_portfolio/by_company/photon/2026-04-02/69a78b921fc3d83b780948a8/resume.md")</f>
       </c>
       <c r="Q877"/>
       <c r="R877">
@@ -56599,7 +56599,7 @@
         </is>
       </c>
       <c r="P879">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sharkninja/2026-04-02/69ceb5ce891d7b11cfccb55b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/sharkninja/2026-04-02/69ceb5ce891d7b11cfccb55b/resume.md")</f>
+        <f>HYPERLINK("by_company/sharkninja/2026-04-02/69ceb5ce891d7b11cfccb55b/resume.md","data/deliverables/resume_portfolio/by_company/sharkninja/2026-04-02/69ceb5ce891d7b11cfccb55b/resume.md")</f>
       </c>
       <c r="Q879"/>
       <c r="R879">
@@ -56723,7 +56723,7 @@
         </is>
       </c>
       <c r="P881">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/blackrock/2026-04-02/69b2fe7ead360c0340a81017/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/blackrock/2026-04-02/69b2fe7ead360c0340a81017/resume.md")</f>
+        <f>HYPERLINK("by_company/blackrock/2026-04-02/69b2fe7ead360c0340a81017/resume.md","data/deliverables/resume_portfolio/by_company/blackrock/2026-04-02/69b2fe7ead360c0340a81017/resume.md")</f>
       </c>
       <c r="Q881"/>
       <c r="R881">
@@ -56789,7 +56789,7 @@
         </is>
       </c>
       <c r="P882">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/leviton/2026-04-02/69b20d9665de58104c717a3c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/leviton/2026-04-02/69b20d9665de58104c717a3c/resume.md")</f>
+        <f>HYPERLINK("by_company/leviton/2026-04-02/69b20d9665de58104c717a3c/resume.md","data/deliverables/resume_portfolio/by_company/leviton/2026-04-02/69b20d9665de58104c717a3c/resume.md")</f>
       </c>
       <c r="Q882"/>
       <c r="R882">
@@ -56971,7 +56971,7 @@
         </is>
       </c>
       <c r="P885">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/arkhya-tech-inc/2026-04-02/69ceb1cf891d7b11cfccb3ff/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/arkhya-tech-inc/2026-04-02/69ceb1cf891d7b11cfccb3ff/resume.md")</f>
+        <f>HYPERLINK("by_company/arkhya-tech-inc/2026-04-02/69ceb1cf891d7b11cfccb3ff/resume.md","data/deliverables/resume_portfolio/by_company/arkhya-tech-inc/2026-04-02/69ceb1cf891d7b11cfccb3ff/resume.md")</f>
       </c>
       <c r="Q885"/>
       <c r="R885">
@@ -57037,7 +57037,7 @@
         </is>
       </c>
       <c r="P886">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/magna-international/2026-04-02/69ceb03d366bb95ba550e085/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/magna-international/2026-04-02/69ceb03d366bb95ba550e085/resume.md")</f>
+        <f>HYPERLINK("by_company/magna-international/2026-04-02/69ceb03d366bb95ba550e085/resume.md","data/deliverables/resume_portfolio/by_company/magna-international/2026-04-02/69ceb03d366bb95ba550e085/resume.md")</f>
       </c>
       <c r="Q886"/>
       <c r="R886">
@@ -57103,7 +57103,7 @@
         </is>
       </c>
       <c r="P887">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/citi/2026-04-02/69cd2d71398fb071abf729b9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/citi/2026-04-02/69cd2d71398fb071abf729b9/resume.md")</f>
+        <f>HYPERLINK("by_company/citi/2026-04-02/69cd2d71398fb071abf729b9/resume.md","data/deliverables/resume_portfolio/by_company/citi/2026-04-02/69cd2d71398fb071abf729b9/resume.md")</f>
       </c>
       <c r="Q887"/>
       <c r="R887">
@@ -57169,7 +57169,7 @@
         </is>
       </c>
       <c r="P888">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/altos-labs/2026-04-02/6924e563ec574f4265bb8a10/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/altos-labs/2026-04-02/6924e563ec574f4265bb8a10/resume.md")</f>
+        <f>HYPERLINK("by_company/altos-labs/2026-04-02/6924e563ec574f4265bb8a10/resume.md","data/deliverables/resume_portfolio/by_company/altos-labs/2026-04-02/6924e563ec574f4265bb8a10/resume.md")</f>
       </c>
       <c r="Q888"/>
       <c r="R888">
@@ -57301,7 +57301,7 @@
         </is>
       </c>
       <c r="P890">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/spotify/2026-04-02/69cea94b366bb95ba550de01/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/spotify/2026-04-02/69cea94b366bb95ba550de01/resume.md")</f>
+        <f>HYPERLINK("by_company/spotify/2026-04-02/69cea94b366bb95ba550de01/resume.md","data/deliverables/resume_portfolio/by_company/spotify/2026-04-02/69cea94b366bb95ba550de01/resume.md")</f>
       </c>
       <c r="Q890"/>
       <c r="R890">
@@ -57439,7 +57439,7 @@
         </is>
       </c>
       <c r="P892">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/flextrade/2026-04-02/69cea6facdb525785fb99d09/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/flextrade/2026-04-02/69cea6facdb525785fb99d09/resume.md")</f>
+        <f>HYPERLINK("by_company/flextrade/2026-04-02/69cea6facdb525785fb99d09/resume.md","data/deliverables/resume_portfolio/by_company/flextrade/2026-04-02/69cea6facdb525785fb99d09/resume.md")</f>
       </c>
       <c r="Q892"/>
       <c r="R892">
@@ -57563,7 +57563,7 @@
         </is>
       </c>
       <c r="P894">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cvs-health/2026-04-02/69cea079398fb071abf87380/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cvs-health/2026-04-02/69cea079398fb071abf87380/resume.md")</f>
+        <f>HYPERLINK("by_company/cvs-health/2026-04-02/69cea079398fb071abf87380/resume.md","data/deliverables/resume_portfolio/by_company/cvs-health/2026-04-02/69cea079398fb071abf87380/resume.md")</f>
       </c>
       <c r="Q894"/>
       <c r="R894">
@@ -57919,7 +57919,7 @@
         </is>
       </c>
       <c r="P900">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/natsoft/2026-04-02/69cece4f891d7b11cfcccc3b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/natsoft/2026-04-02/69cece4f891d7b11cfcccc3b/resume.md")</f>
+        <f>HYPERLINK("by_company/natsoft/2026-04-02/69cece4f891d7b11cfcccc3b/resume.md","data/deliverables/resume_portfolio/by_company/natsoft/2026-04-02/69cece4f891d7b11cfcccc3b/resume.md")</f>
       </c>
       <c r="Q900"/>
       <c r="R900">
@@ -57993,7 +57993,7 @@
         </is>
       </c>
       <c r="P901">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/latitude-ai/2026-04-02/69ce99ff366bb95ba550d1ae/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/latitude-ai/2026-04-02/69ce99ff366bb95ba550d1ae/resume.md")</f>
+        <f>HYPERLINK("by_company/latitude-ai/2026-04-02/69ce99ff366bb95ba550d1ae/resume.md","data/deliverables/resume_portfolio/by_company/latitude-ai/2026-04-02/69ce99ff366bb95ba550d1ae/resume.md")</f>
       </c>
       <c r="Q901"/>
       <c r="R901">
@@ -58175,7 +58175,7 @@
         </is>
       </c>
       <c r="P904">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ibm/2026-04-02/69b3d591a8ac8e70ff681f06/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ibm/2026-04-02/69b3d591a8ac8e70ff681f06/resume.md")</f>
+        <f>HYPERLINK("by_company/ibm/2026-04-02/69b3d591a8ac8e70ff681f06/resume.md","data/deliverables/resume_portfolio/by_company/ibm/2026-04-02/69b3d591a8ac8e70ff681f06/resume.md")</f>
       </c>
       <c r="Q904"/>
       <c r="R904">
@@ -58241,7 +58241,7 @@
         </is>
       </c>
       <c r="P905">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cambia-health-solutions/2026-04-02/69cea998366bb95ba550de38/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cambia-health-solutions/2026-04-02/69cea998366bb95ba550de38/resume.md")</f>
+        <f>HYPERLINK("by_company/cambia-health-solutions/2026-04-02/69cea998366bb95ba550de38/resume.md","data/deliverables/resume_portfolio/by_company/cambia-health-solutions/2026-04-02/69cea998366bb95ba550de38/resume.md")</f>
       </c>
       <c r="Q905"/>
       <c r="R905">
@@ -58307,7 +58307,7 @@
         </is>
       </c>
       <c r="P906">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ibm/2026-04-02/69c17a332c312363dcd460fa/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ibm/2026-04-02/69c17a332c312363dcd460fa/resume.md")</f>
+        <f>HYPERLINK("by_company/ibm/2026-04-02/69c17a332c312363dcd460fa/resume.md","data/deliverables/resume_portfolio/by_company/ibm/2026-04-02/69c17a332c312363dcd460fa/resume.md")</f>
       </c>
       <c r="Q906"/>
       <c r="R906">
@@ -58439,7 +58439,7 @@
         </is>
       </c>
       <c r="P908">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualitest/2026-04-02/69ce947e54f00230c6d00767/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualitest/2026-04-02/69ce947e54f00230c6d00767/resume.md")</f>
+        <f>HYPERLINK("by_company/qualitest/2026-04-02/69ce947e54f00230c6d00767/resume.md","data/deliverables/resume_portfolio/by_company/qualitest/2026-04-02/69ce947e54f00230c6d00767/resume.md")</f>
       </c>
       <c r="Q908"/>
       <c r="R908">
@@ -58505,7 +58505,7 @@
         </is>
       </c>
       <c r="P909">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tyler-technologies/2026-04-02/69b1ef2e548f140066e809d2/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tyler-technologies/2026-04-02/69b1ef2e548f140066e809d2/resume.md")</f>
+        <f>HYPERLINK("by_company/tyler-technologies/2026-04-02/69b1ef2e548f140066e809d2/resume.md","data/deliverables/resume_portfolio/by_company/tyler-technologies/2026-04-02/69b1ef2e548f140066e809d2/resume.md")</f>
       </c>
       <c r="Q909"/>
       <c r="R909">
@@ -58571,7 +58571,7 @@
         </is>
       </c>
       <c r="P910">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ibm/2026-04-02/69c15d0479e36d3a847dfc49/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ibm/2026-04-02/69c15d0479e36d3a847dfc49/resume.md")</f>
+        <f>HYPERLINK("by_company/ibm/2026-04-02/69c15d0479e36d3a847dfc49/resume.md","data/deliverables/resume_portfolio/by_company/ibm/2026-04-02/69c15d0479e36d3a847dfc49/resume.md")</f>
       </c>
       <c r="Q910"/>
       <c r="R910">
@@ -58637,7 +58637,7 @@
         </is>
       </c>
       <c r="P911">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fanduel/2026-04-02/69951d7fce78e77b4fd934ed/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fanduel/2026-04-02/69951d7fce78e77b4fd934ed/resume.md")</f>
+        <f>HYPERLINK("by_company/fanduel/2026-04-02/69951d7fce78e77b4fd934ed/resume.md","data/deliverables/resume_portfolio/by_company/fanduel/2026-04-02/69951d7fce78e77b4fd934ed/resume.md")</f>
       </c>
       <c r="Q911"/>
       <c r="R911">
@@ -58775,7 +58775,7 @@
         </is>
       </c>
       <c r="P913">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/barclays-investment-bank/2026-04-02/69ce8e4254f00230c6d004b5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/barclays-investment-bank/2026-04-02/69ce8e4254f00230c6d004b5/resume.md")</f>
+        <f>HYPERLINK("by_company/barclays-investment-bank/2026-04-02/69ce8e4254f00230c6d004b5/resume.md","data/deliverables/resume_portfolio/by_company/barclays-investment-bank/2026-04-02/69ce8e4254f00230c6d004b5/resume.md")</f>
       </c>
       <c r="Q913"/>
       <c r="R913">
@@ -58841,7 +58841,7 @@
         </is>
       </c>
       <c r="P914">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/glean/2026-04-02/69b2c994ad360c0340a7bca1/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/glean/2026-04-02/69b2c994ad360c0340a7bca1/resume.md")</f>
+        <f>HYPERLINK("by_company/glean/2026-04-02/69b2c994ad360c0340a7bca1/resume.md","data/deliverables/resume_portfolio/by_company/glean/2026-04-02/69b2c994ad360c0340a7bca1/resume.md")</f>
       </c>
       <c r="Q914"/>
       <c r="R914">
@@ -58965,7 +58965,7 @@
         </is>
       </c>
       <c r="P916">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cifc-asset-management/2026-04-02/69ceb33e398fb071abf87b66/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cifc-asset-management/2026-04-02/69ceb33e398fb071abf87b66/resume.md")</f>
+        <f>HYPERLINK("by_company/cifc-asset-management/2026-04-02/69ceb33e398fb071abf87b66/resume.md","data/deliverables/resume_portfolio/by_company/cifc-asset-management/2026-04-02/69ceb33e398fb071abf87b66/resume.md")</f>
       </c>
       <c r="Q916"/>
       <c r="R916">
@@ -59031,7 +59031,7 @@
         </is>
       </c>
       <c r="P917">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/phantom/2026-04-02/69b20992d04c69566c74ae72/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/phantom/2026-04-02/69b20992d04c69566c74ae72/resume.md")</f>
+        <f>HYPERLINK("by_company/phantom/2026-04-02/69b20992d04c69566c74ae72/resume.md","data/deliverables/resume_portfolio/by_company/phantom/2026-04-02/69b20992d04c69566c74ae72/resume.md")</f>
       </c>
       <c r="Q917"/>
       <c r="R917">
@@ -59155,7 +59155,7 @@
         </is>
       </c>
       <c r="P919">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/unum/2026-04-02/69b176afd04c69566c73c3bf/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/unum/2026-04-02/69b176afd04c69566c73c3bf/resume.md")</f>
+        <f>HYPERLINK("by_company/unum/2026-04-02/69b176afd04c69566c73c3bf/resume.md","data/deliverables/resume_portfolio/by_company/unum/2026-04-02/69b176afd04c69566c73c3bf/resume.md")</f>
       </c>
       <c r="Q919"/>
       <c r="R919">
@@ -59229,7 +59229,7 @@
         </is>
       </c>
       <c r="P920">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/skydio/2026-04-02/69421283bdcf884a5addd027/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/skydio/2026-04-02/69421283bdcf884a5addd027/resume.md")</f>
+        <f>HYPERLINK("by_company/skydio/2026-04-02/69421283bdcf884a5addd027/resume.md","data/deliverables/resume_portfolio/by_company/skydio/2026-04-02/69421283bdcf884a5addd027/resume.md")</f>
       </c>
       <c r="Q920"/>
       <c r="R920">
@@ -59411,7 +59411,7 @@
         </is>
       </c>
       <c r="P923">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-02/69ce6e5d366bb95ba550b6e8/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/microsoft/2026-04-02/69ce6e5d366bb95ba550b6e8/resume.md")</f>
+        <f>HYPERLINK("by_company/microsoft/2026-04-02/69ce6e5d366bb95ba550b6e8/resume.md","data/deliverables/resume_portfolio/by_company/microsoft/2026-04-02/69ce6e5d366bb95ba550b6e8/resume.md")</f>
       </c>
       <c r="Q923"/>
       <c r="R923">
@@ -59593,7 +59593,7 @@
         </is>
       </c>
       <c r="P926">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tubi/2026-04-02/69b20ab065de58104c7177b8/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tubi/2026-04-02/69b20ab065de58104c7177b8/resume.md")</f>
+        <f>HYPERLINK("by_company/tubi/2026-04-02/69b20ab065de58104c7177b8/resume.md","data/deliverables/resume_portfolio/by_company/tubi/2026-04-02/69b20ab065de58104c7177b8/resume.md")</f>
       </c>
       <c r="Q926"/>
       <c r="R926">
@@ -59659,7 +59659,7 @@
         </is>
       </c>
       <c r="P927">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fico/2026-04-02/697c690a3f57a33569661871/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fico/2026-04-02/697c690a3f57a33569661871/resume.md")</f>
+        <f>HYPERLINK("by_company/fico/2026-04-02/697c690a3f57a33569661871/resume.md","data/deliverables/resume_portfolio/by_company/fico/2026-04-02/697c690a3f57a33569661871/resume.md")</f>
       </c>
       <c r="Q927"/>
       <c r="R927">
@@ -59849,7 +59849,7 @@
         </is>
       </c>
       <c r="P930">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fico/2026-04-02/6999546d81476f6176b1f81f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fico/2026-04-02/6999546d81476f6176b1f81f/resume.md")</f>
+        <f>HYPERLINK("by_company/fico/2026-04-02/6999546d81476f6176b1f81f/resume.md","data/deliverables/resume_portfolio/by_company/fico/2026-04-02/6999546d81476f6176b1f81f/resume.md")</f>
       </c>
       <c r="Q930"/>
       <c r="R930">
@@ -59973,7 +59973,7 @@
         </is>
       </c>
       <c r="P932">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/known/2026-04-02/695c3a48f1f8465b79f24449/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/known/2026-04-02/695c3a48f1f8465b79f24449/resume.md")</f>
+        <f>HYPERLINK("by_company/known/2026-04-02/695c3a48f1f8465b79f24449/resume.md","data/deliverables/resume_portfolio/by_company/known/2026-04-02/695c3a48f1f8465b79f24449/resume.md")</f>
       </c>
       <c r="Q932"/>
       <c r="R932">
@@ -60097,7 +60097,7 @@
         </is>
       </c>
       <c r="P934">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/modmed/2026-04-02/69961353e0bddb6acac472ee/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/modmed/2026-04-02/69961353e0bddb6acac472ee/resume.md")</f>
+        <f>HYPERLINK("by_company/modmed/2026-04-02/69961353e0bddb6acac472ee/resume.md","data/deliverables/resume_portfolio/by_company/modmed/2026-04-02/69961353e0bddb6acac472ee/resume.md")</f>
       </c>
       <c r="Q934"/>
       <c r="R934">
@@ -60171,7 +60171,7 @@
         </is>
       </c>
       <c r="P935">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/valon/2026-04-02/697a7c469d60e431a16bfd27/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/valon/2026-04-02/697a7c469d60e431a16bfd27/resume.md")</f>
+        <f>HYPERLINK("by_company/valon/2026-04-02/697a7c469d60e431a16bfd27/resume.md","data/deliverables/resume_portfolio/by_company/valon/2026-04-02/697a7c469d60e431a16bfd27/resume.md")</f>
       </c>
       <c r="Q935"/>
       <c r="R935">
@@ -60427,7 +60427,7 @@
         </is>
       </c>
       <c r="P939">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/root-inc/2026-04-02/69a3ded90da45516f16cd050/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/root-inc/2026-04-02/69a3ded90da45516f16cd050/resume.md")</f>
+        <f>HYPERLINK("by_company/root-inc/2026-04-02/69a3ded90da45516f16cd050/resume.md","data/deliverables/resume_portfolio/by_company/root-inc/2026-04-02/69a3ded90da45516f16cd050/resume.md")</f>
       </c>
       <c r="Q939"/>
       <c r="R939">
@@ -60617,7 +60617,7 @@
         </is>
       </c>
       <c r="P942">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/suffolk-construction/2026-04-02/69b17630d04c69566c73c128/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/suffolk-construction/2026-04-02/69b17630d04c69566c73c128/resume.md")</f>
+        <f>HYPERLINK("by_company/suffolk-construction/2026-04-02/69b17630d04c69566c73c128/resume.md","data/deliverables/resume_portfolio/by_company/suffolk-construction/2026-04-02/69b17630d04c69566c73c128/resume.md")</f>
       </c>
       <c r="Q942"/>
       <c r="R942">
@@ -60683,7 +60683,7 @@
         </is>
       </c>
       <c r="P943">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/auger/2026-04-02/6941ec3d14ee092a69000521/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/auger/2026-04-02/6941ec3d14ee092a69000521/resume.md")</f>
+        <f>HYPERLINK("by_company/auger/2026-04-02/6941ec3d14ee092a69000521/resume.md","data/deliverables/resume_portfolio/by_company/auger/2026-04-02/6941ec3d14ee092a69000521/resume.md")</f>
       </c>
       <c r="Q943"/>
       <c r="R943">
@@ -60929,7 +60929,7 @@
         </is>
       </c>
       <c r="P947">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/komodo-health/2026-04-02/69bc69ea5b89c002acf21221/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/komodo-health/2026-04-02/69bc69ea5b89c002acf21221/resume.md")</f>
+        <f>HYPERLINK("by_company/komodo-health/2026-04-02/69bc69ea5b89c002acf21221/resume.md","data/deliverables/resume_portfolio/by_company/komodo-health/2026-04-02/69bc69ea5b89c002acf21221/resume.md")</f>
       </c>
       <c r="Q947"/>
       <c r="R947">
@@ -61003,7 +61003,7 @@
         </is>
       </c>
       <c r="P948">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/affirm/2026-04-02/6941879614ee092a69ffa832/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/affirm/2026-04-02/6941879614ee092a69ffa832/resume.md")</f>
+        <f>HYPERLINK("by_company/affirm/2026-04-02/6941879614ee092a69ffa832/resume.md","data/deliverables/resume_portfolio/by_company/affirm/2026-04-02/6941879614ee092a69ffa832/resume.md")</f>
       </c>
       <c r="Q948"/>
       <c r="R948">
@@ -61127,7 +61127,7 @@
         </is>
       </c>
       <c r="P950">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/auger/2026-04-02/694197d7bdcf884a5add4d85/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/auger/2026-04-02/694197d7bdcf884a5add4d85/resume.md")</f>
+        <f>HYPERLINK("by_company/auger/2026-04-02/694197d7bdcf884a5add4d85/resume.md","data/deliverables/resume_portfolio/by_company/auger/2026-04-02/694197d7bdcf884a5add4d85/resume.md")</f>
       </c>
       <c r="Q950"/>
       <c r="R950">
@@ -61251,7 +61251,7 @@
         </is>
       </c>
       <c r="P952">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/retell-ai/2026-04-02/6977cf9cfdeb8243a27abd6b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/retell-ai/2026-04-02/6977cf9cfdeb8243a27abd6b/resume.md")</f>
+        <f>HYPERLINK("by_company/retell-ai/2026-04-02/6977cf9cfdeb8243a27abd6b/resume.md","data/deliverables/resume_portfolio/by_company/retell-ai/2026-04-02/6977cf9cfdeb8243a27abd6b/resume.md")</f>
       </c>
       <c r="Q952"/>
       <c r="R952">
@@ -61325,7 +61325,7 @@
         </is>
       </c>
       <c r="P953">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intuit/2026-04-02/69ce4d90398fb071abf84215/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intuit/2026-04-02/69ce4d90398fb071abf84215/resume.md")</f>
+        <f>HYPERLINK("by_company/intuit/2026-04-02/69ce4d90398fb071abf84215/resume.md","data/deliverables/resume_portfolio/by_company/intuit/2026-04-02/69ce4d90398fb071abf84215/resume.md")</f>
       </c>
       <c r="Q953"/>
       <c r="R953">
@@ -61449,7 +61449,7 @@
         </is>
       </c>
       <c r="P955">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gumgum/2026-04-02/6979c301d7df290257fc302c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gumgum/2026-04-02/6979c301d7df290257fc302c/resume.md")</f>
+        <f>HYPERLINK("by_company/gumgum/2026-04-02/6979c301d7df290257fc302c/resume.md","data/deliverables/resume_portfolio/by_company/gumgum/2026-04-02/6979c301d7df290257fc302c/resume.md")</f>
       </c>
       <c r="Q955"/>
       <c r="R955">
@@ -61573,7 +61573,7 @@
         </is>
       </c>
       <c r="P957">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-02/69b23bcca8ac8e70ff660fe9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-02/69b23bcca8ac8e70ff660fe9/resume.md")</f>
+        <f>HYPERLINK("by_company/adobe/2026-04-02/69b23bcca8ac8e70ff660fe9/resume.md","data/deliverables/resume_portfolio/by_company/adobe/2026-04-02/69b23bcca8ac8e70ff660fe9/resume.md")</f>
       </c>
       <c r="Q957"/>
       <c r="R957">
@@ -61639,7 +61639,7 @@
         </is>
       </c>
       <c r="P958">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-02/696896b11703f05405aa695a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/adobe/2026-04-02/696896b11703f05405aa695a/resume.md")</f>
+        <f>HYPERLINK("by_company/adobe/2026-04-02/696896b11703f05405aa695a/resume.md","data/deliverables/resume_portfolio/by_company/adobe/2026-04-02/696896b11703f05405aa695a/resume.md")</f>
       </c>
       <c r="Q958"/>
       <c r="R958">
@@ -61713,7 +61713,7 @@
         </is>
       </c>
       <c r="P959">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-02/697028e4587dfa0bb55daadd/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-02/697028e4587dfa0bb55daadd/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-02/697028e4587dfa0bb55daadd/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-02/697028e4587dfa0bb55daadd/resume.md")</f>
       </c>
       <c r="Q959"/>
       <c r="R959">
@@ -61779,7 +61779,7 @@
         </is>
       </c>
       <c r="P960">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-02/69b2297a65de58104c719ffc/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-02/69b2297a65de58104c719ffc/resume.md")</f>
+        <f>HYPERLINK("by_company/paypal/2026-04-02/69b2297a65de58104c719ffc/resume.md","data/deliverables/resume_portfolio/by_company/paypal/2026-04-02/69b2297a65de58104c719ffc/resume.md")</f>
       </c>
       <c r="Q960"/>
       <c r="R960">
@@ -61845,7 +61845,7 @@
         </is>
       </c>
       <c r="P961">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/certara/2026-04-02/6995e965ce78e77b4fd9e92a/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/certara/2026-04-02/6995e965ce78e77b4fd9e92a/resume.md")</f>
+        <f>HYPERLINK("by_company/certara/2026-04-02/6995e965ce78e77b4fd9e92a/resume.md","data/deliverables/resume_portfolio/by_company/certara/2026-04-02/6995e965ce78e77b4fd9e92a/resume.md")</f>
       </c>
       <c r="Q961"/>
       <c r="R961">
@@ -61911,7 +61911,7 @@
         </is>
       </c>
       <c r="P962">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-02/69c8cbc51b5ad02887395602/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-02/69c8cbc51b5ad02887395602/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-02/69c8cbc51b5ad02887395602/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-02/69c8cbc51b5ad02887395602/resume.md")</f>
       </c>
       <c r="Q962"/>
       <c r="R962">
@@ -62035,7 +62035,7 @@
         </is>
       </c>
       <c r="P964">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/crowdstrike/2026-04-02/69bbcf0378a5df4797fd7081/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/crowdstrike/2026-04-02/69bbcf0378a5df4797fd7081/resume.md")</f>
+        <f>HYPERLINK("by_company/crowdstrike/2026-04-02/69bbcf0378a5df4797fd7081/resume.md","data/deliverables/resume_portfolio/by_company/crowdstrike/2026-04-02/69bbcf0378a5df4797fd7081/resume.md")</f>
       </c>
       <c r="Q964"/>
       <c r="R964">
@@ -62101,7 +62101,7 @@
         </is>
       </c>
       <c r="P965">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/modmed/2026-04-02/695da7a3f1f8465b79f3efd5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/modmed/2026-04-02/695da7a3f1f8465b79f3efd5/resume.md")</f>
+        <f>HYPERLINK("by_company/modmed/2026-04-02/695da7a3f1f8465b79f3efd5/resume.md","data/deliverables/resume_portfolio/by_company/modmed/2026-04-02/695da7a3f1f8465b79f3efd5/resume.md")</f>
       </c>
       <c r="Q965"/>
       <c r="R965">
@@ -62167,7 +62167,7 @@
         </is>
       </c>
       <c r="P966">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/td-securities/2026-04-02/69ce4048891d7b11cfcc67c3/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/td-securities/2026-04-02/69ce4048891d7b11cfcc67c3/resume.md")</f>
+        <f>HYPERLINK("by_company/td-securities/2026-04-02/69ce4048891d7b11cfcc67c3/resume.md","data/deliverables/resume_portfolio/by_company/td-securities/2026-04-02/69ce4048891d7b11cfcc67c3/resume.md")</f>
       </c>
       <c r="Q966"/>
       <c r="R966">
@@ -62233,7 +62233,7 @@
         </is>
       </c>
       <c r="P967">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/waystar/2026-04-02/6983fae701214b4cdacc4737/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/waystar/2026-04-02/6983fae701214b4cdacc4737/resume.md")</f>
+        <f>HYPERLINK("by_company/waystar/2026-04-02/6983fae701214b4cdacc4737/resume.md","data/deliverables/resume_portfolio/by_company/waystar/2026-04-02/6983fae701214b4cdacc4737/resume.md")</f>
       </c>
       <c r="Q967"/>
       <c r="R967">
@@ -62299,7 +62299,7 @@
         </is>
       </c>
       <c r="P968">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-02/6994e497ce78e77b4fd8f5ab/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-02/6994e497ce78e77b4fd8f5ab/resume.md")</f>
+        <f>HYPERLINK("by_company/paypal/2026-04-02/6994e497ce78e77b4fd8f5ab/resume.md","data/deliverables/resume_portfolio/by_company/paypal/2026-04-02/6994e497ce78e77b4fd8f5ab/resume.md")</f>
       </c>
       <c r="Q968"/>
       <c r="R968">
@@ -62373,7 +62373,7 @@
         </is>
       </c>
       <c r="P969">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jewelers-mutual-group/2026-04-02/69b1df7fd04c69566c745093/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jewelers-mutual-group/2026-04-02/69b1df7fd04c69566c745093/resume.md")</f>
+        <f>HYPERLINK("by_company/jewelers-mutual-group/2026-04-02/69b1df7fd04c69566c745093/resume.md","data/deliverables/resume_portfolio/by_company/jewelers-mutual-group/2026-04-02/69b1df7fd04c69566c745093/resume.md")</f>
       </c>
       <c r="Q969"/>
       <c r="R969">
@@ -62439,7 +62439,7 @@
         </is>
       </c>
       <c r="P970">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/publicis-sapient/2026-04-02/69c35849753c101b2156fe0b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/publicis-sapient/2026-04-02/69c35849753c101b2156fe0b/resume.md")</f>
+        <f>HYPERLINK("by_company/publicis-sapient/2026-04-02/69c35849753c101b2156fe0b/resume.md","data/deliverables/resume_portfolio/by_company/publicis-sapient/2026-04-02/69c35849753c101b2156fe0b/resume.md")</f>
       </c>
       <c r="Q970"/>
       <c r="R970">
@@ -62737,7 +62737,7 @@
         </is>
       </c>
       <c r="P975">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hone-health/2026-04-02/69ce23ffcdb525785fb943a2/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/hone-health/2026-04-02/69ce23ffcdb525785fb943a2/resume.md")</f>
+        <f>HYPERLINK("by_company/hone-health/2026-04-02/69ce23ffcdb525785fb943a2/resume.md","data/deliverables/resume_portfolio/by_company/hone-health/2026-04-02/69ce23ffcdb525785fb943a2/resume.md")</f>
       </c>
       <c r="Q975"/>
       <c r="R975">
@@ -62803,7 +62803,7 @@
         </is>
       </c>
       <c r="P976">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/optimal-blue/2026-04-02/69ce2393891d7b11cfcc5705/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/optimal-blue/2026-04-02/69ce2393891d7b11cfcc5705/resume.md")</f>
+        <f>HYPERLINK("by_company/optimal-blue/2026-04-02/69ce2393891d7b11cfcc5705/resume.md","data/deliverables/resume_portfolio/by_company/optimal-blue/2026-04-02/69ce2393891d7b11cfcc5705/resume.md")</f>
       </c>
       <c r="Q976"/>
       <c r="R976">
@@ -62935,7 +62935,7 @@
         </is>
       </c>
       <c r="P978">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tubi/2026-04-02/69c482876f4f855eeda7180c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tubi/2026-04-02/69c482876f4f855eeda7180c/resume.md")</f>
+        <f>HYPERLINK("by_company/tubi/2026-04-02/69c482876f4f855eeda7180c/resume.md","data/deliverables/resume_portfolio/by_company/tubi/2026-04-02/69c482876f4f855eeda7180c/resume.md")</f>
       </c>
       <c r="Q978"/>
       <c r="R978">
@@ -63059,7 +63059,7 @@
         </is>
       </c>
       <c r="P980">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/its-logistics/2026-04-02/69aa23461f59c56275e2f0b1/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/its-logistics/2026-04-02/69aa23461f59c56275e2f0b1/resume.md")</f>
+        <f>HYPERLINK("by_company/its-logistics/2026-04-02/69aa23461f59c56275e2f0b1/resume.md","data/deliverables/resume_portfolio/by_company/its-logistics/2026-04-02/69aa23461f59c56275e2f0b1/resume.md")</f>
       </c>
       <c r="Q980"/>
       <c r="R980">
@@ -63125,7 +63125,7 @@
         </is>
       </c>
       <c r="P981">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/avenue-code/2026-04-02/69c44fa5d5a1016e98db70a0/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/avenue-code/2026-04-02/69c44fa5d5a1016e98db70a0/resume.md")</f>
+        <f>HYPERLINK("by_company/avenue-code/2026-04-02/69c44fa5d5a1016e98db70a0/resume.md","data/deliverables/resume_portfolio/by_company/avenue-code/2026-04-02/69c44fa5d5a1016e98db70a0/resume.md")</f>
       </c>
       <c r="Q981"/>
       <c r="R981">
@@ -63257,7 +63257,7 @@
         </is>
       </c>
       <c r="P983">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/supio/2026-04-02/69ce0161398fb071abf80503/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/supio/2026-04-02/69ce0161398fb071abf80503/resume.md")</f>
+        <f>HYPERLINK("by_company/supio/2026-04-02/69ce0161398fb071abf80503/resume.md","data/deliverables/resume_portfolio/by_company/supio/2026-04-02/69ce0161398fb071abf80503/resume.md")</f>
       </c>
       <c r="Q983"/>
       <c r="R983">
@@ -63389,7 +63389,7 @@
         </is>
       </c>
       <c r="P985">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/uber/2026-04-02/69cdf7eb54f00230c6cfa375/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/uber/2026-04-02/69cdf7eb54f00230c6cfa375/resume.md")</f>
+        <f>HYPERLINK("by_company/uber/2026-04-02/69cdf7eb54f00230c6cfa375/resume.md","data/deliverables/resume_portfolio/by_company/uber/2026-04-02/69cdf7eb54f00230c6cfa375/resume.md")</f>
       </c>
       <c r="Q985"/>
       <c r="R985">
@@ -63463,7 +63463,7 @@
         </is>
       </c>
       <c r="P986">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/waymo/2026-04-01/69846d438da7a612045e943f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/waymo/2026-04-01/69846d438da7a612045e943f/resume.md")</f>
+        <f>HYPERLINK("by_company/waymo/2026-04-01/69846d438da7a612045e943f/resume.md","data/deliverables/resume_portfolio/by_company/waymo/2026-04-01/69846d438da7a612045e943f/resume.md")</f>
       </c>
       <c r="Q986"/>
       <c r="R986">
@@ -63529,7 +63529,7 @@
         </is>
       </c>
       <c r="P987">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/zendesk/2026-04-01/69cf12e754f00230c6d0657e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/zendesk/2026-04-01/69cf12e754f00230c6d0657e/resume.md")</f>
+        <f>HYPERLINK("by_company/zendesk/2026-04-01/69cf12e754f00230c6d0657e/resume.md","data/deliverables/resume_portfolio/by_company/zendesk/2026-04-01/69cf12e754f00230c6d0657e/resume.md")</f>
       </c>
       <c r="Q987"/>
       <c r="R987">
@@ -63595,7 +63595,7 @@
         </is>
       </c>
       <c r="P988">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-01/69cde879cdb525785fb9047f/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-01/69cde879cdb525785fb9047f/resume.md")</f>
+        <f>HYPERLINK("by_company/paypal/2026-04-01/69cde879cdb525785fb9047f/resume.md","data/deliverables/resume_portfolio/by_company/paypal/2026-04-01/69cde879cdb525785fb9047f/resume.md")</f>
       </c>
       <c r="Q988"/>
       <c r="R988">
@@ -63793,7 +63793,7 @@
         </is>
       </c>
       <c r="P991">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/motherduck/2026-04-01/69cdd60ecdb525785fb8f358/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/motherduck/2026-04-01/69cdd60ecdb525785fb8f358/resume.md")</f>
+        <f>HYPERLINK("by_company/motherduck/2026-04-01/69cdd60ecdb525785fb8f358/resume.md","data/deliverables/resume_portfolio/by_company/motherduck/2026-04-01/69cdd60ecdb525785fb8f358/resume.md")</f>
       </c>
       <c r="Q991"/>
       <c r="R991">
@@ -63859,7 +63859,7 @@
         </is>
       </c>
       <c r="P992">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-01/69cdd467891d7b11cfcc0380/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-01/69cdd467891d7b11cfcc0380/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-01/69cdd467891d7b11cfcc0380/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-01/69cdd467891d7b11cfcc0380/resume.md")</f>
       </c>
       <c r="Q992"/>
       <c r="R992">
@@ -63925,7 +63925,7 @@
         </is>
       </c>
       <c r="P993">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/checkr-inc/2026-04-01/69cdd467891d7b11cfcc0382/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/checkr-inc/2026-04-01/69cdd467891d7b11cfcc0382/resume.md")</f>
+        <f>HYPERLINK("by_company/checkr-inc/2026-04-01/69cdd467891d7b11cfcc0382/resume.md","data/deliverables/resume_portfolio/by_company/checkr-inc/2026-04-01/69cdd467891d7b11cfcc0382/resume.md")</f>
       </c>
       <c r="Q993"/>
       <c r="R993">
@@ -63991,7 +63991,7 @@
         </is>
       </c>
       <c r="P994">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-01/69cdd45354f00230c6cf6d55/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-01/69cdd45354f00230c6cf6d55/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-01/69cdd45354f00230c6cf6d55/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-01/69cdd45354f00230c6cf6d55/resume.md")</f>
       </c>
       <c r="Q994"/>
       <c r="R994">
@@ -64057,7 +64057,7 @@
         </is>
       </c>
       <c r="P995">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-01/69cdd45054f00230c6cf6d4d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-01/69cdd45054f00230c6cf6d4d/resume.md")</f>
+        <f>HYPERLINK("by_company/jpmorganchase/2026-04-01/69cdd45054f00230c6cf6d4d/resume.md","data/deliverables/resume_portfolio/by_company/jpmorganchase/2026-04-01/69cdd45054f00230c6cf6d4d/resume.md")</f>
       </c>
       <c r="Q995"/>
       <c r="R995">
@@ -64123,7 +64123,7 @@
         </is>
       </c>
       <c r="P996">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intone/2026-04-01/69cde8a2cdb525785fb90497/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/intone/2026-04-01/69cde8a2cdb525785fb90497/resume.md")</f>
+        <f>HYPERLINK("by_company/intone/2026-04-01/69cde8a2cdb525785fb90497/resume.md","data/deliverables/resume_portfolio/by_company/intone/2026-04-01/69cde8a2cdb525785fb90497/resume.md")</f>
       </c>
       <c r="Q996"/>
       <c r="R996">
@@ -64253,7 +64253,7 @@
         </is>
       </c>
       <c r="P998">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/revspring/2026-04-01/69bdfca7482822729300b481/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/revspring/2026-04-01/69bdfca7482822729300b481/resume.md")</f>
+        <f>HYPERLINK("by_company/revspring/2026-04-01/69bdfca7482822729300b481/resume.md","data/deliverables/resume_portfolio/by_company/revspring/2026-04-01/69bdfca7482822729300b481/resume.md")</f>
       </c>
       <c r="Q998"/>
       <c r="R998">
@@ -64385,7 +64385,7 @@
         </is>
       </c>
       <c r="P1000">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/informatica/2026-04-01/69cdd1dd398fb071abf7cab2/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/informatica/2026-04-01/69cdd1dd398fb071abf7cab2/resume.md")</f>
+        <f>HYPERLINK("by_company/informatica/2026-04-01/69cdd1dd398fb071abf7cab2/resume.md","data/deliverables/resume_portfolio/by_company/informatica/2026-04-01/69cdd1dd398fb071abf7cab2/resume.md")</f>
       </c>
       <c r="Q1000"/>
       <c r="R1000">
@@ -64451,7 +64451,7 @@
         </is>
       </c>
       <c r="P1001">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gains/2026-04-01/69cec507398fb071abf88ea0/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/gains/2026-04-01/69cec507398fb071abf88ea0/resume.md")</f>
+        <f>HYPERLINK("by_company/gains/2026-04-01/69cec507398fb071abf88ea0/resume.md","data/deliverables/resume_portfolio/by_company/gains/2026-04-01/69cec507398fb071abf88ea0/resume.md")</f>
       </c>
       <c r="Q1001"/>
       <c r="R1001">
@@ -64517,7 +64517,7 @@
         </is>
       </c>
       <c r="P1002">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/thermo-fisher-scientific/2026-04-01/69cdac59cdb525785fb8d815/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/thermo-fisher-scientific/2026-04-01/69cdac59cdb525785fb8d815/resume.md")</f>
+        <f>HYPERLINK("by_company/thermo-fisher-scientific/2026-04-01/69cdac59cdb525785fb8d815/resume.md","data/deliverables/resume_portfolio/by_company/thermo-fisher-scientific/2026-04-01/69cdac59cdb525785fb8d815/resume.md")</f>
       </c>
       <c r="Q1002"/>
       <c r="R1002">
@@ -64583,7 +64583,7 @@
         </is>
       </c>
       <c r="P1003">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/egen/2026-04-01/69cda26c398fb071abf7a98d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/egen/2026-04-01/69cda26c398fb071abf7a98d/resume.md")</f>
+        <f>HYPERLINK("by_company/egen/2026-04-01/69cda26c398fb071abf7a98d/resume.md","data/deliverables/resume_portfolio/by_company/egen/2026-04-01/69cda26c398fb071abf7a98d/resume.md")</f>
       </c>
       <c r="Q1003"/>
       <c r="R1003">
@@ -64707,7 +64707,7 @@
         </is>
       </c>
       <c r="P1005">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-01/69cd9310891d7b11cfcbdbf5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-01/69cd9310891d7b11cfcbdbf5/resume.md")</f>
+        <f>HYPERLINK("by_company/paypal/2026-04-01/69cd9310891d7b11cfcbdbf5/resume.md","data/deliverables/resume_portfolio/by_company/paypal/2026-04-01/69cd9310891d7b11cfcbdbf5/resume.md")</f>
       </c>
       <c r="Q1005"/>
       <c r="R1005">
@@ -64773,7 +64773,7 @@
         </is>
       </c>
       <c r="P1006">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/trimble-inc/2026-04-01/69cd92f3891d7b11cfcbdbcc/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/trimble-inc/2026-04-01/69cd92f3891d7b11cfcbdbcc/resume.md")</f>
+        <f>HYPERLINK("by_company/trimble-inc/2026-04-01/69cd92f3891d7b11cfcbdbcc/resume.md","data/deliverables/resume_portfolio/by_company/trimble-inc/2026-04-01/69cd92f3891d7b11cfcbdbcc/resume.md")</f>
       </c>
       <c r="Q1006"/>
       <c r="R1006">
@@ -64897,7 +64897,7 @@
         </is>
       </c>
       <c r="P1008">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fullsteam/2026-04-01/69cd8c1f366bb95ba54ffef6/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/fullsteam/2026-04-01/69cd8c1f366bb95ba54ffef6/resume.md")</f>
+        <f>HYPERLINK("by_company/fullsteam/2026-04-01/69cd8c1f366bb95ba54ffef6/resume.md","data/deliverables/resume_portfolio/by_company/fullsteam/2026-04-01/69cd8c1f366bb95ba54ffef6/resume.md")</f>
       </c>
       <c r="Q1008"/>
       <c r="R1008">
@@ -64963,7 +64963,7 @@
         </is>
       </c>
       <c r="P1009">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/state-street/2026-04-01/69c6510e1b5ad028873838ba/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/state-street/2026-04-01/69c6510e1b5ad028873838ba/resume.md")</f>
+        <f>HYPERLINK("by_company/state-street/2026-04-01/69c6510e1b5ad028873838ba/resume.md","data/deliverables/resume_portfolio/by_company/state-street/2026-04-01/69c6510e1b5ad028873838ba/resume.md")</f>
       </c>
       <c r="Q1009"/>
       <c r="R1009">
@@ -65153,7 +65153,7 @@
         </is>
       </c>
       <c r="P1012">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/chalk/2026-04-01/69892a320f6f7e7a2ce426df/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/chalk/2026-04-01/69892a320f6f7e7a2ce426df/resume.md")</f>
+        <f>HYPERLINK("by_company/chalk/2026-04-01/69892a320f6f7e7a2ce426df/resume.md","data/deliverables/resume_portfolio/by_company/chalk/2026-04-01/69892a320f6f7e7a2ce426df/resume.md")</f>
       </c>
       <c r="Q1012"/>
       <c r="R1012">
@@ -65343,7 +65343,7 @@
         </is>
       </c>
       <c r="P1015">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-01/6863199bf31c4006c6c3a06e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-01/6863199bf31c4006c6c3a06e/resume.md")</f>
+        <f>HYPERLINK("by_company/applied-intuition/2026-04-01/6863199bf31c4006c6c3a06e/resume.md","data/deliverables/resume_portfolio/by_company/applied-intuition/2026-04-01/6863199bf31c4006c6c3a06e/resume.md")</f>
       </c>
       <c r="Q1015"/>
       <c r="R1015">
@@ -65475,7 +65475,7 @@
         </is>
       </c>
       <c r="P1017">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualitest/2026-04-01/69cd8019891d7b11cfcb993e/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualitest/2026-04-01/69cd8019891d7b11cfcb993e/resume.md")</f>
+        <f>HYPERLINK("by_company/qualitest/2026-04-01/69cd8019891d7b11cfcb993e/resume.md","data/deliverables/resume_portfolio/by_company/qualitest/2026-04-01/69cd8019891d7b11cfcb993e/resume.md")</f>
       </c>
       <c r="Q1017"/>
       <c r="R1017">
@@ -65723,7 +65723,7 @@
         </is>
       </c>
       <c r="P1021">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/affirm/2026-04-01/69a1f3930da45516f16b3db5/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/affirm/2026-04-01/69a1f3930da45516f16b3db5/resume.md")</f>
+        <f>HYPERLINK("by_company/affirm/2026-04-01/69a1f3930da45516f16b3db5/resume.md","data/deliverables/resume_portfolio/by_company/affirm/2026-04-01/69a1f3930da45516f16b3db5/resume.md")</f>
       </c>
       <c r="Q1021"/>
       <c r="R1021">
@@ -65789,7 +65789,7 @@
         </is>
       </c>
       <c r="P1022">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/bloom-energy/2026-04-01/69cd644fcdb525785fb8744b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/bloom-energy/2026-04-01/69cd644fcdb525785fb8744b/resume.md")</f>
+        <f>HYPERLINK("by_company/bloom-energy/2026-04-01/69cd644fcdb525785fb8744b/resume.md","data/deliverables/resume_portfolio/by_company/bloom-energy/2026-04-01/69cd644fcdb525785fb8744b/resume.md")</f>
       </c>
       <c r="Q1022"/>
       <c r="R1022">
@@ -65913,7 +65913,7 @@
         </is>
       </c>
       <c r="P1024">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cotiviti/2026-04-01/69cd5fbacfdc6132f9417f65/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cotiviti/2026-04-01/69cd5fbacfdc6132f9417f65/resume.md")</f>
+        <f>HYPERLINK("by_company/cotiviti/2026-04-01/69cd5fbacfdc6132f9417f65/resume.md","data/deliverables/resume_portfolio/by_company/cotiviti/2026-04-01/69cd5fbacfdc6132f9417f65/resume.md")</f>
       </c>
       <c r="Q1024"/>
       <c r="R1024">
@@ -65979,7 +65979,7 @@
         </is>
       </c>
       <c r="P1025">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/github/2026-04-01/69b0af71dfaeda6ff59b045b/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/github/2026-04-01/69b0af71dfaeda6ff59b045b/resume.md")</f>
+        <f>HYPERLINK("by_company/github/2026-04-01/69b0af71dfaeda6ff59b045b/resume.md","data/deliverables/resume_portfolio/by_company/github/2026-04-01/69b0af71dfaeda6ff59b045b/resume.md")</f>
       </c>
       <c r="Q1025"/>
       <c r="R1025">
@@ -66045,7 +66045,7 @@
         </is>
       </c>
       <c r="P1026">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/lendbuzz/2026-04-01/69b18acb65de58104c70997c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/lendbuzz/2026-04-01/69b18acb65de58104c70997c/resume.md")</f>
+        <f>HYPERLINK("by_company/lendbuzz/2026-04-01/69b18acb65de58104c70997c/resume.md","data/deliverables/resume_portfolio/by_company/lendbuzz/2026-04-01/69b18acb65de58104c70997c/resume.md")</f>
       </c>
       <c r="Q1026"/>
       <c r="R1026">
@@ -66111,7 +66111,7 @@
         </is>
       </c>
       <c r="P1027">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/usi-insurance-services/2026-04-01/69163c04286ccf0a151339f6/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/usi-insurance-services/2026-04-01/69163c04286ccf0a151339f6/resume.md")</f>
+        <f>HYPERLINK("by_company/usi-insurance-services/2026-04-01/69163c04286ccf0a151339f6/resume.md","data/deliverables/resume_portfolio/by_company/usi-insurance-services/2026-04-01/69163c04286ccf0a151339f6/resume.md")</f>
       </c>
       <c r="Q1027"/>
       <c r="R1027">
@@ -66293,7 +66293,7 @@
         </is>
       </c>
       <c r="P1030">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/aig/2026-04-01/699397fece78e77b4fd76a48/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/aig/2026-04-01/699397fece78e77b4fd76a48/resume.md")</f>
+        <f>HYPERLINK("by_company/aig/2026-04-01/699397fece78e77b4fd76a48/resume.md","data/deliverables/resume_portfolio/by_company/aig/2026-04-01/699397fece78e77b4fd76a48/resume.md")</f>
       </c>
       <c r="Q1030"/>
       <c r="R1030">
@@ -66425,7 +66425,7 @@
         </is>
       </c>
       <c r="P1032">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cribl/2026-04-01/69b57b5c56973837413ac6e3/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cribl/2026-04-01/69b57b5c56973837413ac6e3/resume.md")</f>
+        <f>HYPERLINK("by_company/cribl/2026-04-01/69b57b5c56973837413ac6e3/resume.md","data/deliverables/resume_portfolio/by_company/cribl/2026-04-01/69b57b5c56973837413ac6e3/resume.md")</f>
       </c>
       <c r="Q1032"/>
       <c r="R1032">
@@ -66491,7 +66491,7 @@
         </is>
       </c>
       <c r="P1033">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nordstrom/2026-04-01/69b0d500749500645097dca8/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/nordstrom/2026-04-01/69b0d500749500645097dca8/resume.md")</f>
+        <f>HYPERLINK("by_company/nordstrom/2026-04-01/69b0d500749500645097dca8/resume.md","data/deliverables/resume_portfolio/by_company/nordstrom/2026-04-01/69b0d500749500645097dca8/resume.md")</f>
       </c>
       <c r="Q1033"/>
       <c r="R1033">
@@ -66557,7 +66557,7 @@
         </is>
       </c>
       <c r="P1034">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/scale-ai/2026-04-01/68e9e5abcdf8d94b293a2e83/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/scale-ai/2026-04-01/68e9e5abcdf8d94b293a2e83/resume.md")</f>
+        <f>HYPERLINK("by_company/scale-ai/2026-04-01/68e9e5abcdf8d94b293a2e83/resume.md","data/deliverables/resume_portfolio/by_company/scale-ai/2026-04-01/68e9e5abcdf8d94b293a2e83/resume.md")</f>
       </c>
       <c r="Q1034"/>
       <c r="R1034">
@@ -66623,7 +66623,7 @@
         </is>
       </c>
       <c r="P1035">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-01/6976813dbc8e722e7b1b1f91/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/amazon/2026-04-01/6976813dbc8e722e7b1b1f91/resume.md")</f>
+        <f>HYPERLINK("by_company/amazon/2026-04-01/6976813dbc8e722e7b1b1f91/resume.md","data/deliverables/resume_portfolio/by_company/amazon/2026-04-01/6976813dbc8e722e7b1b1f91/resume.md")</f>
       </c>
       <c r="Q1035"/>
       <c r="R1035">
@@ -66697,7 +66697,7 @@
         </is>
       </c>
       <c r="P1036">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualcomm/2026-04-01/69cd30bc398fb071abf72f55/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualcomm/2026-04-01/69cd30bc398fb071abf72f55/resume.md")</f>
+        <f>HYPERLINK("by_company/qualcomm/2026-04-01/69cd30bc398fb071abf72f55/resume.md","data/deliverables/resume_portfolio/by_company/qualcomm/2026-04-01/69cd30bc398fb071abf72f55/resume.md")</f>
       </c>
       <c r="Q1036"/>
       <c r="R1036">
@@ -66763,7 +66763,7 @@
         </is>
       </c>
       <c r="P1037">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualcomm/2026-04-01/69cd28e8891d7b11cfcb64a2/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/qualcomm/2026-04-01/69cd28e8891d7b11cfcb64a2/resume.md")</f>
+        <f>HYPERLINK("by_company/qualcomm/2026-04-01/69cd28e8891d7b11cfcb64a2/resume.md","data/deliverables/resume_portfolio/by_company/qualcomm/2026-04-01/69cd28e8891d7b11cfcb64a2/resume.md")</f>
       </c>
       <c r="Q1037"/>
       <c r="R1037">
@@ -66829,7 +66829,7 @@
         </is>
       </c>
       <c r="P1038">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/workday/2026-04-01/69ce811acfdc6132f9428f33/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/workday/2026-04-01/69ce811acfdc6132f9428f33/resume.md")</f>
+        <f>HYPERLINK("by_company/workday/2026-04-01/69ce811acfdc6132f9428f33/resume.md","data/deliverables/resume_portfolio/by_company/workday/2026-04-01/69ce811acfdc6132f9428f33/resume.md")</f>
       </c>
       <c r="Q1038"/>
       <c r="R1038">
@@ -66895,7 +66895,7 @@
         </is>
       </c>
       <c r="P1039">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/pure-storage/2026-04-01/68b0f6cce815524ae11fa204/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/pure-storage/2026-04-01/68b0f6cce815524ae11fa204/resume.md")</f>
+        <f>HYPERLINK("by_company/pure-storage/2026-04-01/68b0f6cce815524ae11fa204/resume.md","data/deliverables/resume_portfolio/by_company/pure-storage/2026-04-01/68b0f6cce815524ae11fa204/resume.md")</f>
       </c>
       <c r="Q1039"/>
       <c r="R1039">
@@ -66961,7 +66961,7 @@
         </is>
       </c>
       <c r="P1040">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tyler-technologies/2026-04-01/69b0a1170b2db6275c04e6f9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/tyler-technologies/2026-04-01/69b0a1170b2db6275c04e6f9/resume.md")</f>
+        <f>HYPERLINK("by_company/tyler-technologies/2026-04-01/69b0a1170b2db6275c04e6f9/resume.md","data/deliverables/resume_portfolio/by_company/tyler-technologies/2026-04-01/69b0a1170b2db6275c04e6f9/resume.md")</f>
       </c>
       <c r="Q1040"/>
       <c r="R1040">
@@ -67151,7 +67151,7 @@
         </is>
       </c>
       <c r="P1043">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/klaviyo/2026-04-01/69b085680b2db6275c049f13/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/klaviyo/2026-04-01/69b085680b2db6275c049f13/resume.md")</f>
+        <f>HYPERLINK("by_company/klaviyo/2026-04-01/69b085680b2db6275c049f13/resume.md","data/deliverables/resume_portfolio/by_company/klaviyo/2026-04-01/69b085680b2db6275c049f13/resume.md")</f>
       </c>
       <c r="Q1043"/>
       <c r="R1043">
@@ -67283,7 +67283,7 @@
         </is>
       </c>
       <c r="P1045">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/together-ai/2026-04-01/69b0758ddfaeda6ff59a4ff9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/together-ai/2026-04-01/69b0758ddfaeda6ff59a4ff9/resume.md")</f>
+        <f>HYPERLINK("by_company/together-ai/2026-04-01/69b0758ddfaeda6ff59a4ff9/resume.md","data/deliverables/resume_portfolio/by_company/together-ai/2026-04-01/69b0758ddfaeda6ff59a4ff9/resume.md")</f>
       </c>
       <c r="Q1045"/>
       <c r="R1045">
@@ -67413,7 +67413,7 @@
         </is>
       </c>
       <c r="P1047">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-01/6994e428ce78e77b4fd8f521/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/paypal/2026-04-01/6994e428ce78e77b4fd8f521/resume.md")</f>
+        <f>HYPERLINK("by_company/paypal/2026-04-01/6994e428ce78e77b4fd8f521/resume.md","data/deliverables/resume_portfolio/by_company/paypal/2026-04-01/6994e428ce78e77b4fd8f521/resume.md")</f>
       </c>
       <c r="Q1047"/>
       <c r="R1047">
@@ -67479,7 +67479,7 @@
         </is>
       </c>
       <c r="P1048">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/oclc/2026-04-01/6993b60cce78e77b4fd78b60/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/oclc/2026-04-01/6993b60cce78e77b4fd78b60/resume.md")</f>
+        <f>HYPERLINK("by_company/oclc/2026-04-01/6993b60cce78e77b4fd78b60/resume.md","data/deliverables/resume_portfolio/by_company/oclc/2026-04-01/6993b60cce78e77b4fd78b60/resume.md")</f>
       </c>
       <c r="Q1048"/>
       <c r="R1048">
@@ -67611,7 +67611,7 @@
         </is>
       </c>
       <c r="P1050">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/zoox/2026-04-01/69252701d47de4798eccd7d9/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/zoox/2026-04-01/69252701d47de4798eccd7d9/resume.md")</f>
+        <f>HYPERLINK("by_company/zoox/2026-04-01/69252701d47de4798eccd7d9/resume.md","data/deliverables/resume_portfolio/by_company/zoox/2026-04-01/69252701d47de4798eccd7d9/resume.md")</f>
       </c>
       <c r="Q1050"/>
       <c r="R1050">
@@ -67677,7 +67677,7 @@
         </is>
       </c>
       <c r="P1051">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/waystar/2026-04-01/69c7850faa3c2c1995e1916c/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/waystar/2026-04-01/69c7850faa3c2c1995e1916c/resume.md")</f>
+        <f>HYPERLINK("by_company/waystar/2026-04-01/69c7850faa3c2c1995e1916c/resume.md","data/deliverables/resume_portfolio/by_company/waystar/2026-04-01/69c7850faa3c2c1995e1916c/resume.md")</f>
       </c>
       <c r="Q1051"/>
       <c r="R1051">
@@ -67801,7 +67801,7 @@
         </is>
       </c>
       <c r="P1053">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cadence/2026-04-01/69af4318dfaeda6ff5976464/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/cadence/2026-04-01/69af4318dfaeda6ff5976464/resume.md")</f>
+        <f>HYPERLINK("by_company/cadence/2026-04-01/69af4318dfaeda6ff5976464/resume.md","data/deliverables/resume_portfolio/by_company/cadence/2026-04-01/69af4318dfaeda6ff5976464/resume.md")</f>
       </c>
       <c r="Q1053"/>
       <c r="R1053">
@@ -67875,7 +67875,7 @@
         </is>
       </c>
       <c r="P1054">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/orchard/2026-04-01/69ccb759cfdc6132f9412768/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/orchard/2026-04-01/69ccb759cfdc6132f9412768/resume.md")</f>
+        <f>HYPERLINK("by_company/orchard/2026-04-01/69ccb759cfdc6132f9412768/resume.md","data/deliverables/resume_portfolio/by_company/orchard/2026-04-01/69ccb759cfdc6132f9412768/resume.md")</f>
       </c>
       <c r="Q1054"/>
       <c r="R1054">
@@ -67941,7 +67941,7 @@
         </is>
       </c>
       <c r="P1055">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/vorto/2026-03-31/69cca2c8cfdc6132f94115cd/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/vorto/2026-03-31/69cca2c8cfdc6132f94115cd/resume.md")</f>
+        <f>HYPERLINK("by_company/vorto/2026-03-31/69cca2c8cfdc6132f94115cd/resume.md","data/deliverables/resume_portfolio/by_company/vorto/2026-03-31/69cca2c8cfdc6132f94115cd/resume.md")</f>
       </c>
       <c r="Q1055"/>
       <c r="R1055">
@@ -68007,7 +68007,7 @@
         </is>
       </c>
       <c r="P1056">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ondo-finance/2026-03-31/69cc942b891d7b11cfcb01d2/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/ondo-finance/2026-03-31/69cc942b891d7b11cfcb01d2/resume.md")</f>
+        <f>HYPERLINK("by_company/ondo-finance/2026-03-31/69cc942b891d7b11cfcb01d2/resume.md","data/deliverables/resume_portfolio/by_company/ondo-finance/2026-03-31/69cc942b891d7b11cfcb01d2/resume.md")</f>
       </c>
       <c r="Q1056"/>
       <c r="R1056">
@@ -68139,7 +68139,7 @@
         </is>
       </c>
       <c r="P1058">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/electronic-arts-ea/2026-03-31/69cc8855cfdc6132f940f397/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/electronic-arts-ea/2026-03-31/69cc8855cfdc6132f940f397/resume.md")</f>
+        <f>HYPERLINK("by_company/electronic-arts-ea/2026-03-31/69cc8855cfdc6132f940f397/resume.md","data/deliverables/resume_portfolio/by_company/electronic-arts-ea/2026-03-31/69cc8855cfdc6132f940f397/resume.md")</f>
       </c>
       <c r="Q1058"/>
       <c r="R1058">
@@ -68205,7 +68205,7 @@
         </is>
       </c>
       <c r="P1059">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/luminai/2026-03-31/69cc8152366bb95ba54f0d79/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/luminai/2026-03-31/69cc8152366bb95ba54f0d79/resume.md")</f>
+        <f>HYPERLINK("by_company/luminai/2026-03-31/69cc8152366bb95ba54f0d79/resume.md","data/deliverables/resume_portfolio/by_company/luminai/2026-03-31/69cc8152366bb95ba54f0d79/resume.md")</f>
       </c>
       <c r="Q1059"/>
       <c r="R1059">
@@ -68271,7 +68271,7 @@
         </is>
       </c>
       <c r="P1060">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/eightfold-ai/2026-03-31/69cc7ae3366bb95ba54efb65/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/eightfold-ai/2026-03-31/69cc7ae3366bb95ba54efb65/resume.md")</f>
+        <f>HYPERLINK("by_company/eightfold-ai/2026-03-31/69cc7ae3366bb95ba54efb65/resume.md","data/deliverables/resume_portfolio/by_company/eightfold-ai/2026-03-31/69cc7ae3366bb95ba54efb65/resume.md")</f>
       </c>
       <c r="Q1060"/>
       <c r="R1060">
@@ -68345,7 +68345,7 @@
         </is>
       </c>
       <c r="P1061">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/exl/2026-03-31/69cc936c366bb95ba54f3134/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/exl/2026-03-31/69cc936c366bb95ba54f3134/resume.md")</f>
+        <f>HYPERLINK("by_company/exl/2026-03-31/69cc936c366bb95ba54f3134/resume.md","data/deliverables/resume_portfolio/by_company/exl/2026-03-31/69cc936c366bb95ba54f3134/resume.md")</f>
       </c>
       <c r="Q1061"/>
       <c r="R1061">
@@ -68411,7 +68411,7 @@
         </is>
       </c>
       <c r="P1062">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kohl-s/2026-03-31/69be41ce482822729301078d/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/kohl-s/2026-03-31/69be41ce482822729301078d/resume.md")</f>
+        <f>HYPERLINK("by_company/kohl-s/2026-03-31/69be41ce482822729301078d/resume.md","data/deliverables/resume_portfolio/by_company/kohl-s/2026-03-31/69be41ce482822729301078d/resume.md")</f>
       </c>
       <c r="Q1062"/>
       <c r="R1062">
@@ -68477,7 +68477,7 @@
         </is>
       </c>
       <c r="P1063">
-        <f>HYPERLINK("file:///Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/harbourvest-partners/2026-03-31/69cc8379891d7b11cfcae5f2/resume.md","/Users/jingyizhang/Documents/Playground/projects/local_job_resume_pipeline/data/deliverables/resume_portfolio/by_company/harbourvest-partners/2026-03-31/69cc8379891d7b11cfcae5f2/resume.md")</f>
+        <f>HYPERLINK("by_company/harbourvest-partners/2026-03-31/69cc8379891d7b11cfcae5f2/resume.md","data/deliverables/resume_portfolio/by_company/harbourvest-partners/2026-03-31/69cc8379891d7b11cfcae5f2/resume.md")</f>
       </c>
       <c r="Q1063"/>
       <c r="R1063">
